--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7891D4-3A17-42C0-A3CF-0696335B58AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55427D72-6C7A-4CC6-AB02-F71DF2A2DBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'6-2026'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'6-2026'!$A$2:$G$8</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -57,25 +57,19 @@
     <t>Nội dung</t>
   </si>
   <si>
-    <t>Trạng thái</t>
-  </si>
-  <si>
     <t>Xử lý thiết bị BH A. Tuấn BG</t>
   </si>
   <si>
     <t>Nhận thiết bị BH A. Trực</t>
   </si>
   <si>
-    <t>Hoàn thành</t>
-  </si>
-  <si>
-    <t>Chưa hoàn thành</t>
-  </si>
-  <si>
-    <t>Nhập kho RFID</t>
-  </si>
-  <si>
-    <t>Test hoàn thiện thành phẩm VNSH03</t>
+    <t>Nhập kho 200 CardReader</t>
+  </si>
+  <si>
+    <t>Lấy 100 mỗi loại (anten GPS, GSM, dây nguồn LE tổng 200/500 xuất kho)</t>
+  </si>
+  <si>
+    <t>Nhập kho 12/27 thiết bị VNSH03 nhận ngày 29/06/26</t>
   </si>
 </sst>
 </file>
@@ -118,7 +112,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -178,144 +172,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -625,169 +548,165 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="6" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>46202</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>46202</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3" t="s">
+      <c r="C9" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="4" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>46203</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>10</v>
+      <c r="C12" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
+  <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
     <filterColumn colId="2" showButton="0"/>
     <filterColumn colId="3" showButton="0"/>
     <filterColumn colId="4" showButton="0"/>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
-  <mergeCells count="10">
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C7:G7"/>
+  <mergeCells count="12">
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="C7:G7"/>
   </mergeCells>
-  <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>H1="Hoàn thành"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>H1="Chưa hoàn thành"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55427D72-6C7A-4CC6-AB02-F71DF2A2DBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2777622-2661-4594-B0E4-876C97CC2685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -63,13 +63,16 @@
     <t>Nhận thiết bị BH A. Trực</t>
   </si>
   <si>
-    <t>Nhập kho 200 CardReader</t>
-  </si>
-  <si>
-    <t>Lấy 100 mỗi loại (anten GPS, GSM, dây nguồn LE tổng 200/500 xuất kho)</t>
-  </si>
-  <si>
-    <t>Nhập kho 12/27 thiết bị VNSH03 nhận ngày 29/06/26</t>
+    <t>Nhận 53 VNSH03 X-Force gửi qua</t>
+  </si>
+  <si>
+    <t>Nhập kho 100 CardReader</t>
+  </si>
+  <si>
+    <t>Nhập kho 22/27 thiết bị VNSH03 nhận ngày 29/06/26</t>
+  </si>
+  <si>
+    <t>Xuất kho 100 mỗi loại (anten GPS, GSM, dây nguồn LE tổng 200/500 xuất kho)</t>
   </si>
 </sst>
 </file>
@@ -112,7 +115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -175,15 +178,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -194,11 +188,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -209,30 +212,28 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,22 +549,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="69.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="14">
+      <c r="A1" s="3">
         <v>46174</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -572,119 +574,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="15">
         <v>46202</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6" t="s">
+      <c r="A7" s="15"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="15"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="A9" s="15">
         <v>46203</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="10" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="12" t="s">
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C13" s="12" t="s">
         <v>9</v>
       </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -693,9 +722,11 @@
     <filterColumn colId="4" showButton="0"/>
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
-  <mergeCells count="12">
+  <mergeCells count="18">
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="A3:A8"/>
-    <mergeCell ref="B9:B11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -706,6 +737,10 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2777622-2661-4594-B0E4-876C97CC2685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D229781C-B3D7-4E91-8644-16E33AB8B6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="07-2026" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'6-2026'!$A$2:$G$8</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -73,6 +74,18 @@
   </si>
   <si>
     <t>Xuất kho 100 mỗi loại (anten GPS, GSM, dây nguồn LE tổng 200/500 xuất kho)</t>
+  </si>
+  <si>
+    <t>Nhập kho 40 thiết bị VNSH03</t>
+  </si>
+  <si>
+    <t>Xuất kho đổi BH 1 thiết bị VNSH03 SEA, thiết bị cũ giữ lại gửi qua X-Force xử lý</t>
+  </si>
+  <si>
+    <t>Xử lý xong thiết bị BH của Victory chưa trả</t>
+  </si>
+  <si>
+    <t>Xử lý xong thiết bị BH A.Tuấn BG chưa trả</t>
   </si>
 </sst>
 </file>
@@ -188,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -196,6 +209,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -223,17 +248,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,15 +582,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="3">
+      <c r="A1" s="7">
         <v>46174</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -574,146 +599,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="6">
         <v>46202</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="6">
         <v>46203</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="12" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="14"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="12" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="12" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="6"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -723,6 +748,8 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
@@ -739,8 +766,113 @@
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="19">
+        <v>46204</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
+        <v>46205</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D229781C-B3D7-4E91-8644-16E33AB8B6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5389BC2F-1CA5-4E4D-94A6-D04BE5237CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -86,6 +86,27 @@
   </si>
   <si>
     <t>Xử lý xong thiết bị BH A.Tuấn BG chưa trả</t>
+  </si>
+  <si>
+    <t>Nhập kho 12 VNSH02</t>
+  </si>
+  <si>
+    <t>Trả BH Victory - Tuấn Anh</t>
+  </si>
+  <si>
+    <t>Trả BH Anh Tuấn BG - A. Lực</t>
+  </si>
+  <si>
+    <t>Trả BH SEA - A. Bảo</t>
+  </si>
+  <si>
+    <t>Gửi BH X-Force 1 VNSH03 - VNET861385071484094 (gửi A. Cảnh)</t>
+  </si>
+  <si>
+    <t>Gửi X-Force BH 1 VNSH03 - VNET861385071545191 X-Force ( gửi A. Cảnh)</t>
+  </si>
+  <si>
+    <t>Nhận 9 LE nâng cấp 2G-&gt;4G anh Tuấn BG</t>
   </si>
 </sst>
 </file>
@@ -128,7 +149,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -197,11 +218,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -210,6 +268,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -239,26 +306,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -582,15 +658,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="7">
+      <c r="A1" s="10">
         <v>46174</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -599,146 +675,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="9">
         <v>46202</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="9">
         <v>46203</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="3" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="5"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="3" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
+      <c r="A13" s="9"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="5"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -748,11 +824,8 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -764,8 +837,11 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -773,25 +849,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="19">
+      <c r="A1" s="16">
         <v>46204</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -800,71 +876,159 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="9">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17">
+      <c r="A7" s="20">
         <v>46205</v>
       </c>
+      <c r="B7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="18">
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="A3:A6"/>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5389BC2F-1CA5-4E4D-94A6-D04BE5237CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100DCEA3-4DBD-41BB-B98D-35031B4CDE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -107,6 +107,24 @@
   </si>
   <si>
     <t>Nhận 9 LE nâng cấp 2G-&gt;4G anh Tuấn BG</t>
+  </si>
+  <si>
+    <t>Nhập kho 23 thiết bị VNSH03</t>
+  </si>
+  <si>
+    <t>Nhập kho 100 RFID</t>
+  </si>
+  <si>
+    <t>Xuất 100 anten GSM + GPS + dây nguồn LE trong tổng là 300/500</t>
+  </si>
+  <si>
+    <t>Nhận 1 ACT-01 từ kho dán lại tem đã trả trong ngày</t>
+  </si>
+  <si>
+    <t>Xuất kho 80 nắp chặn quạt gió, 10 nắp chặn nguồn vỏ hộp VNSH03 gửi qua X-Force (A. Cảnh)</t>
+  </si>
+  <si>
+    <t>Xuất linh kiện BH chưa trả kho phiếu (thứ 06/06/26 làm phiếu trả sau)</t>
   </si>
 </sst>
 </file>
@@ -259,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -268,6 +286,36 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -285,25 +333,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -315,25 +360,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -658,15 +691,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="10">
+      <c r="A1" s="8">
         <v>46174</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -675,146 +708,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="14"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="6">
         <v>46202</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="A9" s="6">
         <v>46203</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="6" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="6" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
+      <c r="A13" s="6"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -824,6 +857,8 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="A3:A8"/>
@@ -840,8 +875,6 @@
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -849,25 +882,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" customWidth="1"/>
+    <col min="3" max="3" width="45.28515625" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="16">
+      <c r="A1" s="25">
         <v>46204</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -876,149 +909,237 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="6">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="15" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+      <c r="A7" s="19">
         <v>46205</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="20"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="8"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="6" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="20"/>
+      <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="20"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="18"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="6" t="s">
+      <c r="A12" s="20"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="22"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="6" t="s">
+      <c r="A13" s="21"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
+        <v>46206</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="29"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="29"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="29"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="15"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="29"/>
+      <c r="B18" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="15"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="30"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="26">
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A7:A13"/>
     <mergeCell ref="B7:B9"/>
@@ -1029,14 +1150,6 @@
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100DCEA3-4DBD-41BB-B98D-35031B4CDE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD2859A-4E7B-45B5-BA31-CC9D0CA6626B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -125,6 +125,48 @@
   </si>
   <si>
     <t>Xuất linh kiện BH chưa trả kho phiếu (thứ 06/06/26 làm phiếu trả sau)</t>
+  </si>
+  <si>
+    <t>Xuất kho linh kiện bảo hành cho VNSH01-VNSH02</t>
+  </si>
+  <si>
+    <t>Nhận 200 VNSH03 X-Force giao qua (A. Cảnh)</t>
+  </si>
+  <si>
+    <t>Kế toán kho Mai lấy 2 thiết bị CAM 2 mắt (Tồn 29/31 bộ bình thường)</t>
+  </si>
+  <si>
+    <t>Nhận BH A. Tuấn BG</t>
+  </si>
+  <si>
+    <t>Nhận BH Việt Bảo Tín</t>
+  </si>
+  <si>
+    <t>Nhận BH GPS Tây Ninh</t>
+  </si>
+  <si>
+    <t>Nhận BH A. Trực</t>
+  </si>
+  <si>
+    <t>Nhận BH Victory</t>
+  </si>
+  <si>
+    <t>Nhận BH A. Thái QN</t>
+  </si>
+  <si>
+    <t>Nhận BH Nhật Quang</t>
+  </si>
+  <si>
+    <t>Nhận BH A. Hồng PT</t>
+  </si>
+  <si>
+    <t>Nhận BH Ngọc Hoàn</t>
+  </si>
+  <si>
+    <t>Nhận BH Trần tài</t>
+  </si>
+  <si>
+    <t>Nhận BH Etuka</t>
   </si>
 </sst>
 </file>
@@ -277,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -294,6 +336,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -324,14 +375,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -342,32 +411,8 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -691,15 +736,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8">
+      <c r="A1" s="11">
         <v>46174</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -708,146 +753,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="9">
         <v>46202</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="9">
         <v>46203</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="16" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="16" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="18"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="16" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="18"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
+      <c r="A13" s="9"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -857,11 +902,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -872,6 +912,11 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
@@ -882,7 +927,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -918,23 +963,23 @@
       <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="9">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="27" t="s">
@@ -946,115 +991,115 @@
       <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
+      <c r="A7" s="28">
         <v>46205</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="16" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="16" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
-      <c r="B10" s="7" t="s">
+      <c r="A10" s="29"/>
+      <c r="B10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="16" t="s">
+      <c r="A11" s="29"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="18"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="16" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="18"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="16" t="s">
+      <c r="A13" s="30"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="18"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
+      <c r="A14" s="22">
         <v>46206</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="19" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1066,71 +1111,256 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="13" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="13" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="13" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="31">
+        <v>46209</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="31"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="31"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="31"/>
+      <c r="B23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="31"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="31"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="31"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="18"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="31"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="31"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="31"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="18"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="31"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="18"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="31"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="18"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="31"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="31"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="31"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
+  <mergeCells count="44">
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -1147,9 +1377,13 @@
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD2859A-4E7B-45B5-BA31-CC9D0CA6626B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE06B0AC-B9C1-42D3-B57A-CD4A1D98C2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -167,6 +167,33 @@
   </si>
   <si>
     <t>Nhận BH Etuka</t>
+  </si>
+  <si>
+    <t>Nhập kho 15 VNSH03</t>
+  </si>
+  <si>
+    <t>Trả 29 CAM 2 mắt (còn tồn 137 CAM 2 mắt)</t>
+  </si>
+  <si>
+    <t>Trả BH Victory (A.Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Trần Tài (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH AT. Việt Nam (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Ngọc Hoàn - trả trước 6 thiết bị (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Etuka (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Nhật Quang (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH ID: 0032002605 (A. Bảo)</t>
   </si>
 </sst>
 </file>
@@ -319,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -336,6 +363,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -348,24 +393,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -375,14 +402,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -411,8 +432,20 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -736,15 +769,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="11">
+      <c r="A1" s="6">
         <v>46174</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -753,91 +786,91 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="15">
         <v>46202</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10" t="s">
+      <c r="A7" s="15"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10" t="s">
+      <c r="A8" s="15"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="A9" s="15">
         <v>46203</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -849,50 +882,50 @@
       <c r="G9" s="18"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="6" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="15"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="6" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -902,6 +935,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -912,14 +953,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -927,7 +960,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -937,15 +970,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="25">
+      <c r="A1" s="23">
         <v>46204</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -954,69 +987,69 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="15">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="A7" s="26">
         <v>46205</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="29" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="16" t="s">
@@ -1028,78 +1061,78 @@
       <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="27"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="8"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="6" t="s">
+      <c r="A9" s="27"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="10" t="s">
+      <c r="A10" s="27"/>
+      <c r="B10" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="6" t="s">
+      <c r="A12" s="27"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="8"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="6" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="20">
         <v>46206</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="29" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1111,8 +1144,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
-      <c r="B15" s="21"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="30"/>
       <c r="C15" s="16" t="s">
         <v>26</v>
       </c>
@@ -1122,8 +1155,8 @@
       <c r="G15" s="18"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="23"/>
-      <c r="B16" s="21"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="16" t="s">
         <v>28</v>
       </c>
@@ -1133,8 +1166,8 @@
       <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="20"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="16" t="s">
         <v>27</v>
       </c>
@@ -1144,8 +1177,8 @@
       <c r="G17" s="18"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="19" t="s">
+      <c r="A18" s="21"/>
+      <c r="B18" s="29" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="16" t="s">
@@ -1157,8 +1190,8 @@
       <c r="G18" s="18"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="20"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="16" t="s">
         <v>31</v>
       </c>
@@ -1168,58 +1201,58 @@
       <c r="G19" s="18"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="31">
+      <c r="A20" s="19">
         <v>46209</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="31"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10" t="s">
+      <c r="A21" s="19"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="31"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10" t="s">
+      <c r="A22" s="19"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="31"/>
-      <c r="B23" s="10" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="31"/>
-      <c r="B24" s="10"/>
+      <c r="A24" s="19"/>
+      <c r="B24" s="11"/>
       <c r="C24" s="16" t="s">
         <v>35</v>
       </c>
@@ -1229,8 +1262,8 @@
       <c r="G24" s="18"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="31"/>
-      <c r="B25" s="10"/>
+      <c r="A25" s="19"/>
+      <c r="B25" s="11"/>
       <c r="C25" s="16" t="s">
         <v>36</v>
       </c>
@@ -1240,8 +1273,8 @@
       <c r="G25" s="18"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="31"/>
-      <c r="B26" s="10"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="11"/>
       <c r="C26" s="16" t="s">
         <v>37</v>
       </c>
@@ -1251,8 +1284,8 @@
       <c r="G26" s="18"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="31"/>
-      <c r="B27" s="10"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="11"/>
       <c r="C27" s="16" t="s">
         <v>38</v>
       </c>
@@ -1262,8 +1295,8 @@
       <c r="G27" s="18"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="31"/>
-      <c r="B28" s="10"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="11"/>
       <c r="C28" s="16" t="s">
         <v>39</v>
       </c>
@@ -1273,8 +1306,8 @@
       <c r="G28" s="18"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="31"/>
-      <c r="B29" s="10"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="16" t="s">
         <v>40</v>
       </c>
@@ -1284,8 +1317,8 @@
       <c r="G29" s="18"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="31"/>
-      <c r="B30" s="10"/>
+      <c r="A30" s="19"/>
+      <c r="B30" s="11"/>
       <c r="C30" s="16" t="s">
         <v>45</v>
       </c>
@@ -1295,8 +1328,8 @@
       <c r="G30" s="18"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="31"/>
-      <c r="B31" s="10"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="11"/>
       <c r="C31" s="16" t="s">
         <v>41</v>
       </c>
@@ -1306,8 +1339,8 @@
       <c r="G31" s="18"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="31"/>
-      <c r="B32" s="10"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="11"/>
       <c r="C32" s="16" t="s">
         <v>42</v>
       </c>
@@ -1317,8 +1350,8 @@
       <c r="G32" s="18"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="31"/>
-      <c r="B33" s="10"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="11"/>
       <c r="C33" s="16" t="s">
         <v>43</v>
       </c>
@@ -1328,8 +1361,8 @@
       <c r="G33" s="18"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="31"/>
-      <c r="B34" s="10"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="11"/>
       <c r="C34" s="16" t="s">
         <v>44</v>
       </c>
@@ -1338,29 +1371,137 @@
       <c r="F34" s="17"/>
       <c r="G34" s="18"/>
     </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="33">
+        <v>46210</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="33"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="33"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="33"/>
+      <c r="B38" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="33"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="33"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="33"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="33"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="33"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="33"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="18"/>
+    </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
+  <mergeCells count="57">
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -1377,6 +1518,21 @@
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C19:G19"/>
@@ -1384,6 +1540,12 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE06B0AC-B9C1-42D3-B57A-CD4A1D98C2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA31980-610E-4AE5-922C-7E80E33B531B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -194,6 +194,9 @@
   </si>
   <si>
     <t>Trả BH ID: 0032002605 (A. Bảo)</t>
+  </si>
+  <si>
+    <t>Nộp lại cho kế toán phí sửa chữa ID: 00320026F0 (600k)</t>
   </si>
 </sst>
 </file>
@@ -346,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -363,6 +366,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -379,73 +409,49 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -769,15 +775,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6">
+      <c r="A1" s="15">
         <v>46174</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -786,16 +792,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="10">
         <v>46202</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -810,7 +816,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11" t="s">
         <v>0</v>
@@ -821,7 +827,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="10"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
         <v>3</v>
@@ -832,7 +838,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
+      <c r="A6" s="10"/>
       <c r="B6" s="11" t="s">
         <v>4</v>
       </c>
@@ -845,7 +851,7 @@
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="10"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11" t="s">
         <v>10</v>
@@ -856,7 +862,7 @@
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="11" t="s">
         <v>9</v>
@@ -867,65 +873,65 @@
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
+      <c r="A9" s="10">
         <v>46203</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="18"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="11"/>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="14"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="11"/>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -935,14 +941,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -953,6 +951,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -960,7 +966,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -970,15 +976,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="23">
+      <c r="A1" s="25">
         <v>46204</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -987,16 +993,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+      <c r="A3" s="10">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1011,20 +1017,20 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="10"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
         <v>17</v>
@@ -1035,7 +1041,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
+      <c r="A6" s="10"/>
       <c r="B6" s="11"/>
       <c r="C6" s="11" t="s">
         <v>18</v>
@@ -1046,93 +1052,93 @@
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="28">
         <v>46205</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="18"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="12" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="14"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="11"/>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="11"/>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+      <c r="A14" s="22">
         <v>46206</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1144,64 +1150,64 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="16" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="18"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="16" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="18"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="16" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="18"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="14"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="22"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="16" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="14"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="19">
+      <c r="A20" s="34">
         <v>46209</v>
       </c>
       <c r="B20" s="11" t="s">
@@ -1216,7 +1222,7 @@
       <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
+      <c r="A21" s="34"/>
       <c r="B21" s="11"/>
       <c r="C21" s="11" t="s">
         <v>34</v>
@@ -1227,7 +1233,7 @@
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11" t="s">
         <v>15</v>
@@ -1238,7 +1244,7 @@
       <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
+      <c r="A23" s="34"/>
       <c r="B23" s="11" t="s">
         <v>4</v>
       </c>
@@ -1251,128 +1257,128 @@
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
+      <c r="A24" s="34"/>
       <c r="B24" s="11"/>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="18"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="11"/>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="18"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="11"/>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="18"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
+      <c r="A27" s="34"/>
       <c r="B27" s="11"/>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="18"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="14"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="11"/>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="18"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="11"/>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="18"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="14"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="19"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="11"/>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="18"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="14"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="18"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
+      <c r="A32" s="34"/>
       <c r="B32" s="11"/>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="18"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="14"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
+      <c r="A33" s="34"/>
       <c r="B33" s="11"/>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="18"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="11"/>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="18"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="33">
+      <c r="A35" s="21">
         <v>46210</v>
       </c>
       <c r="B35" s="11" t="s">
@@ -1387,7 +1393,7 @@
       <c r="G35" s="11"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="11"/>
       <c r="C36" s="11" t="s">
         <v>27</v>
@@ -1398,7 +1404,7 @@
       <c r="G36" s="11"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11" t="s">
         <v>47</v>
@@ -1409,8 +1415,8 @@
       <c r="G37" s="11"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
-      <c r="B38" s="32" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="20" t="s">
         <v>4</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -1422,8 +1428,8 @@
       <c r="G38" s="11"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="33"/>
-      <c r="B39" s="32"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="20"/>
       <c r="C39" s="11" t="s">
         <v>53</v>
       </c>
@@ -1433,8 +1439,8 @@
       <c r="G39" s="11"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="33"/>
-      <c r="B40" s="32"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="20"/>
       <c r="C40" s="11" t="s">
         <v>48</v>
       </c>
@@ -1444,8 +1450,8 @@
       <c r="G40" s="11"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
-      <c r="B41" s="32"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="20"/>
       <c r="C41" s="11" t="s">
         <v>49</v>
       </c>
@@ -1455,8 +1461,8 @@
       <c r="G41" s="11"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="33"/>
-      <c r="B42" s="32"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="20"/>
       <c r="C42" s="11" t="s">
         <v>50</v>
       </c>
@@ -1466,8 +1472,8 @@
       <c r="G42" s="11"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="33"/>
-      <c r="B43" s="32"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="20"/>
       <c r="C43" s="11" t="s">
         <v>51</v>
       </c>
@@ -1477,29 +1483,64 @@
       <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="33"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="16" t="s">
+      <c r="A44" s="21"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="18"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="14"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>46211</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="B38:B44"/>
+  <mergeCells count="58">
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -1516,36 +1557,17 @@
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA31980-610E-4AE5-922C-7E80E33B531B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8202AACF-D1EB-428E-A4D1-94F5D0D6AD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -197,6 +197,9 @@
   </si>
   <si>
     <t>Nộp lại cho kế toán phí sửa chữa ID: 00320026F0 (600k)</t>
+  </si>
+  <si>
+    <t>Trả BH SEA, trả 10 thiết bị (A. Lực)</t>
   </si>
 </sst>
 </file>
@@ -349,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -369,6 +372,24 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -381,78 +402,61 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,15 +779,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="15">
+      <c r="A1" s="7">
         <v>46174</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -792,146 +796,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="16">
         <v>46202</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="16">
         <v>46203</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="9"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="7" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="15"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -941,6 +945,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -951,14 +963,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -966,7 +970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -976,15 +980,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="25">
+      <c r="A1" s="28">
         <v>46204</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -993,152 +997,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="16">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="A7" s="31">
         <v>46205</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="7" t="s">
+      <c r="A8" s="32"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="7" t="s">
+      <c r="A9" s="32"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="32"/>
+      <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="32"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="9"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="15"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="7" t="s">
+      <c r="A12" s="32"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="7" t="s">
+      <c r="A13" s="33"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="15"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="25">
         <v>46206</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="20" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1150,348 +1154,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="12" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="23"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="12" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="14"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="19"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="12" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="31" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="12" t="s">
+      <c r="A19" s="27"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
+      <c r="A20" s="23">
         <v>46209</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="11" t="s">
+      <c r="A23" s="23"/>
+      <c r="B23" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12" t="s">
+      <c r="A24" s="23"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="14"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12" t="s">
+      <c r="A26" s="23"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="14"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="19"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="14"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="14"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12" t="s">
+      <c r="A29" s="23"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="14"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="14"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12" t="s">
+      <c r="A31" s="23"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="14"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="19"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12" t="s">
+      <c r="A32" s="23"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="14"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="19"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12" t="s">
+      <c r="A33" s="23"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="14"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="19"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="14"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="19"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="21">
+      <c r="A35" s="24">
         <v>46210</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11" t="s">
+      <c r="A36" s="24"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11" t="s">
+      <c r="A37" s="24"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
-      <c r="B38" s="20" t="s">
+      <c r="A38" s="24"/>
+      <c r="B38" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="11" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="11" t="s">
+      <c r="A40" s="24"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="21"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="11" t="s">
+      <c r="A41" s="24"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="21"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="11" t="s">
+      <c r="A42" s="24"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="11" t="s">
+      <c r="A43" s="24"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="21"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="12" t="s">
+      <c r="A44" s="24"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="14"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="19"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1500,31 +1504,55 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="35">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C23:G23"/>
@@ -1541,33 +1569,22 @@
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="C20:G20"/>
     <mergeCell ref="C21:G21"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
     <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8202AACF-D1EB-428E-A4D1-94F5D0D6AD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3C216C-FA41-4D52-8ACA-D7BB5B73384E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -199,7 +199,7 @@
     <t>Nộp lại cho kế toán phí sửa chữa ID: 00320026F0 (600k)</t>
   </si>
   <si>
-    <t>Trả BH SEA, trả 10 thiết bị (A. Lực)</t>
+    <t>Nhận BH Victory VNSH03 (đã làm phiếu đổi trả thiết bị mới)</t>
   </si>
 </sst>
 </file>
@@ -372,6 +372,30 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -388,75 +412,51 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,15 +779,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="7">
+      <c r="A1" s="15">
         <v>46174</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -796,146 +796,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="10">
         <v>46202</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
+      <c r="A9" s="10">
         <v>46203</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="15"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13" t="s">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="15"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="15"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -945,14 +945,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -963,6 +955,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -970,7 +970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -980,15 +980,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="28">
+      <c r="A1" s="25">
         <v>46204</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -997,152 +997,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="10">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="31">
+      <c r="A7" s="28">
         <v>46205</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="13" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="13" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="29"/>
+      <c r="B10" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="15"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13" t="s">
+      <c r="A11" s="29"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="15"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="32"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13" t="s">
+      <c r="A13" s="30"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="15"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="25">
+      <c r="A14" s="22">
         <v>46206</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1154,348 +1154,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="17" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="19"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="17" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="19"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="17" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="19"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="20" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="19"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="14"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="17" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="19"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="14"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="23">
+      <c r="A20" s="34">
         <v>46209</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="23"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12" t="s">
+      <c r="A21" s="34"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="34"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="17" t="s">
+      <c r="A24" s="34"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="19"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="17" t="s">
+      <c r="A25" s="34"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="17" t="s">
+      <c r="A26" s="34"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="19"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="17" t="s">
+      <c r="A27" s="34"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="19"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="14"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="23"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="17" t="s">
+      <c r="A28" s="34"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="19"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="23"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="17" t="s">
+      <c r="A29" s="34"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="19"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="14"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="23"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="17" t="s">
+      <c r="A30" s="34"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="19"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="14"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="17" t="s">
+      <c r="A31" s="34"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="19"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="17" t="s">
+      <c r="A32" s="34"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="19"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="14"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="23"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="17" t="s">
+      <c r="A33" s="34"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="19"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="23"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="17" t="s">
+      <c r="A34" s="34"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="19"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="24">
+      <c r="A35" s="21">
         <v>46210</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12" t="s">
+      <c r="A36" s="21"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
-      <c r="B38" s="34" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="12" t="s">
+      <c r="A39" s="21"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="12" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="12" t="s">
+      <c r="A41" s="21"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="12" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="12" t="s">
+      <c r="A43" s="21"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="17" t="s">
+      <c r="A44" s="21"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="19"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="14"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1504,39 +1504,64 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="35">
+      <c r="A46" s="6">
         <v>46212</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
+      <c r="B46" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C46" s="11" t="s">
         <v>56</v>
       </c>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
+  <mergeCells count="59">
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -1553,38 +1578,16 @@
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3C216C-FA41-4D52-8ACA-D7BB5B73384E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EB4748-0E6D-4338-AF87-90EB7F168377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -199,7 +199,22 @@
     <t>Nộp lại cho kế toán phí sửa chữa ID: 00320026F0 (600k)</t>
   </si>
   <si>
-    <t>Nhận BH Victory VNSH03 (đã làm phiếu đổi trả thiết bị mới)</t>
+    <t>Trả BH SEA trả trước 10 thiết bị (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH A. Tuấn BG (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH GPS Global (A. Lực)</t>
+  </si>
+  <si>
+    <t>Nhận BH Victory VNSH03 (đã làm phiếu đổi trả thiết bị mới), nhận từ KT Kho</t>
+  </si>
+  <si>
+    <t>Trả BH Nam Anh (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Anh Hồng PT (A. Lực)</t>
   </si>
 </sst>
 </file>
@@ -372,6 +387,25 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -384,79 +418,60 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,15 +794,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="15">
+      <c r="A1" s="8">
         <v>46174</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -796,146 +811,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="17">
         <v>46202</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="17">
         <v>46203</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="9"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="7" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -945,6 +960,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -955,14 +978,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -970,7 +985,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -980,15 +995,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="25">
+      <c r="A1" s="29">
         <v>46204</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -997,152 +1012,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="17">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="A7" s="32">
         <v>46205</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="7" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="7" t="s">
+      <c r="A9" s="33"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="9"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="7" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="7" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="26">
         <v>46206</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="21" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1154,348 +1169,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="12" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="23"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="12" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="14"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="12" t="s">
+      <c r="A17" s="27"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="31" t="s">
+      <c r="A18" s="27"/>
+      <c r="B18" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="12" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
+      <c r="A20" s="24">
         <v>46209</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11" t="s">
+      <c r="A21" s="24"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11" t="s">
+      <c r="A22" s="24"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="11" t="s">
+      <c r="A23" s="24"/>
+      <c r="B23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12" t="s">
+      <c r="A24" s="24"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12" t="s">
+      <c r="A25" s="24"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="14"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12" t="s">
+      <c r="A26" s="24"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="14"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12" t="s">
+      <c r="A27" s="24"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="14"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12" t="s">
+      <c r="A28" s="24"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="14"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12" t="s">
+      <c r="A29" s="24"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="14"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="12" t="s">
+      <c r="A30" s="24"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="14"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12" t="s">
+      <c r="A31" s="24"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="14"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12" t="s">
+      <c r="A32" s="24"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="14"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12" t="s">
+      <c r="A33" s="24"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="14"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12" t="s">
+      <c r="A34" s="24"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="14"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="21">
+      <c r="A35" s="25">
         <v>46210</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11" t="s">
+      <c r="A36" s="25"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11" t="s">
+      <c r="A37" s="25"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
-      <c r="B38" s="20" t="s">
+      <c r="A38" s="25"/>
+      <c r="B38" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="11" t="s">
+      <c r="A39" s="25"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="11" t="s">
+      <c r="A40" s="25"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="21"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="11" t="s">
+      <c r="A41" s="25"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="21"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="11" t="s">
+      <c r="A42" s="25"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="11" t="s">
+      <c r="A43" s="25"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="21"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="12" t="s">
+      <c r="A44" s="25"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="14"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1504,31 +1519,140 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>46212</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="26">
+        <v>46578</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="20"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="27"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="20"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="27"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="20"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="27"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="20"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="28"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="66">
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="C46:G46"/>
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B18:B19"/>
@@ -1545,49 +1669,6 @@
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EB4748-0E6D-4338-AF87-90EB7F168377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F50861D-2E04-4BE5-9865-A03593E10F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>Trả BH Anh Hồng PT (A. Lực)</t>
+  </si>
+  <si>
+    <t>Nhập kho 38 thiết bị VNSH03</t>
+  </si>
+  <si>
+    <t>Xuất kho 20 module SIM A7677S(GPS), 2 module SIM EC20_CN</t>
   </si>
 </sst>
 </file>
@@ -388,6 +394,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -403,74 +433,50 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -794,15 +800,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8">
+      <c r="A1" s="16">
         <v>46174</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -811,146 +817,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="11">
         <v>46202</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="11">
         <v>46203</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -960,14 +966,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -978,6 +976,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -985,7 +991,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1021,23 +1027,23 @@
       <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="11">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="31" t="s">
@@ -1049,26 +1055,26 @@
       <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
@@ -1077,84 +1083,84 @@
       <c r="B7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="33"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="33"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="14" t="s">
+      <c r="B9" s="23"/>
+      <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="34"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14" t="s">
+      <c r="B13" s="12"/>
+      <c r="C13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="24">
         <v>46206</v>
       </c>
       <c r="B14" s="21" t="s">
@@ -1169,348 +1175,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="27"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="18" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="18" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="25"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="20"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="18" t="s">
+      <c r="A19" s="26"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="24">
+      <c r="A20" s="35">
         <v>46209</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="35"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="35"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="35"/>
+      <c r="B23" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="18" t="s">
+      <c r="A24" s="35"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="18" t="s">
+      <c r="A25" s="35"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="18" t="s">
+      <c r="A26" s="35"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="18" t="s">
+      <c r="A27" s="35"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="18" t="s">
+      <c r="A28" s="35"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="18" t="s">
+      <c r="A29" s="35"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="18" t="s">
+      <c r="A30" s="35"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="18" t="s">
+      <c r="A31" s="35"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="18" t="s">
+      <c r="A32" s="35"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="24"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="18" t="s">
+      <c r="A33" s="35"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="24"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="18" t="s">
+      <c r="A34" s="35"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="20"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="25">
+      <c r="A35" s="28">
         <v>46210</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="25"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13" t="s">
+      <c r="A36" s="28"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13" t="s">
+      <c r="A37" s="28"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="25"/>
-      <c r="B38" s="35" t="s">
+      <c r="A38" s="28"/>
+      <c r="B38" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="25"/>
-      <c r="B39" s="35"/>
-      <c r="C39" s="13" t="s">
+      <c r="A39" s="28"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="25"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="13" t="s">
+      <c r="A40" s="28"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="25"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="13" t="s">
+      <c r="A41" s="28"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="13" t="s">
+      <c r="A42" s="28"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="25"/>
-      <c r="B43" s="35"/>
-      <c r="C43" s="13" t="s">
+      <c r="A43" s="28"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="25"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="18" t="s">
+      <c r="A44" s="28"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="20"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="15"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1519,13 +1525,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1534,94 +1540,131 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="26">
-        <v>46578</v>
+      <c r="A47" s="24">
+        <v>46213</v>
       </c>
       <c r="B47" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="20"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="18" t="s">
+      <c r="A48" s="25"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="20"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="18" t="s">
+      <c r="A49" s="25"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="20"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="18" t="s">
+      <c r="A50" s="25"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="20"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="28"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="18" t="s">
+      <c r="A51" s="26"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="20"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="15"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="11">
+        <v>46214</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="11"/>
+      <c r="B53" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
+  <mergeCells count="69">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -1638,37 +1681,31 @@
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C23:G23"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F50861D-2E04-4BE5-9865-A03593E10F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1972DA8A-3EB4-4DA7-9AC5-B1CA8B155281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -221,6 +221,36 @@
   </si>
   <si>
     <t>Xuất kho 20 module SIM A7677S(GPS), 2 module SIM EC20_CN</t>
+  </si>
+  <si>
+    <t>Trả BH A. Trực 1 thiết bị VNSH03 từ 2025 ID: 00320073CF (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Kim Long (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Ngọc Hoàn (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Minh Khang (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Anh Thái QN (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Việt Bảo Tín (A. Lực)</t>
+  </si>
+  <si>
+    <t>Nhận 3 Tua vít đề xuất mua, 200 hộp carton</t>
+  </si>
+  <si>
+    <t>Nhận BH Sao Việt</t>
+  </si>
+  <si>
+    <t>Nhận BH AT. Việt Nam</t>
+  </si>
+  <si>
+    <t>Nhận BH Maxconnect</t>
   </si>
 </sst>
 </file>
@@ -373,7 +403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -433,6 +463,39 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -442,41 +505,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -991,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1001,15 +1034,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="29">
+      <c r="A1" s="26">
         <v>46204</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1018,13 +1051,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
@@ -1046,13 +1079,13 @@
       <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
@@ -1077,10 +1110,10 @@
       <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="32">
+      <c r="A7" s="29">
         <v>46205</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="32" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="13" t="s">
@@ -1092,8 +1125,8 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="22"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
@@ -1103,8 +1136,8 @@
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="23"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
@@ -1114,7 +1147,7 @@
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
+      <c r="A10" s="30"/>
       <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
@@ -1127,7 +1160,7 @@
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
+      <c r="A11" s="30"/>
       <c r="B11" s="12"/>
       <c r="C11" s="8" t="s">
         <v>20</v>
@@ -1138,7 +1171,7 @@
       <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
+      <c r="A12" s="30"/>
       <c r="B12" s="12"/>
       <c r="C12" s="8" t="s">
         <v>21</v>
@@ -1149,7 +1182,7 @@
       <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="12"/>
       <c r="C13" s="8" t="s">
         <v>23</v>
@@ -1160,10 +1193,10 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="24">
+      <c r="A14" s="23">
         <v>46206</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="32" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1175,8 +1208,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
-      <c r="B15" s="22"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="33"/>
       <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
@@ -1186,8 +1219,8 @@
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="25"/>
-      <c r="B16" s="22"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="13" t="s">
         <v>28</v>
       </c>
@@ -1197,8 +1230,8 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
-      <c r="B17" s="23"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="34"/>
       <c r="C17" s="13" t="s">
         <v>27</v>
       </c>
@@ -1208,8 +1241,8 @@
       <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="21" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="32" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="13" t="s">
@@ -1221,8 +1254,8 @@
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="23"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="13" t="s">
         <v>31</v>
       </c>
@@ -1403,7 +1436,7 @@
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="28">
+      <c r="A35" s="22">
         <v>46210</v>
       </c>
       <c r="B35" s="12" t="s">
@@ -1418,7 +1451,7 @@
       <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12" t="s">
         <v>27</v>
@@ -1429,7 +1462,7 @@
       <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12" t="s">
         <v>47</v>
@@ -1440,8 +1473,8 @@
       <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="28"/>
-      <c r="B38" s="27" t="s">
+      <c r="A38" s="22"/>
+      <c r="B38" s="21" t="s">
         <v>4</v>
       </c>
       <c r="C38" s="12" t="s">
@@ -1453,8 +1486,8 @@
       <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
-      <c r="B39" s="27"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="21"/>
       <c r="C39" s="12" t="s">
         <v>53</v>
       </c>
@@ -1464,8 +1497,8 @@
       <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="28"/>
-      <c r="B40" s="27"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="21"/>
       <c r="C40" s="12" t="s">
         <v>48</v>
       </c>
@@ -1475,8 +1508,8 @@
       <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="27"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="21"/>
       <c r="C41" s="12" t="s">
         <v>49</v>
       </c>
@@ -1486,8 +1519,8 @@
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
-      <c r="B42" s="27"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="21"/>
       <c r="C42" s="12" t="s">
         <v>50</v>
       </c>
@@ -1497,8 +1530,8 @@
       <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="27"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="21"/>
       <c r="C43" s="12" t="s">
         <v>51</v>
       </c>
@@ -1508,8 +1541,8 @@
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
-      <c r="B44" s="27"/>
+      <c r="A44" s="22"/>
+      <c r="B44" s="21"/>
       <c r="C44" s="13" t="s">
         <v>54</v>
       </c>
@@ -1549,10 +1582,10 @@
       <c r="G46" s="12"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="24">
+      <c r="A47" s="23">
         <v>46213</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="32" t="s">
         <v>4</v>
       </c>
       <c r="C47" s="13" t="s">
@@ -1564,8 +1597,8 @@
       <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="25"/>
-      <c r="B48" s="22"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="33"/>
       <c r="C48" s="13" t="s">
         <v>57</v>
       </c>
@@ -1575,8 +1608,8 @@
       <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="25"/>
-      <c r="B49" s="22"/>
+      <c r="A49" s="24"/>
+      <c r="B49" s="33"/>
       <c r="C49" s="13" t="s">
         <v>58</v>
       </c>
@@ -1586,8 +1619,8 @@
       <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="25"/>
-      <c r="B50" s="22"/>
+      <c r="A50" s="24"/>
+      <c r="B50" s="33"/>
       <c r="C50" s="13" t="s">
         <v>60</v>
       </c>
@@ -1597,8 +1630,8 @@
       <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="26"/>
-      <c r="B51" s="23"/>
+      <c r="A51" s="25"/>
+      <c r="B51" s="34"/>
       <c r="C51" s="13" t="s">
         <v>61</v>
       </c>
@@ -1635,13 +1668,148 @@
       <c r="F53" s="12"/>
       <c r="G53" s="12"/>
     </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="11">
+        <v>46216</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="15"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="36"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="36"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="36"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="36"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="36"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" s="36"/>
+      <c r="E61" s="36"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="36"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" s="36"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="36"/>
+      <c r="G62" s="36"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="D63" s="36"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="36"/>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="81">
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
     <mergeCell ref="C52:G52"/>
     <mergeCell ref="C53:G53"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C46:G46"/>
     <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="B14:B17"/>
@@ -1699,13 +1867,6 @@
     <mergeCell ref="C37:G37"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="B38:B44"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1972DA8A-3EB4-4DA7-9AC5-B1CA8B155281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F76E49-02FF-4C79-984E-2F111F835170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="75">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Nhận BH Maxconnect</t>
+  </si>
+  <si>
+    <t>Nhận BH A. Sửu</t>
   </si>
 </sst>
 </file>
@@ -403,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -510,6 +513,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1024,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1784,8 +1790,51 @@
       <c r="F63" s="36"/>
       <c r="G63" s="36"/>
     </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="22">
+        <v>46217</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="22"/>
+      <c r="B65" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="22"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="81">
+  <mergeCells count="86">
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
     <mergeCell ref="A54:A63"/>
     <mergeCell ref="B55:B63"/>
     <mergeCell ref="C55:G55"/>
@@ -1798,8 +1847,6 @@
     <mergeCell ref="C62:G62"/>
     <mergeCell ref="C63:G63"/>
     <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="C46:G46"/>
     <mergeCell ref="C45:G45"/>
@@ -1861,12 +1908,15 @@
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C64:G64"/>
     <mergeCell ref="B35:B37"/>
     <mergeCell ref="C35:G35"/>
     <mergeCell ref="C36:G36"/>
     <mergeCell ref="C37:G37"/>
     <mergeCell ref="C38:G38"/>
     <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F76E49-02FF-4C79-984E-2F111F835170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D85206A-093A-4F4B-84B9-0BE9E6090950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Nhận BH A. Sửu</t>
+  </si>
+  <si>
+    <t>Nhận 1 thiết bị HTA LE nâng cấp 2G=&gt;4G</t>
   </si>
 </sst>
 </file>
@@ -427,6 +430,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -439,9 +460,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -451,26 +469,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -481,6 +496,9 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -499,23 +517,8 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -839,15 +842,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="16">
+      <c r="A1" s="8">
         <v>46174</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -856,146 +859,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>46202</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="17">
         <v>46203</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="8" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1005,6 +1008,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1015,14 +1026,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1030,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1040,15 +1043,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="26">
+      <c r="A1" s="31">
         <v>46204</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1057,152 +1060,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="29">
+      <c r="A7" s="34">
         <v>46205</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="8" t="s">
+      <c r="A8" s="35"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="8" t="s">
+      <c r="A9" s="35"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="35"/>
+      <c r="B10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="35"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8" t="s">
+      <c r="A13" s="36"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+      <c r="A14" s="27">
         <v>46206</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="24" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1214,348 +1217,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="13" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="13" t="s">
+      <c r="A16" s="28"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="32" t="s">
+      <c r="A18" s="28"/>
+      <c r="B18" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="13" t="s">
+      <c r="A19" s="29"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="35">
+      <c r="A20" s="30">
         <v>46209</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12" t="s">
+      <c r="A21" s="30"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="30"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="30"/>
+      <c r="B23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="35"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
+      <c r="A24" s="30"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13" t="s">
+      <c r="A25" s="30"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13" t="s">
+      <c r="A26" s="30"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13" t="s">
+      <c r="A27" s="30"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13" t="s">
+      <c r="A28" s="30"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="35"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13" t="s">
+      <c r="A29" s="30"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="15"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13" t="s">
+      <c r="A30" s="30"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="15"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13" t="s">
+      <c r="A31" s="30"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="15"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="35"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13" t="s">
+      <c r="A32" s="30"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="35"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13" t="s">
+      <c r="A33" s="30"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="15"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13" t="s">
+      <c r="A34" s="30"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="15"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="22">
+      <c r="A35" s="21">
         <v>46210</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="22"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12" t="s">
+      <c r="A36" s="21"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="22"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="22"/>
-      <c r="B38" s="21" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="22"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="12" t="s">
+      <c r="A39" s="21"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="22"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="12" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="22"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="12" t="s">
+      <c r="A41" s="21"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="22"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="12" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="22"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="12" t="s">
+      <c r="A43" s="21"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="22"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="13" t="s">
+      <c r="A44" s="21"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="15"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1564,13 +1567,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1579,258 +1582,344 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="23">
+      <c r="A47" s="27">
         <v>46213</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="15"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="B48" s="33"/>
-      <c r="C48" s="13" t="s">
+      <c r="A48" s="28"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="15"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="24"/>
-      <c r="B49" s="33"/>
-      <c r="C49" s="13" t="s">
+      <c r="A49" s="28"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="15"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="20"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="24"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="13" t="s">
+      <c r="A50" s="28"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="15"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="20"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="25"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="13" t="s">
+      <c r="A51" s="29"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="15"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="11">
+      <c r="A52" s="17">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
+      <c r="A54" s="17">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="15"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12" t="s">
+      <c r="A55" s="17"/>
+      <c r="B55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="36" t="s">
+      <c r="C55" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="36" t="s">
+      <c r="A56" s="17"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="36" t="s">
+      <c r="A57" s="17"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-      <c r="G57" s="36"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="36" t="s">
+      <c r="A58" s="17"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="36"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="36" t="s">
+      <c r="A59" s="17"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="36" t="s">
+      <c r="A60" s="17"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
-      <c r="G60" s="36"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="36" t="s">
+      <c r="A61" s="17"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="36"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="36" t="s">
+      <c r="A62" s="17"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="36"/>
-      <c r="E62" s="36"/>
-      <c r="F62" s="36"/>
-      <c r="G62" s="36"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="36" t="s">
+      <c r="A63" s="17"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="36"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="36"/>
-      <c r="G63" s="36"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="23"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="22">
+      <c r="A64" s="17">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="22"/>
-      <c r="B65" s="37" t="s">
+      <c r="A65" s="17"/>
+      <c r="B65" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="22"/>
-      <c r="B66" s="37"/>
-      <c r="C66" s="12" t="s">
+      <c r="A66" s="17"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B67" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="86">
+  <mergeCells count="87">
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
     <mergeCell ref="A64:A66"/>
     <mergeCell ref="C65:G65"/>
     <mergeCell ref="C66:G66"/>
@@ -1847,76 +1936,6 @@
     <mergeCell ref="C62:G62"/>
     <mergeCell ref="C63:G63"/>
     <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D85206A-093A-4F4B-84B9-0BE9E6090950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A12667C-3D6D-4851-943D-27C690A657B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="78">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>Nhận 1 thiết bị HTA LE nâng cấp 2G=&gt;4G</t>
+  </si>
+  <si>
+    <t>Trả BH Lắp Đặt 1 VNSH03, 1 C43</t>
+  </si>
+  <si>
+    <t>Trả BH AT. Việt Nam (Quỳnh)</t>
   </si>
 </sst>
 </file>
@@ -430,6 +436,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -446,76 +476,52 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -842,15 +848,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8">
+      <c r="A1" s="16">
         <v>46174</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -859,146 +865,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="11">
         <v>46202</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="11">
         <v>46203</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1008,14 +1014,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1026,6 +1024,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1033,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1043,15 +1049,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="31">
+      <c r="A1" s="26">
         <v>46204</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1060,152 +1066,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="11">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="34">
+      <c r="A7" s="29">
         <v>46205</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="35"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="35"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="30"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="30"/>
+      <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="30"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="31"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="27">
+      <c r="A14" s="23">
         <v>46206</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="32" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1217,348 +1223,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="18" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="18" t="s">
+      <c r="A16" s="24"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="24"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="20"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="29"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="18" t="s">
+      <c r="A19" s="25"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+      <c r="A20" s="35">
         <v>46209</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="35"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="35"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="35"/>
+      <c r="B23" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="18" t="s">
+      <c r="A24" s="35"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="18" t="s">
+      <c r="A25" s="35"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="18" t="s">
+      <c r="A26" s="35"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="18" t="s">
+      <c r="A27" s="35"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="18" t="s">
+      <c r="A28" s="35"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="18" t="s">
+      <c r="A29" s="35"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="18" t="s">
+      <c r="A30" s="35"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="18" t="s">
+      <c r="A31" s="35"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="30"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="18" t="s">
+      <c r="A32" s="35"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="18" t="s">
+      <c r="A33" s="35"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="30"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="18" t="s">
+      <c r="A34" s="35"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="20"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="21">
+      <c r="A35" s="22">
         <v>46210</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13" t="s">
+      <c r="A36" s="22"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13" t="s">
+      <c r="A37" s="22"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
-      <c r="B38" s="22" t="s">
+      <c r="A38" s="22"/>
+      <c r="B38" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="13" t="s">
+      <c r="A39" s="22"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="13" t="s">
+      <c r="A40" s="22"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="21"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="13" t="s">
+      <c r="A41" s="22"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="21"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="13" t="s">
+      <c r="A42" s="22"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="13" t="s">
+      <c r="A43" s="22"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="21"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="18" t="s">
+      <c r="A44" s="22"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="20"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="15"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1567,13 +1573,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1582,295 +1588,352 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="27">
+      <c r="A47" s="23">
         <v>46213</v>
       </c>
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="20"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="28"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="18" t="s">
+      <c r="A48" s="24"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="20"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="18" t="s">
+      <c r="A49" s="24"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="20"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="28"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="18" t="s">
+      <c r="A50" s="24"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="20"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="29"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="18" t="s">
+      <c r="A51" s="25"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="20"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="15"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
+      <c r="A52" s="11">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
+      <c r="A53" s="11"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="17">
+      <c r="A54" s="11">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="20"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="15"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="13" t="s">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="23" t="s">
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="23" t="s">
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
+      <c r="D57" s="36"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="36"/>
+      <c r="G57" s="36"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="17"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="23" t="s">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="36"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="17"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="23" t="s">
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="17"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="23" t="s">
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="36"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="17"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="23" t="s">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
+      <c r="D61" s="36"/>
+      <c r="E61" s="36"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="36"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="17"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="23" t="s">
+      <c r="A62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
+      <c r="D62" s="36"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="36"/>
+      <c r="G62" s="36"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="23" t="s">
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="36"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="17">
+      <c r="A64" s="11">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
-      <c r="B65" s="13" t="s">
+      <c r="A65" s="11"/>
+      <c r="B65" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13" t="s">
+      <c r="A66" s="11"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>46219</v>
       </c>
-      <c r="B67" s="37" t="s">
+      <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="11">
+        <v>46220</v>
+      </c>
+      <c r="B68" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="11"/>
+      <c r="B69" s="37"/>
+      <c r="C69" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="87">
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
+  <mergeCells count="91">
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -1887,55 +1950,28 @@
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A12667C-3D6D-4851-943D-27C690A657B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4EF237-F9DB-4217-82BB-7C1C93A833D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -263,6 +263,33 @@
   </si>
   <si>
     <t>Trả BH AT. Việt Nam (Quỳnh)</t>
+  </si>
+  <si>
+    <t>Nhận BH Phúc Hưng</t>
+  </si>
+  <si>
+    <t>Nhận BH Nam Anh</t>
+  </si>
+  <si>
+    <t>Nhận BH Hải Yến</t>
+  </si>
+  <si>
+    <t>Nhận BH Thành Tâm Nha Trang</t>
+  </si>
+  <si>
+    <t>Nhận BH Gia Thành</t>
+  </si>
+  <si>
+    <t>Trả BH A. Tuấn NB (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Sao Việt (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Maxconnet (A. Lực)</t>
+  </si>
+  <si>
+    <t>Trả BH Victory (A. Lực)</t>
   </si>
 </sst>
 </file>
@@ -415,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -475,9 +502,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -522,9 +546,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1049,15 +1070,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="26">
+      <c r="A1" s="25">
         <v>46204</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1066,13 +1087,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
@@ -1094,13 +1115,13 @@
       <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
@@ -1125,10 +1146,10 @@
       <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="29">
+      <c r="A7" s="28">
         <v>46205</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="13" t="s">
@@ -1140,8 +1161,8 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="33"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1172,8 @@
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="34"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
@@ -1162,7 +1183,7 @@
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
@@ -1175,7 +1196,7 @@
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="12"/>
       <c r="C11" s="8" t="s">
         <v>20</v>
@@ -1186,7 +1207,7 @@
       <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="12"/>
       <c r="C12" s="8" t="s">
         <v>21</v>
@@ -1197,7 +1218,7 @@
       <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="12"/>
       <c r="C13" s="8" t="s">
         <v>23</v>
@@ -1208,10 +1229,10 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+      <c r="A14" s="22">
         <v>46206</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1223,8 +1244,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="33"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="32"/>
       <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
@@ -1234,8 +1255,8 @@
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="24"/>
-      <c r="B16" s="33"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="32"/>
       <c r="C16" s="13" t="s">
         <v>28</v>
       </c>
@@ -1245,8 +1266,8 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
-      <c r="B17" s="34"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="13" t="s">
         <v>27</v>
       </c>
@@ -1256,8 +1277,8 @@
       <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="32" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="31" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="13" t="s">
@@ -1269,8 +1290,8 @@
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="34"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="13" t="s">
         <v>31</v>
       </c>
@@ -1280,7 +1301,7 @@
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="35">
+      <c r="A20" s="34">
         <v>46209</v>
       </c>
       <c r="B20" s="12" t="s">
@@ -1295,7 +1316,7 @@
       <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
+      <c r="A21" s="34"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12" t="s">
         <v>34</v>
@@ -1306,7 +1327,7 @@
       <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12" t="s">
         <v>15</v>
@@ -1317,7 +1338,7 @@
       <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
+      <c r="A23" s="34"/>
       <c r="B23" s="12" t="s">
         <v>4</v>
       </c>
@@ -1330,7 +1351,7 @@
       <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="35"/>
+      <c r="A24" s="34"/>
       <c r="B24" s="12"/>
       <c r="C24" s="13" t="s">
         <v>35</v>
@@ -1341,7 +1362,7 @@
       <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="12"/>
       <c r="C25" s="13" t="s">
         <v>36</v>
@@ -1352,7 +1373,7 @@
       <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="12"/>
       <c r="C26" s="13" t="s">
         <v>37</v>
@@ -1363,7 +1384,7 @@
       <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
+      <c r="A27" s="34"/>
       <c r="B27" s="12"/>
       <c r="C27" s="13" t="s">
         <v>38</v>
@@ -1374,7 +1395,7 @@
       <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="12"/>
       <c r="C28" s="13" t="s">
         <v>39</v>
@@ -1385,7 +1406,7 @@
       <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="35"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="12"/>
       <c r="C29" s="13" t="s">
         <v>40</v>
@@ -1396,7 +1417,7 @@
       <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="12"/>
       <c r="C30" s="13" t="s">
         <v>45</v>
@@ -1407,7 +1428,7 @@
       <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
+      <c r="A31" s="34"/>
       <c r="B31" s="12"/>
       <c r="C31" s="13" t="s">
         <v>41</v>
@@ -1418,7 +1439,7 @@
       <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="35"/>
+      <c r="A32" s="34"/>
       <c r="B32" s="12"/>
       <c r="C32" s="13" t="s">
         <v>42</v>
@@ -1429,7 +1450,7 @@
       <c r="G32" s="15"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="35"/>
+      <c r="A33" s="34"/>
       <c r="B33" s="12"/>
       <c r="C33" s="13" t="s">
         <v>43</v>
@@ -1440,7 +1461,7 @@
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
+      <c r="A34" s="34"/>
       <c r="B34" s="12"/>
       <c r="C34" s="13" t="s">
         <v>44</v>
@@ -1451,7 +1472,7 @@
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="22">
+      <c r="A35" s="21">
         <v>46210</v>
       </c>
       <c r="B35" s="12" t="s">
@@ -1466,7 +1487,7 @@
       <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="22"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12" t="s">
         <v>27</v>
@@ -1477,7 +1498,7 @@
       <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="22"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12" t="s">
         <v>47</v>
@@ -1488,8 +1509,8 @@
       <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="22"/>
-      <c r="B38" s="21" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C38" s="12" t="s">
@@ -1501,8 +1522,8 @@
       <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="22"/>
-      <c r="B39" s="21"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="12"/>
       <c r="C39" s="12" t="s">
         <v>53</v>
       </c>
@@ -1512,8 +1533,8 @@
       <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="22"/>
-      <c r="B40" s="21"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="12"/>
       <c r="C40" s="12" t="s">
         <v>48</v>
       </c>
@@ -1523,8 +1544,8 @@
       <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="22"/>
-      <c r="B41" s="21"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="12"/>
       <c r="C41" s="12" t="s">
         <v>49</v>
       </c>
@@ -1534,8 +1555,8 @@
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="22"/>
-      <c r="B42" s="21"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="12"/>
       <c r="C42" s="12" t="s">
         <v>50</v>
       </c>
@@ -1545,8 +1566,8 @@
       <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="22"/>
-      <c r="B43" s="21"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="12"/>
       <c r="C43" s="12" t="s">
         <v>51</v>
       </c>
@@ -1556,8 +1577,8 @@
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="22"/>
-      <c r="B44" s="21"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="12"/>
       <c r="C44" s="13" t="s">
         <v>54</v>
       </c>
@@ -1597,10 +1618,10 @@
       <c r="G46" s="12"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="23">
+      <c r="A47" s="22">
         <v>46213</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="31" t="s">
         <v>4</v>
       </c>
       <c r="C47" s="13" t="s">
@@ -1612,8 +1633,8 @@
       <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="B48" s="33"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="32"/>
       <c r="C48" s="13" t="s">
         <v>57</v>
       </c>
@@ -1623,8 +1644,8 @@
       <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="24"/>
-      <c r="B49" s="33"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="32"/>
       <c r="C49" s="13" t="s">
         <v>58</v>
       </c>
@@ -1634,8 +1655,8 @@
       <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="24"/>
-      <c r="B50" s="33"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="32"/>
       <c r="C50" s="13" t="s">
         <v>60</v>
       </c>
@@ -1645,8 +1666,8 @@
       <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="25"/>
-      <c r="B51" s="34"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="33"/>
       <c r="C51" s="13" t="s">
         <v>61</v>
       </c>
@@ -1703,101 +1724,101 @@
       <c r="B55" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="36" t="s">
+      <c r="C55" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
       <c r="B56" s="12"/>
-      <c r="C56" s="36" t="s">
+      <c r="C56" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
       <c r="B57" s="12"/>
-      <c r="C57" s="36" t="s">
+      <c r="C57" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-      <c r="G57" s="36"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
       <c r="B58" s="12"/>
-      <c r="C58" s="36" t="s">
+      <c r="C58" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="36"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="12"/>
-      <c r="C59" s="36" t="s">
+      <c r="C59" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
       <c r="B60" s="12"/>
-      <c r="C60" s="36" t="s">
+      <c r="C60" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
-      <c r="G60" s="36"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
       <c r="B61" s="12"/>
-      <c r="C61" s="36" t="s">
+      <c r="C61" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="36"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="12"/>
-      <c r="C62" s="36" t="s">
+      <c r="C62" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="36"/>
-      <c r="E62" s="36"/>
-      <c r="F62" s="36"/>
-      <c r="G62" s="36"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="12"/>
-      <c r="C63" s="36" t="s">
+      <c r="C63" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="36"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="36"/>
-      <c r="G63" s="36"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
@@ -1857,7 +1878,7 @@
       <c r="A68" s="11">
         <v>46220</v>
       </c>
-      <c r="B68" s="37" t="s">
+      <c r="B68" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C68" s="12" t="s">
@@ -1870,7 +1891,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="11"/>
-      <c r="B69" s="37"/>
+      <c r="B69" s="12"/>
       <c r="C69" s="12" t="s">
         <v>77</v>
       </c>
@@ -1879,8 +1900,133 @@
       <c r="F69" s="12"/>
       <c r="G69" s="12"/>
     </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="11">
+        <v>46223</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="15"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="15"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="15"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="15"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="11"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="15"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="15"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="15"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="11"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="10"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="10"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="10"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="104">
     <mergeCell ref="C68:G68"/>
     <mergeCell ref="C69:G69"/>
     <mergeCell ref="A68:A69"/>
@@ -1889,6 +2035,8 @@
     <mergeCell ref="C65:G65"/>
     <mergeCell ref="C66:G66"/>
     <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
     <mergeCell ref="A54:A63"/>
     <mergeCell ref="B55:B63"/>
     <mergeCell ref="C55:G55"/>
@@ -1911,11 +2059,8 @@
     <mergeCell ref="C49:G49"/>
     <mergeCell ref="C50:G50"/>
     <mergeCell ref="C51:G51"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
     <mergeCell ref="C30:G30"/>
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C32:G32"/>
@@ -1925,15 +2070,6 @@
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C20:G20"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -1950,6 +2086,20 @@
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
@@ -1962,16 +2112,25 @@
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4EF237-F9DB-4217-82BB-7C1C93A833D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908F2C7E-9A39-4096-A057-4E5237698200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="88">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Trả BH Victory (A. Lực)</t>
+  </si>
+  <si>
+    <t>Gửi BH 1 VNSH03 cho Thịnh Aithins (ID: VNET861385071516382)</t>
   </si>
 </sst>
 </file>
@@ -463,6 +466,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -475,9 +496,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -487,33 +505,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -532,20 +547,8 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,15 +872,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="16">
+      <c r="A1" s="8">
         <v>46174</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -886,146 +889,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>46202</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="17">
         <v>46203</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="8" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1035,6 +1038,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1045,14 +1056,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1060,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1070,15 +1073,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="25">
+      <c r="A1" s="29">
         <v>46204</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1087,152 +1090,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="A7" s="32">
         <v>46205</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="8" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="8" t="s">
+      <c r="A9" s="33"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="33"/>
+      <c r="B10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="33"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8" t="s">
+      <c r="A13" s="34"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="25">
         <v>46206</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1244,348 +1247,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="13" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="23"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="13" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="26"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="31" t="s">
+      <c r="A18" s="26"/>
+      <c r="B18" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="13" t="s">
+      <c r="A19" s="27"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
+      <c r="A20" s="35">
         <v>46209</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12" t="s">
+      <c r="A21" s="35"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="35"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="35"/>
+      <c r="B23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
+      <c r="A24" s="35"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13" t="s">
+      <c r="A25" s="35"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13" t="s">
+      <c r="A26" s="35"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13" t="s">
+      <c r="A27" s="35"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13" t="s">
+      <c r="A28" s="35"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13" t="s">
+      <c r="A29" s="35"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="15"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13" t="s">
+      <c r="A30" s="35"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="15"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13" t="s">
+      <c r="A31" s="35"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="15"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13" t="s">
+      <c r="A32" s="35"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13" t="s">
+      <c r="A33" s="35"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="15"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13" t="s">
+      <c r="A34" s="35"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="15"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="21">
+      <c r="A35" s="28">
         <v>46210</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12" t="s">
+      <c r="A36" s="28"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12" t="s">
+      <c r="A37" s="28"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
-      <c r="B38" s="12" t="s">
+      <c r="A38" s="28"/>
+      <c r="B38" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12" t="s">
+      <c r="A39" s="28"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12" t="s">
+      <c r="A40" s="28"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="21"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12" t="s">
+      <c r="A41" s="28"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="21"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12" t="s">
+      <c r="A42" s="28"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12" t="s">
+      <c r="A43" s="28"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="21"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="13" t="s">
+      <c r="A44" s="28"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="15"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1594,13 +1597,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1609,255 +1612,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="22">
+      <c r="A47" s="25">
         <v>46213</v>
       </c>
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="15"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="23"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="13" t="s">
+      <c r="A48" s="26"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="15"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="23"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="13" t="s">
+      <c r="A49" s="26"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="15"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="20"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="23"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="13" t="s">
+      <c r="A50" s="26"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="15"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="20"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="24"/>
-      <c r="B51" s="33"/>
-      <c r="C51" s="13" t="s">
+      <c r="A51" s="27"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="15"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="11">
+      <c r="A52" s="17">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
+      <c r="A54" s="17">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="15"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12" t="s">
+      <c r="A55" s="17"/>
+      <c r="B55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="35" t="s">
+      <c r="C55" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="35" t="s">
+      <c r="A56" s="17"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="35" t="s">
+      <c r="A57" s="17"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="35" t="s">
+      <c r="A58" s="17"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="35" t="s">
+      <c r="A59" s="17"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="35" t="s">
+      <c r="A60" s="17"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="35" t="s">
+      <c r="A61" s="17"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="35" t="s">
+      <c r="A62" s="17"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="35"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="35" t="s">
+      <c r="A63" s="17"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
+      <c r="A64" s="17">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12" t="s">
+      <c r="A65" s="17"/>
+      <c r="B65" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12" t="s">
+      <c r="A66" s="17"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1866,210 +1869,220 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
+      <c r="A68" s="17">
         <v>46220</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12" t="s">
+      <c r="A69" s="17"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="11">
+      <c r="A70" s="17">
         <v>46223</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="15"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="20"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="13" t="s">
+      <c r="A71" s="17"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="15"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="20"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13" t="s">
+      <c r="A72" s="17"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="15"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="13" t="s">
+      <c r="A73" s="17"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="15"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="20"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="13" t="s">
+      <c r="A74" s="17"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="15"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="20"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="13" t="s">
+      <c r="A75" s="17"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="15"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="20"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="13" t="s">
+      <c r="A76" s="17"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="15"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="20"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="8" t="s">
+      <c r="A77" s="17"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="10"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="16"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="8" t="s">
+      <c r="A78" s="17"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="10"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="16"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="8" t="s">
+      <c r="A79" s="17"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="10"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="16"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="8" t="s">
+      <c r="A80" s="17"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="10"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="16"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="104">
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
+  <mergeCells count="105">
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2094,43 +2107,49 @@
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="C28:G28"/>
     <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908F2C7E-9A39-4096-A057-4E5237698200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165E394D-BC23-4D41-92D6-CCD43039E0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="94">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -292,7 +292,25 @@
     <t>Trả BH Victory (A. Lực)</t>
   </si>
   <si>
-    <t>Gửi BH 1 VNSH03 cho Thịnh Aithins (ID: VNET861385071516382)</t>
+    <t>Gửi BH 1 VNSH03 cho Thịnh Aithings (ID: VNET861385071516382)</t>
+  </si>
+  <si>
+    <t>Nhận BH Qmaps</t>
+  </si>
+  <si>
+    <t>Nhận BH Nam Định</t>
+  </si>
+  <si>
+    <t>Đổ keo connector LE</t>
+  </si>
+  <si>
+    <t>Nhận 10 thiết bị VNSH03 từ Aithings (nhận lại 1 thiết bị gửi BH)</t>
+  </si>
+  <si>
+    <t>Trả BH AT. Việt Nam (A.Bảo)</t>
+  </si>
+  <si>
+    <t>Trả kho 127 CAM 2 mắt (48 CAM đã sửa, 79 lỗi), còn giữ 1 CAM 2 mắt</t>
   </si>
 </sst>
 </file>
@@ -445,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -466,6 +484,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -481,75 +523,52 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -872,15 +891,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8">
+      <c r="A1" s="16">
         <v>46174</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -889,146 +908,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="11">
         <v>46202</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="11">
         <v>46203</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1038,14 +1057,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1056,6 +1067,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1063,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1073,15 +1092,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="29">
+      <c r="A1" s="28">
         <v>46204</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1090,152 +1109,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="11">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="32">
+      <c r="A7" s="31">
         <v>46205</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="32"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="32"/>
+      <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="32"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="32"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="33"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="25">
         <v>46206</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1249,346 +1268,346 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="26"/>
       <c r="B15" s="23"/>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="26"/>
       <c r="B16" s="23"/>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="26"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="18" t="s">
+      <c r="B17" s="22"/>
+      <c r="C17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="20"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="26"/>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="27"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="18" t="s">
+      <c r="B19" s="22"/>
+      <c r="C19" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="35">
+      <c r="A20" s="34">
         <v>46209</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="34"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="34"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="35"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="18" t="s">
+      <c r="A24" s="34"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="35"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="18" t="s">
+      <c r="A25" s="34"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="18" t="s">
+      <c r="A26" s="34"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="18" t="s">
+      <c r="A27" s="34"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="35"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="18" t="s">
+      <c r="A28" s="34"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="35"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="18" t="s">
+      <c r="A29" s="34"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="18" t="s">
+      <c r="A30" s="34"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="35"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="18" t="s">
+      <c r="A31" s="34"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="35"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="18" t="s">
+      <c r="A32" s="34"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="35"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="18" t="s">
+      <c r="A33" s="34"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="18" t="s">
+      <c r="A34" s="34"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="20"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="28">
+      <c r="A35" s="24">
         <v>46210</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13" t="s">
+      <c r="A36" s="24"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13" t="s">
+      <c r="A37" s="24"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="28"/>
-      <c r="B38" s="13" t="s">
+      <c r="A38" s="24"/>
+      <c r="B38" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13" t="s">
+      <c r="A39" s="24"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="28"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13" t="s">
+      <c r="A40" s="24"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13" t="s">
+      <c r="A41" s="24"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13" t="s">
+      <c r="A42" s="24"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13" t="s">
+      <c r="A43" s="24"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="18" t="s">
+      <c r="A44" s="24"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="20"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="15"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1597,13 +1616,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1612,255 +1631,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="25">
         <v>46213</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="20"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="26"/>
       <c r="B48" s="23"/>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="20"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="26"/>
       <c r="B49" s="23"/>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="20"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="26"/>
       <c r="B50" s="23"/>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="20"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="27"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="18" t="s">
+      <c r="B51" s="22"/>
+      <c r="C51" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="20"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="15"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
+      <c r="A52" s="11">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
+      <c r="A53" s="11"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="17">
+      <c r="A54" s="11">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="20"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="15"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="13" t="s">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="21" t="s">
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="21" t="s">
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="17"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="21" t="s">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="17"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="21" t="s">
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="17"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="21" t="s">
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="17"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="21" t="s">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
-      <c r="G61" s="21"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="17"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="21" t="s">
+      <c r="A62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="21" t="s">
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="17">
+      <c r="A64" s="11">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
-      <c r="B65" s="13" t="s">
+      <c r="A65" s="11"/>
+      <c r="B65" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13" t="s">
+      <c r="A66" s="11"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1869,164 +1888,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="17">
+      <c r="A68" s="11">
         <v>46220</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="17"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13" t="s">
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="17">
+      <c r="A70" s="11">
         <v>46223</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="20"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="15"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="17"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="18" t="s">
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="20"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="15"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="17"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="18" t="s">
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="20"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="15"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="17"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="18" t="s">
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="20"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="15"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="17"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="18" t="s">
+      <c r="A74" s="11"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="20"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="15"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="17"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="18" t="s">
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="20"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="15"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="17"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="18" t="s">
+      <c r="A76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="20"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="15"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="17"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="14" t="s">
+      <c r="A77" s="11"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="16"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="10"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="14" t="s">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="16"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="10"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="17"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="14" t="s">
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="16"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="17"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="14" t="s">
+      <c r="A80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="16"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="10"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2035,16 +2054,151 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="11">
+        <v>46225</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="11"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="11"/>
+      <c r="B85" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="11"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D86" s="12"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="11"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="11"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="15"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="11"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="36">
+        <v>46226</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="117">
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
     <mergeCell ref="C81:G81"/>
     <mergeCell ref="B70:B80"/>
     <mergeCell ref="A70:A80"/>
@@ -2056,28 +2210,40 @@
     <mergeCell ref="C75:G75"/>
     <mergeCell ref="C76:G76"/>
     <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="B14:B17"/>
@@ -2102,54 +2268,32 @@
     <mergeCell ref="A20:A34"/>
     <mergeCell ref="B23:B34"/>
     <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="C28:G28"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165E394D-BC23-4D41-92D6-CCD43039E0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBA687A-0A70-4FC4-8077-21ECE3DA1CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="94">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -484,6 +484,25 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -496,9 +515,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -508,42 +524,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -565,10 +569,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -891,15 +891,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="16">
+      <c r="A1" s="9">
         <v>46174</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -908,146 +908,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="18">
         <v>46202</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="18">
         <v>46203</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="8" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1057,6 +1057,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1067,14 +1075,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1092,15 +1092,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="28">
+      <c r="A1" s="30">
         <v>46204</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1109,152 +1109,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="18">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="31">
+      <c r="A7" s="33">
         <v>46205</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="8" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="32"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="8" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="34"/>
+      <c r="B10" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="34"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="32"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8" t="s">
+      <c r="A13" s="35"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="25">
+      <c r="A14" s="26">
         <v>46206</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="23" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1266,348 +1266,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="13" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="13" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="27"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="21" t="s">
+      <c r="A18" s="27"/>
+      <c r="B18" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="13" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
+      <c r="A20" s="36">
         <v>46209</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12" t="s">
+      <c r="A21" s="36"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="36"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="36"/>
+      <c r="B23" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
+      <c r="A24" s="36"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13" t="s">
+      <c r="A25" s="36"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13" t="s">
+      <c r="A26" s="36"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="21"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13" t="s">
+      <c r="A27" s="36"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13" t="s">
+      <c r="A28" s="36"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13" t="s">
+      <c r="A29" s="36"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="15"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13" t="s">
+      <c r="A30" s="36"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="15"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13" t="s">
+      <c r="A31" s="36"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="15"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="21"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13" t="s">
+      <c r="A32" s="36"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13" t="s">
+      <c r="A33" s="36"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="15"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="21"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13" t="s">
+      <c r="A34" s="36"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="15"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="24">
+      <c r="A35" s="29">
         <v>46210</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12" t="s">
+      <c r="A36" s="29"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12" t="s">
+      <c r="A37" s="29"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
-      <c r="B38" s="12" t="s">
+      <c r="A38" s="29"/>
+      <c r="B38" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12" t="s">
+      <c r="A39" s="29"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12" t="s">
+      <c r="A40" s="29"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12" t="s">
+      <c r="A41" s="29"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12" t="s">
+      <c r="A42" s="29"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12" t="s">
+      <c r="A43" s="29"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="13" t="s">
+      <c r="A44" s="29"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="15"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="21"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1616,13 +1616,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1631,255 +1631,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="25">
+      <c r="A47" s="26">
         <v>46213</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="15"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="21"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="26"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="13" t="s">
+      <c r="A48" s="27"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="15"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="21"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="26"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="13" t="s">
+      <c r="A49" s="27"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="15"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="21"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="26"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="13" t="s">
+      <c r="A50" s="27"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="15"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="21"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="13" t="s">
+      <c r="A51" s="28"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="15"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="11">
+      <c r="A52" s="18">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
+      <c r="A53" s="18"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
+      <c r="A54" s="18">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="15"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="21"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12" t="s">
+      <c r="A55" s="18"/>
+      <c r="B55" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="35" t="s">
+      <c r="C55" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="35" t="s">
+      <c r="A56" s="18"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="35" t="s">
+      <c r="A57" s="18"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="35" t="s">
+      <c r="A58" s="18"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="35" t="s">
+      <c r="A59" s="18"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="35" t="s">
+      <c r="A60" s="18"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="35" t="s">
+      <c r="A61" s="18"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="35" t="s">
+      <c r="A62" s="18"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="35"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="35" t="s">
+      <c r="A63" s="18"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
+      <c r="A64" s="18">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12" t="s">
+      <c r="A65" s="18"/>
+      <c r="B65" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12" t="s">
+      <c r="A66" s="18"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1888,164 +1888,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
+      <c r="A68" s="18">
         <v>46220</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12" t="s">
+      <c r="A69" s="18"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="11">
+      <c r="A70" s="18">
         <v>46223</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="15"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="21"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="13" t="s">
+      <c r="A71" s="18"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="15"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="21"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13" t="s">
+      <c r="A72" s="18"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="15"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="21"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="13" t="s">
+      <c r="A73" s="18"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="15"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="21"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="13" t="s">
+      <c r="A74" s="18"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="15"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="21"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="13" t="s">
+      <c r="A75" s="18"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="15"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="21"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="13" t="s">
+      <c r="A76" s="18"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="15"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="21"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="8" t="s">
+      <c r="A77" s="18"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="10"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="8" t="s">
+      <c r="A78" s="18"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="10"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="8" t="s">
+      <c r="A79" s="18"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="10"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="8" t="s">
+      <c r="A80" s="18"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="10"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2054,199 +2054,144 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="11">
+      <c r="A82" s="18">
         <v>46225</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="11"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12" t="s">
+      <c r="A83" s="18"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="11"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12" t="s">
+      <c r="A84" s="18"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="11"/>
-      <c r="B85" s="12" t="s">
+      <c r="A85" s="18"/>
+      <c r="B85" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="11"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="12" t="s">
+      <c r="A86" s="18"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="11"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12" t="s">
+      <c r="A87" s="18"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="11"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12" t="s">
+      <c r="A88" s="18"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="11"/>
-      <c r="B89" s="12"/>
-      <c r="C89" s="13" t="s">
+      <c r="A89" s="18"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="15"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="21"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="11"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="12" t="s">
+      <c r="A90" s="18"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="12"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="36">
-        <v>46226</v>
-      </c>
-      <c r="B91" t="s">
-        <v>4</v>
-      </c>
+      <c r="A91" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="117">
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
     <mergeCell ref="C34:G34"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="A35:A44"/>
@@ -2271,29 +2216,79 @@
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
     <mergeCell ref="C78:G78"/>
     <mergeCell ref="C79:G79"/>
     <mergeCell ref="C80:G80"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBA687A-0A70-4FC4-8077-21ECE3DA1CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4659657B-0516-46D6-8AE5-33F9B63225A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="96">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>Trả kho 127 CAM 2 mắt (48 CAM đã sửa, 79 lỗi), còn giữ 1 CAM 2 mắt</t>
+  </si>
+  <si>
+    <t>Xuất kho 200 vỏ hộp RFID( ver old)</t>
+  </si>
+  <si>
+    <t>Nhận 200 PCB RFID + DB09 từ Minh Khôi</t>
   </si>
 </sst>
 </file>
@@ -463,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -484,7 +490,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -500,74 +529,50 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -891,15 +896,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="9">
+      <c r="A1" s="16">
         <v>46174</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -908,146 +913,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="11">
         <v>46202</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="11">
         <v>46203</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="21"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1057,14 +1062,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1075,6 +1072,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1082,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1092,15 +1097,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="30">
+      <c r="A1" s="25">
         <v>46204</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1109,152 +1114,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="11">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="33">
+      <c r="A7" s="28">
         <v>46205</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="21"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="15" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="15" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="14" t="s">
+      <c r="A10" s="29"/>
+      <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15" t="s">
+      <c r="A11" s="29"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15" t="s">
+      <c r="A13" s="30"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="22">
         <v>46206</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1266,348 +1271,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="27"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="19" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="21"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="19" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="21"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="23" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="21"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="19" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="21"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="36">
+      <c r="A20" s="34">
         <v>46209</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="34"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14" t="s">
+      <c r="A22" s="34"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="14" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="19" t="s">
+      <c r="A24" s="34"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="21"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="19" t="s">
+      <c r="A25" s="34"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="21"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="19" t="s">
+      <c r="A26" s="34"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="21"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="19" t="s">
+      <c r="A27" s="34"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="21"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="19" t="s">
+      <c r="A28" s="34"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="19" t="s">
+      <c r="A29" s="34"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="21"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="19" t="s">
+      <c r="A30" s="34"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="21"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="19" t="s">
+      <c r="A31" s="34"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="21"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="19" t="s">
+      <c r="A32" s="34"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="21"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="19" t="s">
+      <c r="A33" s="34"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="21"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="19" t="s">
+      <c r="A34" s="34"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="21"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="29">
+      <c r="A35" s="21">
         <v>46210</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="29"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="21"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="29"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="29"/>
-      <c r="B38" s="14" t="s">
+      <c r="A38" s="21"/>
+      <c r="B38" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="29"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14" t="s">
+      <c r="A39" s="21"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="29"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="29"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14" t="s">
+      <c r="A41" s="21"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="29"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14" t="s">
+      <c r="A42" s="21"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="29"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14" t="s">
+      <c r="A43" s="21"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="19" t="s">
+      <c r="A44" s="21"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="21"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="15"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1616,13 +1621,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1631,255 +1636,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="26">
+      <c r="A47" s="22">
         <v>46213</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="21"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="19" t="s">
+      <c r="A48" s="23"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="21"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="19" t="s">
+      <c r="A49" s="23"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="21"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="19" t="s">
+      <c r="A50" s="23"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="21"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="28"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="19" t="s">
+      <c r="A51" s="24"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="21"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="15"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="18">
+      <c r="A52" s="11">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="18"/>
+      <c r="A53" s="11"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="18">
+      <c r="A54" s="11">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="21"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="15"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="18"/>
-      <c r="B55" s="14" t="s">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C55" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="18"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="22" t="s">
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="22" t="s">
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="18"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="22" t="s">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="18"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="22" t="s">
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="22" t="s">
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="18"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="22" t="s">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="18"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="22" t="s">
+      <c r="A62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="18"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="22" t="s">
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="18">
+      <c r="A64" s="11">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="18"/>
-      <c r="B65" s="14" t="s">
+      <c r="A65" s="11"/>
+      <c r="B65" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="18"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14" t="s">
+      <c r="A66" s="11"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1888,164 +1893,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="18">
+      <c r="A68" s="11">
         <v>46220</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="18"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14" t="s">
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="18">
+      <c r="A70" s="11">
         <v>46223</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C70" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="21"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="15"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="18"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="19" t="s">
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="21"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="15"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="18"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="19" t="s">
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="21"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="15"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="18"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="19" t="s">
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="21"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="15"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="18"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="19" t="s">
+      <c r="A74" s="11"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="21"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="15"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="18"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="19" t="s">
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="21"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="15"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="18"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="19" t="s">
+      <c r="A76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="21"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="15"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="18"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="15" t="s">
+      <c r="A77" s="11"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="17"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="10"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="18"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="15" t="s">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="17"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="10"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="18"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="15" t="s">
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="17"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="18"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="15" t="s">
+      <c r="A80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="17"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="10"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2054,146 +2059,214 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="18">
+      <c r="A82" s="11">
         <v>46225</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="18"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14" t="s">
+      <c r="A83" s="11"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="18"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14" t="s">
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="18"/>
-      <c r="B85" s="14" t="s">
+      <c r="A85" s="11"/>
+      <c r="B85" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="14" t="s">
+      <c r="C85" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="18"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14" t="s">
+      <c r="A86" s="11"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="18"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="14" t="s">
+      <c r="A87" s="11"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="18"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14" t="s">
+      <c r="A88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="18"/>
-      <c r="B89" s="14"/>
-      <c r="C89" s="19" t="s">
+      <c r="A89" s="11"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="20"/>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
-      <c r="G89" s="21"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="15"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="18"/>
-      <c r="B90" s="14"/>
-      <c r="C90" s="14" t="s">
+      <c r="A90" s="11"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="8"/>
+      <c r="A91" s="22">
+        <v>46227</v>
+      </c>
+      <c r="B91" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="24"/>
+      <c r="B92" s="33"/>
+      <c r="C92" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="117">
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
+  <mergeCells count="121">
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2218,77 +2291,36 @@
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4659657B-0516-46D6-8AE5-33F9B63225A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38917265-D6B6-4C6C-9556-C20C96682E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -317,6 +317,24 @@
   </si>
   <si>
     <t>Nhận 200 PCB RFID + DB09 từ Minh Khôi</t>
+  </si>
+  <si>
+    <t>Trả BH Victory (Quân)</t>
+  </si>
+  <si>
+    <t>Trả BH Phúc Hưng (Quân)</t>
+  </si>
+  <si>
+    <t>Trả BH Hải Yến (Quân)</t>
+  </si>
+  <si>
+    <t>Trả BH A. Sửu (Quân)</t>
+  </si>
+  <si>
+    <t>Trả BH A. Trực (Quân)</t>
+  </si>
+  <si>
+    <t>Trả BH Anh Tuấn BG (Quân)</t>
   </si>
 </sst>
 </file>
@@ -529,44 +547,44 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1087,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1097,15 +1115,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="25">
+      <c r="A1" s="21">
         <v>46204</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1114,13 +1132,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
@@ -1142,13 +1160,13 @@
       <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
@@ -1173,10 +1191,10 @@
       <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="A7" s="24">
         <v>46205</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="13" t="s">
@@ -1188,8 +1206,8 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="32"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
@@ -1199,8 +1217,8 @@
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="33"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
@@ -1210,7 +1228,7 @@
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
@@ -1223,7 +1241,7 @@
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="12"/>
       <c r="C11" s="8" t="s">
         <v>20</v>
@@ -1234,7 +1252,7 @@
       <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="12"/>
       <c r="C12" s="8" t="s">
         <v>21</v>
@@ -1245,7 +1263,7 @@
       <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="12"/>
       <c r="C13" s="8" t="s">
         <v>23</v>
@@ -1256,10 +1274,10 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="30">
         <v>46206</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1271,8 +1289,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
-      <c r="B15" s="32"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="28"/>
       <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
@@ -1282,8 +1300,8 @@
       <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="23"/>
-      <c r="B16" s="32"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="28"/>
       <c r="C16" s="13" t="s">
         <v>28</v>
       </c>
@@ -1293,8 +1311,8 @@
       <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="33"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="29"/>
       <c r="C17" s="13" t="s">
         <v>27</v>
       </c>
@@ -1304,8 +1322,8 @@
       <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="31" t="s">
+      <c r="A18" s="31"/>
+      <c r="B18" s="27" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="13" t="s">
@@ -1317,8 +1335,8 @@
       <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="13" t="s">
         <v>31</v>
       </c>
@@ -1499,7 +1517,7 @@
       <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="21">
+      <c r="A35" s="33">
         <v>46210</v>
       </c>
       <c r="B35" s="12" t="s">
@@ -1514,7 +1532,7 @@
       <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
+      <c r="A36" s="33"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12" t="s">
         <v>27</v>
@@ -1525,7 +1543,7 @@
       <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
+      <c r="A37" s="33"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12" t="s">
         <v>47</v>
@@ -1536,7 +1554,7 @@
       <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
+      <c r="A38" s="33"/>
       <c r="B38" s="12" t="s">
         <v>4</v>
       </c>
@@ -1549,7 +1567,7 @@
       <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
+      <c r="A39" s="33"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12" t="s">
         <v>53</v>
@@ -1560,7 +1578,7 @@
       <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
+      <c r="A40" s="33"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12" t="s">
         <v>48</v>
@@ -1571,7 +1589,7 @@
       <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="21"/>
+      <c r="A41" s="33"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12" t="s">
         <v>49</v>
@@ -1582,7 +1600,7 @@
       <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="21"/>
+      <c r="A42" s="33"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12" t="s">
         <v>50</v>
@@ -1593,7 +1611,7 @@
       <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
+      <c r="A43" s="33"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12" t="s">
         <v>51</v>
@@ -1604,7 +1622,7 @@
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="21"/>
+      <c r="A44" s="33"/>
       <c r="B44" s="12"/>
       <c r="C44" s="13" t="s">
         <v>54</v>
@@ -1645,10 +1663,10 @@
       <c r="G46" s="12"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="22">
+      <c r="A47" s="30">
         <v>46213</v>
       </c>
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="27" t="s">
         <v>4</v>
       </c>
       <c r="C47" s="13" t="s">
@@ -1660,8 +1678,8 @@
       <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="23"/>
-      <c r="B48" s="32"/>
+      <c r="A48" s="31"/>
+      <c r="B48" s="28"/>
       <c r="C48" s="13" t="s">
         <v>57</v>
       </c>
@@ -1671,8 +1689,8 @@
       <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="23"/>
-      <c r="B49" s="32"/>
+      <c r="A49" s="31"/>
+      <c r="B49" s="28"/>
       <c r="C49" s="13" t="s">
         <v>58</v>
       </c>
@@ -1682,8 +1700,8 @@
       <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="23"/>
-      <c r="B50" s="32"/>
+      <c r="A50" s="31"/>
+      <c r="B50" s="28"/>
       <c r="C50" s="13" t="s">
         <v>60</v>
       </c>
@@ -1693,8 +1711,8 @@
       <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="24"/>
-      <c r="B51" s="33"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="29"/>
       <c r="C51" s="13" t="s">
         <v>61</v>
       </c>
@@ -2173,10 +2191,10 @@
       <c r="G90" s="12"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="22">
+      <c r="A91" s="30">
         <v>46227</v>
       </c>
-      <c r="B91" s="31" t="s">
+      <c r="B91" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C91" s="12" t="s">
@@ -2188,18 +2206,96 @@
       <c r="G91" s="12"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="24"/>
-      <c r="B92" s="33"/>
-      <c r="C92" s="12" t="s">
+      <c r="A92" s="32"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="12"/>
-      <c r="E92" s="12"/>
-      <c r="F92" s="12"/>
-      <c r="G92" s="12"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="15"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="11">
+        <v>46228</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="11"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="11"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="11"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="11"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="129">
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
     <mergeCell ref="C91:G91"/>
     <mergeCell ref="C92:G92"/>
     <mergeCell ref="B91:B92"/>
@@ -2270,6 +2366,12 @@
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="A3:A6"/>
@@ -2282,15 +2384,7 @@
     <mergeCell ref="A7:A13"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C23:G23"/>
@@ -2321,6 +2415,8 @@
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C32:G32"/>
     <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38917265-D6B6-4C6C-9556-C20C96682E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED864458-EA82-438C-8DB5-9E6313C70419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -508,6 +508,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -520,9 +538,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -532,20 +547,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -564,33 +591,6 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -914,15 +914,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="16">
+      <c r="A1" s="8">
         <v>46174</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -931,146 +931,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>46202</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="17">
         <v>46203</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="8" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1080,6 +1080,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1090,14 +1098,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1115,15 +1115,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="21">
+      <c r="A1" s="30">
         <v>46204</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1132,152 +1132,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
+      <c r="A7" s="33">
         <v>46205</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="25"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="8" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="8" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="34"/>
+      <c r="B10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="34"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8" t="s">
+      <c r="A13" s="35"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
+      <c r="A14" s="23">
         <v>46206</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="21" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1289,348 +1289,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="13" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="13" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="27"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="31"/>
-      <c r="B18" s="27" t="s">
+      <c r="A18" s="27"/>
+      <c r="B18" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="32"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="13" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
+      <c r="A20" s="29">
         <v>46209</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12" t="s">
+      <c r="A21" s="29"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="29"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="29"/>
+      <c r="B23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
+      <c r="A24" s="29"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13" t="s">
+      <c r="A25" s="29"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13" t="s">
+      <c r="A26" s="29"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13" t="s">
+      <c r="A27" s="29"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13" t="s">
+      <c r="A28" s="29"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13" t="s">
+      <c r="A29" s="29"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="15"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13" t="s">
+      <c r="A30" s="29"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="15"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13" t="s">
+      <c r="A31" s="29"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="15"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13" t="s">
+      <c r="A32" s="29"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13" t="s">
+      <c r="A33" s="29"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="15"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13" t="s">
+      <c r="A34" s="29"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="15"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="33">
+      <c r="A35" s="28">
         <v>46210</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12" t="s">
+      <c r="A36" s="28"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12" t="s">
+      <c r="A37" s="28"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
-      <c r="B38" s="12" t="s">
+      <c r="A38" s="28"/>
+      <c r="B38" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="33"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12" t="s">
+      <c r="A39" s="28"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="33"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12" t="s">
+      <c r="A40" s="28"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12" t="s">
+      <c r="A41" s="28"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="33"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12" t="s">
+      <c r="A42" s="28"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="33"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12" t="s">
+      <c r="A43" s="28"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="33"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="13" t="s">
+      <c r="A44" s="28"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="15"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1639,13 +1639,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1654,255 +1654,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="30">
+      <c r="A47" s="23">
         <v>46213</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="15"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="31"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="13" t="s">
+      <c r="A48" s="27"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="15"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="31"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="13" t="s">
+      <c r="A49" s="27"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="15"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="20"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="31"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="13" t="s">
+      <c r="A50" s="27"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="15"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="20"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="32"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="13" t="s">
+      <c r="A51" s="24"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="15"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="11">
+      <c r="A52" s="17">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
+      <c r="A54" s="17">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="15"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12" t="s">
+      <c r="A55" s="17"/>
+      <c r="B55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="35" t="s">
+      <c r="C55" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="35" t="s">
+      <c r="A56" s="17"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="35" t="s">
+      <c r="A57" s="17"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="35" t="s">
+      <c r="A58" s="17"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="35" t="s">
+      <c r="A59" s="17"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="35" t="s">
+      <c r="A60" s="17"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="35" t="s">
+      <c r="A61" s="17"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="35" t="s">
+      <c r="A62" s="17"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="35"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="35" t="s">
+      <c r="A63" s="17"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
+      <c r="A64" s="17">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12" t="s">
+      <c r="A65" s="17"/>
+      <c r="B65" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12" t="s">
+      <c r="A66" s="17"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1911,164 +1911,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
+      <c r="A68" s="17">
         <v>46220</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12" t="s">
+      <c r="A69" s="17"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="11">
+      <c r="A70" s="17">
         <v>46223</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="15"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="20"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="13" t="s">
+      <c r="A71" s="17"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="15"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="20"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13" t="s">
+      <c r="A72" s="17"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="15"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="13" t="s">
+      <c r="A73" s="17"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="15"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="20"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="13" t="s">
+      <c r="A74" s="17"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="15"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="20"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="13" t="s">
+      <c r="A75" s="17"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="15"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="20"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="13" t="s">
+      <c r="A76" s="17"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="15"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="20"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="8" t="s">
+      <c r="A77" s="17"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="10"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="16"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="8" t="s">
+      <c r="A78" s="17"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="10"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="16"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="8" t="s">
+      <c r="A79" s="17"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="10"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="16"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="8" t="s">
+      <c r="A80" s="17"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="10"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="16"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2077,277 +2077,262 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="11">
+      <c r="A82" s="17">
         <v>46225</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="11"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12" t="s">
+      <c r="A83" s="17"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="11"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12" t="s">
+      <c r="A84" s="17"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="11"/>
-      <c r="B85" s="12" t="s">
+      <c r="A85" s="17"/>
+      <c r="B85" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="11"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="12" t="s">
+      <c r="A86" s="17"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="11"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12" t="s">
+      <c r="A87" s="17"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="11"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12" t="s">
+      <c r="A88" s="17"/>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="11"/>
-      <c r="B89" s="12"/>
-      <c r="C89" s="13" t="s">
+      <c r="A89" s="17"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="15"/>
+      <c r="D89" s="19"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="20"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="11"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="12" t="s">
+      <c r="A90" s="17"/>
+      <c r="B90" s="13"/>
+      <c r="C90" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="12"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="30">
+      <c r="A91" s="23">
         <v>46227</v>
       </c>
-      <c r="B91" s="27" t="s">
+      <c r="B91" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="12"/>
-      <c r="E91" s="12"/>
-      <c r="F91" s="12"/>
-      <c r="G91" s="12"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="32"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="13" t="s">
+      <c r="A92" s="24"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="15"/>
+      <c r="D92" s="19"/>
+      <c r="E92" s="19"/>
+      <c r="F92" s="19"/>
+      <c r="G92" s="20"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="11">
+      <c r="A93" s="17">
         <v>46228</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="12"/>
-      <c r="E93" s="12"/>
-      <c r="F93" s="12"/>
-      <c r="G93" s="12"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="11"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="12" t="s">
+      <c r="A94" s="17"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="12"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="12"/>
-      <c r="G94" s="12"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="11"/>
-      <c r="B95" s="12"/>
-      <c r="C95" s="12" t="s">
+      <c r="A95" s="17"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="12"/>
-      <c r="E95" s="12"/>
-      <c r="F95" s="12"/>
-      <c r="G95" s="12"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="11"/>
-      <c r="B96" s="12"/>
-      <c r="C96" s="12" t="s">
+      <c r="A96" s="17"/>
+      <c r="B96" s="13"/>
+      <c r="C96" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="12"/>
-      <c r="E96" s="12"/>
-      <c r="F96" s="12"/>
-      <c r="G96" s="12"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="11"/>
-      <c r="B97" s="12"/>
-      <c r="C97" s="12" t="s">
+      <c r="A97" s="17"/>
+      <c r="B97" s="13"/>
+      <c r="C97" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="12"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="12"/>
-      <c r="G97" s="12"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="11"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="12" t="s">
+      <c r="A98" s="17"/>
+      <c r="B98" s="13"/>
+      <c r="C98" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="12"/>
-      <c r="E98" s="12"/>
-      <c r="F98" s="12"/>
-      <c r="G98" s="12"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="129">
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="B14:B17"/>
@@ -2372,51 +2357,66 @@
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED864458-EA82-438C-8DB5-9E6313C70419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF9D6C6-CBCE-4B74-B545-EE895EC8AD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>Trả BH Anh Tuấn BG (Quân)</t>
+  </si>
+  <si>
+    <t>Nhận BH A.Trực</t>
   </si>
 </sst>
 </file>
@@ -508,6 +511,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -523,74 +550,50 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -914,15 +917,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8">
+      <c r="A1" s="16">
         <v>46174</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -931,146 +934,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="11">
         <v>46202</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="11">
         <v>46203</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1080,14 +1083,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1098,6 +1093,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1105,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1115,15 +1118,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="30">
+      <c r="A1" s="21">
         <v>46204</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1132,152 +1135,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="11">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="33">
+      <c r="A7" s="24">
         <v>46205</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="25"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="25"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="25"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="26"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+      <c r="A14" s="30">
         <v>46206</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1289,348 +1292,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="27"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="18" t="s">
+      <c r="A15" s="31"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="18" t="s">
+      <c r="A16" s="31"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="31"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="20"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="21" t="s">
+      <c r="A18" s="31"/>
+      <c r="B18" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="18" t="s">
+      <c r="A19" s="32"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="29">
+      <c r="A20" s="34">
         <v>46209</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="34"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="34"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="29"/>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="18" t="s">
+      <c r="A24" s="34"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="18" t="s">
+      <c r="A25" s="34"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="18" t="s">
+      <c r="A26" s="34"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="29"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="18" t="s">
+      <c r="A27" s="34"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="18" t="s">
+      <c r="A28" s="34"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="18" t="s">
+      <c r="A29" s="34"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="18" t="s">
+      <c r="A30" s="34"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="18" t="s">
+      <c r="A31" s="34"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="18" t="s">
+      <c r="A32" s="34"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="18" t="s">
+      <c r="A33" s="34"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="15"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="29"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="18" t="s">
+      <c r="A34" s="34"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="20"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="15"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="28">
+      <c r="A35" s="33">
         <v>46210</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13" t="s">
+      <c r="A36" s="33"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13" t="s">
+      <c r="A37" s="33"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="28"/>
-      <c r="B38" s="13" t="s">
+      <c r="A38" s="33"/>
+      <c r="B38" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13" t="s">
+      <c r="A39" s="33"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="28"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13" t="s">
+      <c r="A40" s="33"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13" t="s">
+      <c r="A41" s="33"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13" t="s">
+      <c r="A42" s="33"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13" t="s">
+      <c r="A43" s="33"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="18" t="s">
+      <c r="A44" s="33"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="20"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="15"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1639,13 +1642,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1654,255 +1657,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="23">
+      <c r="A47" s="30">
         <v>46213</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="20"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="15"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="18" t="s">
+      <c r="A48" s="31"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="20"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="15"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="18" t="s">
+      <c r="A49" s="31"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="20"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="18" t="s">
+      <c r="A50" s="31"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="20"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="15"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="24"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="18" t="s">
+      <c r="A51" s="32"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="20"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="15"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
+      <c r="A52" s="11">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
+      <c r="A53" s="11"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="17">
+      <c r="A54" s="11">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="20"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="15"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="13" t="s">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="25" t="s">
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="25" t="s">
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="17"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="25" t="s">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="17"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="25" t="s">
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="17"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="25" t="s">
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="17"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="25" t="s">
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="17"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="25" t="s">
+      <c r="A62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="25" t="s">
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="17">
+      <c r="A64" s="11">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
-      <c r="B65" s="13" t="s">
+      <c r="A65" s="11"/>
+      <c r="B65" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13" t="s">
+      <c r="A66" s="11"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1911,164 +1914,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="17">
+      <c r="A68" s="11">
         <v>46220</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="17"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13" t="s">
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="17">
+      <c r="A70" s="11">
         <v>46223</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="20"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="15"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="17"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="18" t="s">
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="20"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="15"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="17"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="18" t="s">
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="20"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="15"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="17"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="18" t="s">
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="20"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="15"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="17"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="18" t="s">
+      <c r="A74" s="11"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="20"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="15"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="17"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="18" t="s">
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="20"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="15"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="17"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="18" t="s">
+      <c r="A76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="20"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="15"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="17"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="14" t="s">
+      <c r="A77" s="11"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="16"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="10"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="14" t="s">
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="16"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="10"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="17"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="14" t="s">
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="16"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="17"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="14" t="s">
+      <c r="A80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="16"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="10"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2077,262 +2080,307 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="17">
+      <c r="A82" s="11">
         <v>46225</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="17"/>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13" t="s">
+      <c r="A83" s="11"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="17"/>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13" t="s">
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="17"/>
-      <c r="B85" s="13" t="s">
+      <c r="A85" s="11"/>
+      <c r="B85" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="17"/>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13" t="s">
+      <c r="A86" s="11"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="17"/>
-      <c r="B87" s="13"/>
-      <c r="C87" s="13" t="s">
+      <c r="A87" s="11"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="17"/>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13" t="s">
+      <c r="A88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="17"/>
-      <c r="B89" s="13"/>
-      <c r="C89" s="18" t="s">
+      <c r="A89" s="11"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="19"/>
-      <c r="G89" s="20"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="15"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="17"/>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13" t="s">
+      <c r="A90" s="11"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="23">
+      <c r="A91" s="30">
         <v>46227</v>
       </c>
-      <c r="B91" s="21" t="s">
+      <c r="B91" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="24"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="18" t="s">
+      <c r="A92" s="32"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19"/>
-      <c r="G92" s="20"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="15"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="17">
+      <c r="A93" s="11">
         <v>46228</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="17"/>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13" t="s">
+      <c r="A94" s="11"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="17"/>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13" t="s">
+      <c r="A95" s="11"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="17"/>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13" t="s">
+      <c r="A96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="17"/>
-      <c r="B97" s="13"/>
-      <c r="C97" s="13" t="s">
+      <c r="A97" s="11"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="17"/>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13" t="s">
+      <c r="A98" s="11"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="11">
+        <v>46200</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="129">
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
+  <mergeCells count="133">
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="B14:B17"/>
@@ -2357,66 +2405,51 @@
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF9D6C6-CBCE-4B74-B545-EE895EC8AD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45D31BE-517D-4488-9707-055CB703565F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="105">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t>Nhận BH A.Trực</t>
+  </si>
+  <si>
+    <t>Nhập kho 20 RFID(old) + 100 RFID(new)</t>
+  </si>
+  <si>
+    <t>Nhận BH Minh Huy</t>
   </si>
 </sst>
 </file>
@@ -490,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -511,6 +517,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -523,9 +547,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -535,20 +556,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -568,32 +601,14 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -917,15 +932,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="16">
+      <c r="A1" s="8">
         <v>46174</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -934,146 +949,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>46202</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="17">
         <v>46203</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="8" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1083,6 +1098,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1093,14 +1116,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1108,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1118,15 +1133,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="21">
+      <c r="A1" s="30">
         <v>46204</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1135,152 +1150,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="17">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
+      <c r="A7" s="33">
         <v>46205</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="25"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="8" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="8" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="34"/>
+      <c r="B10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="34"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8" t="s">
+      <c r="A13" s="35"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="30">
+      <c r="A14" s="23">
         <v>46206</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="21" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1292,348 +1307,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="13" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="13" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="27"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="31"/>
-      <c r="B18" s="27" t="s">
+      <c r="A18" s="27"/>
+      <c r="B18" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="15"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="32"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="13" t="s">
+      <c r="A19" s="24"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="15"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
+      <c r="A20" s="29">
         <v>46209</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12" t="s">
+      <c r="A21" s="29"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="29"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="29"/>
+      <c r="B23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
+      <c r="A24" s="29"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13" t="s">
+      <c r="A25" s="29"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="15"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13" t="s">
+      <c r="A26" s="29"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13" t="s">
+      <c r="A27" s="29"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="15"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="20"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13" t="s">
+      <c r="A28" s="29"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="13" t="s">
+      <c r="A29" s="29"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="15"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="20"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="34"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="13" t="s">
+      <c r="A30" s="29"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="15"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="20"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="34"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="13" t="s">
+      <c r="A31" s="29"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="15"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="20"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="13" t="s">
+      <c r="A32" s="29"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="15"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="20"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="13" t="s">
+      <c r="A33" s="29"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="15"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="13" t="s">
+      <c r="A34" s="29"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="15"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="33">
+      <c r="A35" s="28">
         <v>46210</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12" t="s">
+      <c r="A36" s="28"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12" t="s">
+      <c r="A37" s="28"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
-      <c r="B38" s="12" t="s">
+      <c r="A38" s="28"/>
+      <c r="B38" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="33"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12" t="s">
+      <c r="A39" s="28"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="33"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12" t="s">
+      <c r="A40" s="28"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12" t="s">
+      <c r="A41" s="28"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="33"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12" t="s">
+      <c r="A42" s="28"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="33"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12" t="s">
+      <c r="A43" s="28"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="33"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="13" t="s">
+      <c r="A44" s="28"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="15"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1642,13 +1657,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1657,255 +1672,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="30">
+      <c r="A47" s="23">
         <v>46213</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="15"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="20"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="31"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="13" t="s">
+      <c r="A48" s="27"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="15"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="20"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="31"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="13" t="s">
+      <c r="A49" s="27"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="15"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="20"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="31"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="13" t="s">
+      <c r="A50" s="27"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="15"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="20"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="32"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="13" t="s">
+      <c r="A51" s="24"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="15"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="20"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="11">
+      <c r="A52" s="17">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
+      <c r="A54" s="17">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="15"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="20"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12" t="s">
+      <c r="A55" s="17"/>
+      <c r="B55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="35" t="s">
+      <c r="C55" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="35" t="s">
+      <c r="A56" s="17"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="35" t="s">
+      <c r="A57" s="17"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="35" t="s">
+      <c r="A58" s="17"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="35" t="s">
+      <c r="A59" s="17"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="35" t="s">
+      <c r="A60" s="17"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="35" t="s">
+      <c r="A61" s="17"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="35" t="s">
+      <c r="A62" s="17"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="35"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="35" t="s">
+      <c r="A63" s="17"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
+      <c r="A64" s="17">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12" t="s">
+      <c r="A65" s="17"/>
+      <c r="B65" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12" t="s">
+      <c r="A66" s="17"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1914,164 +1929,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
+      <c r="A68" s="17">
         <v>46220</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12" t="s">
+      <c r="A69" s="17"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="11">
+      <c r="A70" s="17">
         <v>46223</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="15"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="20"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="13" t="s">
+      <c r="A71" s="17"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="15"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="20"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13" t="s">
+      <c r="A72" s="17"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="15"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="13" t="s">
+      <c r="A73" s="17"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="15"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="20"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="13" t="s">
+      <c r="A74" s="17"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="15"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="20"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="13" t="s">
+      <c r="A75" s="17"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="15"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="20"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="13" t="s">
+      <c r="A76" s="17"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="15"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="20"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="8" t="s">
+      <c r="A77" s="17"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="10"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="16"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="8" t="s">
+      <c r="A78" s="17"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="10"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="16"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="8" t="s">
+      <c r="A79" s="17"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="10"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="16"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="8" t="s">
+      <c r="A80" s="17"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="10"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="16"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2080,307 +2095,319 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="11">
+      <c r="A82" s="17">
         <v>46225</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="11"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12" t="s">
+      <c r="A83" s="17"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="11"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12" t="s">
+      <c r="A84" s="17"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="11"/>
-      <c r="B85" s="12" t="s">
+      <c r="A85" s="17"/>
+      <c r="B85" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="11"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="12" t="s">
+      <c r="A86" s="17"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="11"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12" t="s">
+      <c r="A87" s="17"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="11"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12" t="s">
+      <c r="A88" s="17"/>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="11"/>
-      <c r="B89" s="12"/>
-      <c r="C89" s="13" t="s">
+      <c r="A89" s="17"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="15"/>
+      <c r="D89" s="19"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="20"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="11"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="12" t="s">
+      <c r="A90" s="17"/>
+      <c r="B90" s="13"/>
+      <c r="C90" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
-      <c r="F90" s="12"/>
-      <c r="G90" s="12"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="30">
+      <c r="A91" s="23">
         <v>46227</v>
       </c>
-      <c r="B91" s="27" t="s">
+      <c r="B91" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="12"/>
-      <c r="E91" s="12"/>
-      <c r="F91" s="12"/>
-      <c r="G91" s="12"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="32"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="13" t="s">
+      <c r="A92" s="24"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="15"/>
+      <c r="D92" s="19"/>
+      <c r="E92" s="19"/>
+      <c r="F92" s="19"/>
+      <c r="G92" s="20"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="11">
+      <c r="A93" s="17">
         <v>46228</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="12"/>
-      <c r="E93" s="12"/>
-      <c r="F93" s="12"/>
-      <c r="G93" s="12"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="11"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="12" t="s">
+      <c r="A94" s="17"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="12"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="12"/>
-      <c r="G94" s="12"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="11"/>
-      <c r="B95" s="12"/>
-      <c r="C95" s="12" t="s">
+      <c r="A95" s="17"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="12"/>
-      <c r="E95" s="12"/>
-      <c r="F95" s="12"/>
-      <c r="G95" s="12"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="11"/>
-      <c r="B96" s="12"/>
-      <c r="C96" s="12" t="s">
+      <c r="A96" s="17"/>
+      <c r="B96" s="13"/>
+      <c r="C96" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="12"/>
-      <c r="E96" s="12"/>
-      <c r="F96" s="12"/>
-      <c r="G96" s="12"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="11"/>
-      <c r="B97" s="12"/>
-      <c r="C97" s="12" t="s">
+      <c r="A97" s="17"/>
+      <c r="B97" s="13"/>
+      <c r="C97" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="12"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="12"/>
-      <c r="G97" s="12"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="11"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="12" t="s">
+      <c r="A98" s="17"/>
+      <c r="B98" s="13"/>
+      <c r="C98" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="12"/>
-      <c r="E98" s="12"/>
-      <c r="F98" s="12"/>
-      <c r="G98" s="12"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="11">
+      <c r="A99" s="17">
         <v>46200</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="12"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="12"/>
-      <c r="G99" s="12"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="11"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="12" t="s">
+      <c r="A100" s="17"/>
+      <c r="B100" s="13"/>
+      <c r="C100" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="12"/>
-      <c r="E100" s="12"/>
-      <c r="F100" s="12"/>
-      <c r="G100" s="12"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="36">
+        <v>46201</v>
+      </c>
+      <c r="B101" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="36"/>
+      <c r="B102" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" s="38"/>
+      <c r="E102" s="38"/>
+      <c r="F102" s="38"/>
+      <c r="G102" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="133">
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
+  <mergeCells count="136">
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="B14:B17"/>
@@ -2405,51 +2432,70 @@
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45D31BE-517D-4488-9707-055CB703565F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A015B6-949C-4F5E-B5A5-C3CA2CD9395A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -340,10 +340,10 @@
     <t>Nhận BH A.Trực</t>
   </si>
   <si>
-    <t>Nhập kho 20 RFID(old) + 100 RFID(new)</t>
-  </si>
-  <si>
     <t>Nhận BH Minh Huy</t>
+  </si>
+  <si>
+    <t>Nhập kho 200 RFID(old) + 100 RFID(new)</t>
   </si>
 </sst>
 </file>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -517,6 +517,33 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -533,82 +560,52 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -932,15 +929,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="8">
+      <c r="A1" s="17">
         <v>46174</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -949,16 +946,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="12">
         <v>46202</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -973,7 +970,7 @@
       <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
+      <c r="A4" s="12"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13" t="s">
         <v>0</v>
@@ -984,7 +981,7 @@
       <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13" t="s">
         <v>3</v>
@@ -995,7 +992,7 @@
       <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
@@ -1008,7 +1005,7 @@
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13" t="s">
         <v>10</v>
@@ -1019,7 +1016,7 @@
       <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13" t="s">
         <v>9</v>
@@ -1030,65 +1027,65 @@
       <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="12">
         <v>46203</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+      <c r="A10" s="12"/>
       <c r="B10" s="13"/>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1098,14 +1095,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1116,6 +1105,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1133,15 +1130,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="30">
+      <c r="A1" s="23">
         <v>46204</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1150,16 +1147,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="12">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1174,20 +1171,20 @@
       <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
+      <c r="A4" s="12"/>
       <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13" t="s">
         <v>17</v>
@@ -1198,7 +1195,7 @@
       <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13" t="s">
         <v>18</v>
@@ -1209,93 +1206,93 @@
       <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="33">
+      <c r="A7" s="26">
         <v>46205</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="27"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="27"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="13"/>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="13"/>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="13"/>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="23">
+      <c r="A14" s="32">
         <v>46206</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="29" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1307,64 +1304,64 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="27"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="18" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="18" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="20"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="20"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="21" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="18" t="s">
+      <c r="A19" s="34"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="20"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="29">
+      <c r="A20" s="36">
         <v>46209</v>
       </c>
       <c r="B20" s="13" t="s">
@@ -1379,7 +1376,7 @@
       <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13" t="s">
         <v>34</v>
@@ -1390,7 +1387,7 @@
       <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13" t="s">
         <v>15</v>
@@ -1401,7 +1398,7 @@
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="29"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="13" t="s">
         <v>4</v>
       </c>
@@ -1414,128 +1411,128 @@
       <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="13"/>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="13"/>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="13"/>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="20"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="29"/>
+      <c r="A27" s="36"/>
       <c r="B27" s="13"/>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
+      <c r="A28" s="36"/>
       <c r="B28" s="13"/>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="13"/>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="13"/>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
+      <c r="A31" s="36"/>
       <c r="B31" s="13"/>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
+      <c r="A32" s="36"/>
       <c r="B32" s="13"/>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="20"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
+      <c r="A33" s="36"/>
       <c r="B33" s="13"/>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="20"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="29"/>
+      <c r="A34" s="36"/>
       <c r="B34" s="13"/>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="20"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="28">
+      <c r="A35" s="35">
         <v>46210</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -1550,7 +1547,7 @@
       <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
+      <c r="A36" s="35"/>
       <c r="B36" s="13"/>
       <c r="C36" s="13" t="s">
         <v>27</v>
@@ -1561,7 +1558,7 @@
       <c r="G36" s="13"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
+      <c r="A37" s="35"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13" t="s">
         <v>47</v>
@@ -1572,7 +1569,7 @@
       <c r="G37" s="13"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="28"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="13" t="s">
         <v>4</v>
       </c>
@@ -1585,7 +1582,7 @@
       <c r="G38" s="13"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
+      <c r="A39" s="35"/>
       <c r="B39" s="13"/>
       <c r="C39" s="13" t="s">
         <v>53</v>
@@ -1596,7 +1593,7 @@
       <c r="G39" s="13"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="28"/>
+      <c r="A40" s="35"/>
       <c r="B40" s="13"/>
       <c r="C40" s="13" t="s">
         <v>48</v>
@@ -1607,7 +1604,7 @@
       <c r="G40" s="13"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="13"/>
       <c r="C41" s="13" t="s">
         <v>49</v>
@@ -1618,7 +1615,7 @@
       <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
+      <c r="A42" s="35"/>
       <c r="B42" s="13"/>
       <c r="C42" s="13" t="s">
         <v>50</v>
@@ -1629,7 +1626,7 @@
       <c r="G42" s="13"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
+      <c r="A43" s="35"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13" t="s">
         <v>51</v>
@@ -1640,15 +1637,15 @@
       <c r="G43" s="13"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
+      <c r="A44" s="35"/>
       <c r="B44" s="13"/>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="20"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1681,66 +1678,66 @@
       <c r="G46" s="13"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="23">
+      <c r="A47" s="32">
         <v>46213</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="20"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="16"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="18" t="s">
+      <c r="A48" s="33"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="20"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="16"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="18" t="s">
+      <c r="A49" s="33"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="20"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="16"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="18" t="s">
+      <c r="A50" s="33"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="20"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="16"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="24"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="18" t="s">
+      <c r="A51" s="34"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="20"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="16"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
+      <c r="A52" s="12">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -1755,7 +1752,7 @@
       <c r="G52" s="13"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
+      <c r="A53" s="12"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
@@ -1768,123 +1765,123 @@
       <c r="G53" s="13"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="17">
+      <c r="A54" s="12">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="20"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
+      <c r="A55" s="12"/>
       <c r="B55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="37"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
+      <c r="A56" s="12"/>
       <c r="B56" s="13"/>
-      <c r="C56" s="25" t="s">
+      <c r="C56" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
+      <c r="A57" s="12"/>
       <c r="B57" s="13"/>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="17"/>
+      <c r="A58" s="12"/>
       <c r="B58" s="13"/>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25"/>
-      <c r="G58" s="25"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="17"/>
+      <c r="A59" s="12"/>
       <c r="B59" s="13"/>
-      <c r="C59" s="25" t="s">
+      <c r="C59" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-      <c r="G59" s="25"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="17"/>
+      <c r="A60" s="12"/>
       <c r="B60" s="13"/>
-      <c r="C60" s="25" t="s">
+      <c r="C60" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="17"/>
+      <c r="A61" s="12"/>
       <c r="B61" s="13"/>
-      <c r="C61" s="25" t="s">
+      <c r="C61" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="17"/>
+      <c r="A62" s="12"/>
       <c r="B62" s="13"/>
-      <c r="C62" s="25" t="s">
+      <c r="C62" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
+      <c r="A63" s="12"/>
       <c r="B63" s="13"/>
-      <c r="C63" s="25" t="s">
+      <c r="C63" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="17">
+      <c r="A64" s="12">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -1899,7 +1896,7 @@
       <c r="G64" s="13"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
+      <c r="A65" s="12"/>
       <c r="B65" s="13" t="s">
         <v>4</v>
       </c>
@@ -1912,7 +1909,7 @@
       <c r="G65" s="13"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
+      <c r="A66" s="12"/>
       <c r="B66" s="13"/>
       <c r="C66" s="13" t="s">
         <v>74</v>
@@ -1938,7 +1935,7 @@
       <c r="G67" s="13"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="17">
+      <c r="A68" s="12">
         <v>46220</v>
       </c>
       <c r="B68" s="13" t="s">
@@ -1953,7 +1950,7 @@
       <c r="G68" s="13"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="17"/>
+      <c r="A69" s="12"/>
       <c r="B69" s="13"/>
       <c r="C69" s="13" t="s">
         <v>77</v>
@@ -1964,129 +1961,129 @@
       <c r="G69" s="13"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="17">
+      <c r="A70" s="12">
         <v>46223</v>
       </c>
       <c r="B70" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="20"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="16"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="17"/>
+      <c r="A71" s="12"/>
       <c r="B71" s="13"/>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="20"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="16"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="17"/>
+      <c r="A72" s="12"/>
       <c r="B72" s="13"/>
-      <c r="C72" s="18" t="s">
+      <c r="C72" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="20"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="15"/>
+      <c r="G72" s="16"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="17"/>
+      <c r="A73" s="12"/>
       <c r="B73" s="13"/>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="20"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="16"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="17"/>
+      <c r="A74" s="12"/>
       <c r="B74" s="13"/>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="20"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="16"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="17"/>
+      <c r="A75" s="12"/>
       <c r="B75" s="13"/>
-      <c r="C75" s="18" t="s">
+      <c r="C75" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="20"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="16"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="17"/>
+      <c r="A76" s="12"/>
       <c r="B76" s="13"/>
-      <c r="C76" s="18" t="s">
+      <c r="C76" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="20"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="16"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="17"/>
+      <c r="A77" s="12"/>
       <c r="B77" s="13"/>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="16"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="10"/>
+      <c r="G77" s="11"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
+      <c r="A78" s="12"/>
       <c r="B78" s="13"/>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="16"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="11"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="17"/>
+      <c r="A79" s="12"/>
       <c r="B79" s="13"/>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="16"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="11"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="17"/>
+      <c r="A80" s="12"/>
       <c r="B80" s="13"/>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="16"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="11"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2104,7 +2101,7 @@
       <c r="G81" s="13"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="17">
+      <c r="A82" s="12">
         <v>46225</v>
       </c>
       <c r="B82" s="13" t="s">
@@ -2119,7 +2116,7 @@
       <c r="G82" s="13"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="17"/>
+      <c r="A83" s="12"/>
       <c r="B83" s="13"/>
       <c r="C83" s="13" t="s">
         <v>90</v>
@@ -2130,7 +2127,7 @@
       <c r="G83" s="13"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="17"/>
+      <c r="A84" s="12"/>
       <c r="B84" s="13"/>
       <c r="C84" s="13" t="s">
         <v>93</v>
@@ -2141,7 +2138,7 @@
       <c r="G84" s="13"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="17"/>
+      <c r="A85" s="12"/>
       <c r="B85" s="13" t="s">
         <v>4</v>
       </c>
@@ -2154,7 +2151,7 @@
       <c r="G85" s="13"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="17"/>
+      <c r="A86" s="12"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13" t="s">
         <v>72</v>
@@ -2165,7 +2162,7 @@
       <c r="G86" s="13"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="17"/>
+      <c r="A87" s="12"/>
       <c r="B87" s="13"/>
       <c r="C87" s="13" t="s">
         <v>89</v>
@@ -2176,7 +2173,7 @@
       <c r="G87" s="13"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="17"/>
+      <c r="A88" s="12"/>
       <c r="B88" s="13"/>
       <c r="C88" s="13" t="s">
         <v>35</v>
@@ -2187,18 +2184,18 @@
       <c r="G88" s="13"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="17"/>
+      <c r="A89" s="12"/>
       <c r="B89" s="13"/>
-      <c r="C89" s="18" t="s">
+      <c r="C89" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="19"/>
-      <c r="G89" s="20"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="15"/>
+      <c r="G89" s="16"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="17"/>
+      <c r="A90" s="12"/>
       <c r="B90" s="13"/>
       <c r="C90" s="13" t="s">
         <v>92</v>
@@ -2209,10 +2206,10 @@
       <c r="G90" s="13"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="23">
+      <c r="A91" s="32">
         <v>46227</v>
       </c>
-      <c r="B91" s="21" t="s">
+      <c r="B91" s="29" t="s">
         <v>5</v>
       </c>
       <c r="C91" s="13" t="s">
@@ -2224,18 +2221,18 @@
       <c r="G91" s="13"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="24"/>
-      <c r="B92" s="22"/>
-      <c r="C92" s="18" t="s">
+      <c r="A92" s="34"/>
+      <c r="B92" s="31"/>
+      <c r="C92" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19"/>
-      <c r="G92" s="20"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="15"/>
+      <c r="G92" s="16"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="17">
+      <c r="A93" s="12">
         <v>46228</v>
       </c>
       <c r="B93" s="13" t="s">
@@ -2250,7 +2247,7 @@
       <c r="G93" s="13"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="17"/>
+      <c r="A94" s="12"/>
       <c r="B94" s="13"/>
       <c r="C94" s="13" t="s">
         <v>97</v>
@@ -2261,7 +2258,7 @@
       <c r="G94" s="13"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="17"/>
+      <c r="A95" s="12"/>
       <c r="B95" s="13"/>
       <c r="C95" s="13" t="s">
         <v>98</v>
@@ -2272,7 +2269,7 @@
       <c r="G95" s="13"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="17"/>
+      <c r="A96" s="12"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13" t="s">
         <v>99</v>
@@ -2283,7 +2280,7 @@
       <c r="G96" s="13"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="17"/>
+      <c r="A97" s="12"/>
       <c r="B97" s="13"/>
       <c r="C97" s="13" t="s">
         <v>100</v>
@@ -2294,7 +2291,7 @@
       <c r="G97" s="13"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="17"/>
+      <c r="A98" s="12"/>
       <c r="B98" s="13"/>
       <c r="C98" s="13" t="s">
         <v>101</v>
@@ -2305,7 +2302,7 @@
       <c r="G98" s="13"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="17">
+      <c r="A99" s="12">
         <v>46200</v>
       </c>
       <c r="B99" s="13" t="s">
@@ -2320,7 +2317,7 @@
       <c r="G99" s="13"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="17"/>
+      <c r="A100" s="12"/>
       <c r="B100" s="13"/>
       <c r="C100" s="13" t="s">
         <v>39</v>
@@ -2331,57 +2328,123 @@
       <c r="G100" s="13"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="36">
+      <c r="A101" s="12">
         <v>46201</v>
       </c>
-      <c r="B101" s="37" t="s">
+      <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="38" t="s">
+      <c r="C101" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="22"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="12"/>
+      <c r="B102" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D101" s="38"/>
-      <c r="E101" s="38"/>
-      <c r="F101" s="38"/>
-      <c r="G101" s="38"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="36"/>
-      <c r="B102" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="C102" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D102" s="38"/>
-      <c r="E102" s="38"/>
-      <c r="F102" s="38"/>
-      <c r="G102" s="38"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
     <mergeCell ref="C15:G15"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="C19:G19"/>
@@ -2406,96 +2469,30 @@
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A015B6-949C-4F5E-B5A5-C3CA2CD9395A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086F5CE0-57A4-460A-B01B-9B280E6747E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -344,6 +344,15 @@
   </si>
   <si>
     <t>Nhập kho 200 RFID(old) + 100 RFID(new)</t>
+  </si>
+  <si>
+    <t>30/07/26</t>
+  </si>
+  <si>
+    <t>Trả BH Anh Tuấn BG (A. Lực)</t>
+  </si>
+  <si>
+    <t>Nhận BH Tuyên Hằng</t>
   </si>
 </sst>
 </file>
@@ -496,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -520,6 +529,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -532,9 +559,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -544,69 +568,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -929,15 +939,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="17">
+      <c r="A1" s="9">
         <v>46174</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -946,146 +956,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="18">
         <v>46202</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="18">
         <v>46203</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="9" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="9" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="9" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1095,6 +1105,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1105,14 +1123,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1120,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1130,15 +1140,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="23">
+      <c r="A1" s="31">
         <v>46204</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1147,152 +1157,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="18">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="34">
         <v>46205</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="16"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="9" t="s">
+      <c r="A8" s="35"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="9" t="s">
+      <c r="A9" s="35"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="35"/>
+      <c r="B10" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="9" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="9" t="s">
+      <c r="A12" s="35"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="9" t="s">
+      <c r="A13" s="36"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="32">
+      <c r="A14" s="24">
         <v>46206</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="22" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1304,348 +1314,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="28"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="14" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="28"/>
+      <c r="B18" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="14" t="s">
+      <c r="A19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="36">
+      <c r="A20" s="30">
         <v>46209</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="30"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="30"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="30"/>
+      <c r="B23" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14" t="s">
+      <c r="A24" s="30"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14" t="s">
+      <c r="A25" s="30"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14" t="s">
+      <c r="A26" s="30"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="21"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="14" t="s">
+      <c r="A27" s="30"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="14" t="s">
+      <c r="A28" s="30"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="14" t="s">
+      <c r="A29" s="30"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="16"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="14" t="s">
+      <c r="A30" s="30"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="16"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14" t="s">
+      <c r="A31" s="30"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="16"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="21"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="14" t="s">
+      <c r="A32" s="30"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="16"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="14" t="s">
+      <c r="A33" s="30"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="16"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="21"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="14" t="s">
+      <c r="A34" s="30"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="16"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="35">
+      <c r="A35" s="29">
         <v>46210</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13" t="s">
+      <c r="A36" s="29"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13" t="s">
+      <c r="A37" s="29"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
-      <c r="B38" s="13" t="s">
+      <c r="A38" s="29"/>
+      <c r="B38" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13" t="s">
+      <c r="A39" s="29"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="35"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13" t="s">
+      <c r="A40" s="29"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13" t="s">
+      <c r="A41" s="29"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="35"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13" t="s">
+      <c r="A42" s="29"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="35"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13" t="s">
+      <c r="A43" s="29"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="35"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14" t="s">
+      <c r="A44" s="29"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="16"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="21"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1654,13 +1664,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1669,255 +1679,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="32">
+      <c r="A47" s="24">
         <v>46213</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="16"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="21"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="33"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="14" t="s">
+      <c r="A48" s="28"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="16"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="21"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="33"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="14" t="s">
+      <c r="A49" s="28"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="16"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="21"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="33"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="14" t="s">
+      <c r="A50" s="28"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="16"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="21"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="34"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="14" t="s">
+      <c r="A51" s="25"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="16"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="12">
+      <c r="A52" s="18">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+      <c r="A53" s="18"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="12">
+      <c r="A54" s="18">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="16"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="21"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
-      <c r="B55" s="13" t="s">
+      <c r="A55" s="18"/>
+      <c r="B55" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="37" t="s">
+      <c r="C55" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="37" t="s">
+      <c r="A56" s="18"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="37" t="s">
+      <c r="A57" s="18"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="37" t="s">
+      <c r="A58" s="18"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="37" t="s">
+      <c r="A59" s="18"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="37" t="s">
+      <c r="A60" s="18"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="37" t="s">
+      <c r="A61" s="18"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="37" t="s">
+      <c r="A62" s="18"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="37" t="s">
+      <c r="A63" s="18"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="12">
+      <c r="A64" s="18">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
-      <c r="B65" s="13" t="s">
+      <c r="A65" s="18"/>
+      <c r="B65" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="12"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13" t="s">
+      <c r="A66" s="18"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1926,164 +1936,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="12">
+      <c r="A68" s="18">
         <v>46220</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="12"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13" t="s">
+      <c r="A69" s="18"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="12">
+      <c r="A70" s="18">
         <v>46223</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="16"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="21"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="12"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="14" t="s">
+      <c r="A71" s="18"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="16"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="21"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="12"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="14" t="s">
+      <c r="A72" s="18"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="16"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="21"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="12"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="14" t="s">
+      <c r="A73" s="18"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="16"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="21"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="12"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="14" t="s">
+      <c r="A74" s="18"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="16"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="21"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="12"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="14" t="s">
+      <c r="A75" s="18"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="15"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="16"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="21"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="12"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="14" t="s">
+      <c r="A76" s="18"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="16"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="21"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="12"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="9" t="s">
+      <c r="A77" s="18"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="11"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="12"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="9" t="s">
+      <c r="A78" s="18"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="11"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="12"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="9" t="s">
+      <c r="A79" s="18"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="11"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="12"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="9" t="s">
+      <c r="A80" s="18"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="11"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2092,335 +2102,350 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="12">
+      <c r="A82" s="18">
         <v>46225</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="12"/>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13" t="s">
+      <c r="A83" s="18"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="12"/>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13" t="s">
+      <c r="A84" s="18"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="12"/>
-      <c r="B85" s="13" t="s">
+      <c r="A85" s="18"/>
+      <c r="B85" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="12"/>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13" t="s">
+      <c r="A86" s="18"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="12"/>
-      <c r="B87" s="13"/>
-      <c r="C87" s="13" t="s">
+      <c r="A87" s="18"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="12"/>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13" t="s">
+      <c r="A88" s="18"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="12"/>
-      <c r="B89" s="13"/>
-      <c r="C89" s="14" t="s">
+      <c r="A89" s="18"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
-      <c r="G89" s="16"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="21"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="12"/>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13" t="s">
+      <c r="A90" s="18"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="32">
+      <c r="A91" s="24">
         <v>46227</v>
       </c>
-      <c r="B91" s="29" t="s">
+      <c r="B91" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="34"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="14" t="s">
+      <c r="A92" s="25"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="16"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="21"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="12">
+      <c r="A93" s="18">
         <v>46228</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="12"/>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13" t="s">
+      <c r="A94" s="18"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="12"/>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13" t="s">
+      <c r="A95" s="18"/>
+      <c r="B95" s="14"/>
+      <c r="C95" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="14"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="12"/>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13" t="s">
+      <c r="A96" s="18"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="12"/>
-      <c r="B97" s="13"/>
-      <c r="C97" s="13" t="s">
+      <c r="A97" s="18"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="12"/>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13" t="s">
+      <c r="A98" s="18"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="12">
-        <v>46200</v>
-      </c>
-      <c r="B99" s="13" t="s">
+      <c r="A99" s="18">
+        <v>46230</v>
+      </c>
+      <c r="B99" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="12"/>
-      <c r="B100" s="13"/>
-      <c r="C100" s="13" t="s">
+      <c r="A100" s="18"/>
+      <c r="B100" s="14"/>
+      <c r="C100" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="12">
-        <v>46201</v>
+      <c r="A101" s="18">
+        <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="22" t="s">
+      <c r="C101" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="22"/>
-      <c r="E101" s="22"/>
-      <c r="F101" s="22"/>
-      <c r="G101" s="22"/>
+      <c r="D101" s="37"/>
+      <c r="E101" s="37"/>
+      <c r="F101" s="37"/>
+      <c r="G101" s="37"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="12"/>
+      <c r="A102" s="18"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="22" t="s">
+      <c r="C102" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="22"/>
-      <c r="E102" s="22"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="22"/>
+      <c r="D102" s="37"/>
+      <c r="E102" s="37"/>
+      <c r="F102" s="37"/>
+      <c r="G102" s="37"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C104" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C105" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C106" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C107" t="s">
+        <v>107</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="B18:B19"/>
@@ -2445,54 +2470,70 @@
     <mergeCell ref="A20:A34"/>
     <mergeCell ref="B23:B34"/>
     <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086F5CE0-57A4-460A-B01B-9B280E6747E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E959D6-E8C4-4D33-ABB3-25000C43D38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -529,6 +529,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -545,78 +569,56 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -939,15 +941,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="9">
+      <c r="A1" s="17">
         <v>46174</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -956,146 +958,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="12">
         <v>46202</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14" t="s">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="12">
         <v>46203</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="21"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15" t="s">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15" t="s">
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15" t="s">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1105,14 +1107,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1123,6 +1117,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1140,15 +1142,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="31">
+      <c r="A1" s="23">
         <v>46204</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1157,152 +1159,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="12">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="34">
+      <c r="A7" s="26">
         <v>46205</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="21"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="35"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="15" t="s">
+      <c r="A8" s="27"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="35"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="15" t="s">
+      <c r="A9" s="27"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
-      <c r="B10" s="14" t="s">
+      <c r="A10" s="27"/>
+      <c r="B10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15" t="s">
+      <c r="A12" s="27"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="24">
+      <c r="A14" s="32">
         <v>46206</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="29" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1314,348 +1316,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="19" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="21"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="19" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="21"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="21"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="19" t="s">
+      <c r="A19" s="34"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="21"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="30">
+      <c r="A20" s="36">
         <v>46209</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="36"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14" t="s">
+      <c r="A22" s="36"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="14" t="s">
+      <c r="A23" s="36"/>
+      <c r="B23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="19" t="s">
+      <c r="A24" s="36"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="21"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="19" t="s">
+      <c r="A25" s="36"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="21"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="19" t="s">
+      <c r="A26" s="36"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="21"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="19" t="s">
+      <c r="A27" s="36"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="21"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="19" t="s">
+      <c r="A28" s="36"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="19" t="s">
+      <c r="A29" s="36"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="21"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="19" t="s">
+      <c r="A30" s="36"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="21"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="19" t="s">
+      <c r="A31" s="36"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="21"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="30"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="19" t="s">
+      <c r="A32" s="36"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="21"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="19" t="s">
+      <c r="A33" s="36"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="21"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="30"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="19" t="s">
+      <c r="A34" s="36"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="21"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="29">
+      <c r="A35" s="35">
         <v>46210</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="29"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="35"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="29"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14" t="s">
+      <c r="A37" s="35"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="29"/>
-      <c r="B38" s="14" t="s">
+      <c r="A38" s="35"/>
+      <c r="B38" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="29"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14" t="s">
+      <c r="A39" s="35"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="29"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14" t="s">
+      <c r="A40" s="35"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="29"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14" t="s">
+      <c r="A41" s="35"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="29"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14" t="s">
+      <c r="A42" s="35"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="29"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14" t="s">
+      <c r="A43" s="35"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="19" t="s">
+      <c r="A44" s="35"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="21"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1664,13 +1666,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1679,255 +1681,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="24">
+      <c r="A47" s="32">
         <v>46213</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="21"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="16"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="28"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="19" t="s">
+      <c r="A48" s="33"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="21"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="16"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="19" t="s">
+      <c r="A49" s="33"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="21"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="16"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="28"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="19" t="s">
+      <c r="A50" s="33"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="21"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="16"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="25"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="19" t="s">
+      <c r="A51" s="34"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="21"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="16"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="18">
+      <c r="A52" s="12">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="18"/>
+      <c r="A53" s="12"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="18">
+      <c r="A54" s="12">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="21"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="18"/>
-      <c r="B55" s="14" t="s">
+      <c r="A55" s="12"/>
+      <c r="B55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="26" t="s">
+      <c r="C55" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="37"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="18"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="26" t="s">
+      <c r="A56" s="12"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="26" t="s">
+      <c r="A57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="18"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="26" t="s">
+      <c r="A58" s="12"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="18"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="26" t="s">
+      <c r="A59" s="12"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="26" t="s">
+      <c r="A60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="18"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="26" t="s">
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="18"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="26" t="s">
+      <c r="A62" s="12"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="18"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="26" t="s">
+      <c r="A63" s="12"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="18">
+      <c r="A64" s="12">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="18"/>
-      <c r="B65" s="14" t="s">
+      <c r="A65" s="12"/>
+      <c r="B65" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="18"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14" t="s">
+      <c r="A66" s="12"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1936,164 +1938,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="18">
+      <c r="A68" s="12">
         <v>46220</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="18"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14" t="s">
+      <c r="A69" s="12"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="18">
+      <c r="A70" s="12">
         <v>46223</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C70" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="21"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="16"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="18"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="19" t="s">
+      <c r="A71" s="12"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="21"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="16"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="18"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="19" t="s">
+      <c r="A72" s="12"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="21"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="15"/>
+      <c r="G72" s="16"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="18"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="19" t="s">
+      <c r="A73" s="12"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="21"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="16"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="18"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="19" t="s">
+      <c r="A74" s="12"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="21"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="16"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="18"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="19" t="s">
+      <c r="A75" s="12"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="21"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="16"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="18"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="19" t="s">
+      <c r="A76" s="12"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="21"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="16"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="18"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="15" t="s">
+      <c r="A77" s="12"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="17"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="10"/>
+      <c r="G77" s="11"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="18"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="15" t="s">
+      <c r="A78" s="12"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="17"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="11"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="18"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="15" t="s">
+      <c r="A79" s="12"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="17"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="11"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="18"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="15" t="s">
+      <c r="A80" s="12"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="17"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="11"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2102,302 +2104,449 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="18">
+      <c r="A82" s="12">
         <v>46225</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="18"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14" t="s">
+      <c r="A83" s="12"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
+      <c r="G83" s="13"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="18"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14" t="s">
+      <c r="A84" s="12"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="18"/>
-      <c r="B85" s="14" t="s">
+      <c r="A85" s="12"/>
+      <c r="B85" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="14" t="s">
+      <c r="C85" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
+      <c r="D85" s="13"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
+      <c r="G85" s="13"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="18"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14" t="s">
+      <c r="A86" s="12"/>
+      <c r="B86" s="13"/>
+      <c r="C86" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
+      <c r="D86" s="13"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="18"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="14" t="s">
+      <c r="A87" s="12"/>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="18"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14" t="s">
+      <c r="A88" s="12"/>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
+      <c r="G88" s="13"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="18"/>
-      <c r="B89" s="14"/>
-      <c r="C89" s="19" t="s">
+      <c r="A89" s="12"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="20"/>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
-      <c r="G89" s="21"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="15"/>
+      <c r="G89" s="16"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="18"/>
-      <c r="B90" s="14"/>
-      <c r="C90" s="14" t="s">
+      <c r="A90" s="12"/>
+      <c r="B90" s="13"/>
+      <c r="C90" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
+      <c r="G90" s="13"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="24">
+      <c r="A91" s="32">
         <v>46227</v>
       </c>
-      <c r="B91" s="22" t="s">
+      <c r="B91" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="25"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="19" t="s">
+      <c r="A92" s="34"/>
+      <c r="B92" s="31"/>
+      <c r="C92" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="20"/>
-      <c r="E92" s="20"/>
-      <c r="F92" s="20"/>
-      <c r="G92" s="21"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="15"/>
+      <c r="G92" s="16"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="18">
+      <c r="A93" s="12">
         <v>46228</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="14"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="18"/>
-      <c r="B94" s="14"/>
-      <c r="C94" s="14" t="s">
+      <c r="A94" s="12"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="18"/>
-      <c r="B95" s="14"/>
-      <c r="C95" s="14" t="s">
+      <c r="A95" s="12"/>
+      <c r="B95" s="13"/>
+      <c r="C95" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="18"/>
-      <c r="B96" s="14"/>
-      <c r="C96" s="14" t="s">
+      <c r="A96" s="12"/>
+      <c r="B96" s="13"/>
+      <c r="C96" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14"/>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="18"/>
-      <c r="B97" s="14"/>
-      <c r="C97" s="14" t="s">
+      <c r="A97" s="12"/>
+      <c r="B97" s="13"/>
+      <c r="C97" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="14"/>
-      <c r="E97" s="14"/>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="18"/>
-      <c r="B98" s="14"/>
-      <c r="C98" s="14" t="s">
+      <c r="A98" s="12"/>
+      <c r="B98" s="13"/>
+      <c r="C98" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="18">
+      <c r="A99" s="12">
         <v>46230</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="B99" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="14" t="s">
+      <c r="C99" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="14"/>
-      <c r="E99" s="14"/>
-      <c r="F99" s="14"/>
-      <c r="G99" s="14"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="18"/>
-      <c r="B100" s="14"/>
-      <c r="C100" s="14" t="s">
+      <c r="A100" s="12"/>
+      <c r="B100" s="13"/>
+      <c r="C100" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="14"/>
-      <c r="E100" s="14"/>
-      <c r="F100" s="14"/>
-      <c r="G100" s="14"/>
+      <c r="D100" s="13"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
+      <c r="G100" s="13"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="18">
+      <c r="A101" s="12">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="37" t="s">
+      <c r="C101" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="37"/>
-      <c r="E101" s="37"/>
-      <c r="F101" s="37"/>
-      <c r="G101" s="37"/>
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="22"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="18"/>
+      <c r="A102" s="12"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="37" t="s">
+      <c r="C102" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="37"/>
-      <c r="E102" s="37"/>
-      <c r="F102" s="37"/>
-      <c r="G102" s="37"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="25" t="s">
         <v>106</v>
       </c>
+      <c r="D103" s="25"/>
+      <c r="E103" s="25"/>
+      <c r="F103" s="25"/>
+      <c r="G103" s="25"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C104" t="s">
+      <c r="A104" s="38"/>
+      <c r="B104" s="13"/>
+      <c r="C104" s="13" t="s">
         <v>86</v>
       </c>
+      <c r="D104" s="13"/>
+      <c r="E104" s="13"/>
+      <c r="F104" s="13"/>
+      <c r="G104" s="13"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C105" t="s">
+      <c r="A105" s="38"/>
+      <c r="B105" s="13"/>
+      <c r="C105" s="13" t="s">
         <v>60</v>
       </c>
+      <c r="D105" s="13"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="13"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C106" t="s">
+      <c r="A106" s="38"/>
+      <c r="B106" s="13"/>
+      <c r="C106" s="13" t="s">
         <v>50</v>
       </c>
+      <c r="D106" s="13"/>
+      <c r="E106" s="13"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="13"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C107" t="s">
+      <c r="A107" s="38"/>
+      <c r="B107" s="13"/>
+      <c r="C107" s="13" t="s">
         <v>107</v>
       </c>
+      <c r="D107" s="13"/>
+      <c r="E107" s="13"/>
+      <c r="F107" s="13"/>
+      <c r="G107" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="136">
+  <mergeCells count="143">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="C101:G101"/>
     <mergeCell ref="C102:G102"/>
     <mergeCell ref="A101:A102"/>
@@ -2422,118 +2571,6 @@
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E959D6-E8C4-4D33-ABB3-25000C43D38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1785F7-486A-4839-9926-A947979C8835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
     <sheet name="07-2026" sheetId="2" r:id="rId2"/>
+    <sheet name="08-2026" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'6-2026'!$A$2:$G$8</definedName>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -353,6 +354,9 @@
   </si>
   <si>
     <t>Nhận BH Tuyên Hằng</t>
+  </si>
+  <si>
+    <t>Nhận BH Dũng Thu</t>
   </si>
 </sst>
 </file>
@@ -529,6 +533,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -541,9 +563,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -553,71 +572,56 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -941,15 +945,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="17">
+      <c r="A1" s="9">
         <v>46174</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -958,146 +962,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="18">
         <v>46202</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="18">
         <v>46203</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="9" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="9" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="9" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1107,6 +1111,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1117,14 +1129,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1132,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1142,15 +1146,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="23">
+      <c r="A1" s="33">
         <v>46204</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1159,152 +1163,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="18">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="35">
         <v>46205</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="16"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="9" t="s">
+      <c r="A8" s="36"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="9" t="s">
+      <c r="A9" s="36"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="36"/>
+      <c r="B10" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="9" t="s">
+      <c r="A11" s="36"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="9" t="s">
+      <c r="A12" s="36"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="9" t="s">
+      <c r="A13" s="37"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="32">
+      <c r="A14" s="26">
         <v>46206</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="24" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1316,348 +1320,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="30"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="30"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="14" t="s">
+      <c r="A17" s="30"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="30"/>
+      <c r="B18" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="14" t="s">
+      <c r="A19" s="27"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="36">
+      <c r="A20" s="32">
         <v>46209</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="32"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="32"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="13" t="s">
+      <c r="A23" s="32"/>
+      <c r="B23" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14" t="s">
+      <c r="A24" s="32"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14" t="s">
+      <c r="A25" s="32"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14" t="s">
+      <c r="A26" s="32"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="21"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="14" t="s">
+      <c r="A27" s="32"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="14" t="s">
+      <c r="A28" s="32"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="14" t="s">
+      <c r="A29" s="32"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="16"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="14" t="s">
+      <c r="A30" s="32"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="16"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14" t="s">
+      <c r="A31" s="32"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="16"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="21"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="14" t="s">
+      <c r="A32" s="32"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="16"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="14" t="s">
+      <c r="A33" s="32"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="16"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="21"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="14" t="s">
+      <c r="A34" s="32"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="16"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="35">
+      <c r="A35" s="31">
         <v>46210</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13" t="s">
+      <c r="A36" s="31"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13" t="s">
+      <c r="A37" s="31"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
-      <c r="B38" s="13" t="s">
+      <c r="A38" s="31"/>
+      <c r="B38" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13" t="s">
+      <c r="A39" s="31"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="35"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13" t="s">
+      <c r="A40" s="31"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13" t="s">
+      <c r="A41" s="31"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="35"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13" t="s">
+      <c r="A42" s="31"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="35"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13" t="s">
+      <c r="A43" s="31"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="35"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14" t="s">
+      <c r="A44" s="31"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="16"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="21"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1666,13 +1670,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1681,255 +1685,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="32">
+      <c r="A47" s="26">
         <v>46213</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="16"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="21"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="33"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="14" t="s">
+      <c r="A48" s="30"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="16"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="21"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="33"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="14" t="s">
+      <c r="A49" s="30"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="16"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="21"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="33"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="14" t="s">
+      <c r="A50" s="30"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="16"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="21"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="34"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="14" t="s">
+      <c r="A51" s="27"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="16"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="12">
+      <c r="A52" s="18">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="12"/>
+      <c r="A53" s="18"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="12">
+      <c r="A54" s="18">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="16"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="21"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="12"/>
-      <c r="B55" s="13" t="s">
+      <c r="A55" s="18"/>
+      <c r="B55" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="37" t="s">
+      <c r="C55" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="37" t="s">
+      <c r="A56" s="18"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="12"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="37" t="s">
+      <c r="A57" s="18"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="37" t="s">
+      <c r="A58" s="18"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="37" t="s">
+      <c r="A59" s="18"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="37" t="s">
+      <c r="A60" s="18"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="37" t="s">
+      <c r="A61" s="18"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="37" t="s">
+      <c r="A62" s="18"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="37" t="s">
+      <c r="A63" s="18"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="12">
+      <c r="A64" s="18">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="12"/>
-      <c r="B65" s="13" t="s">
+      <c r="A65" s="18"/>
+      <c r="B65" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="12"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13" t="s">
+      <c r="A66" s="18"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -1938,164 +1942,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="12">
+      <c r="A68" s="18">
         <v>46220</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="12"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13" t="s">
+      <c r="A69" s="18"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="12">
+      <c r="A70" s="18">
         <v>46223</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="16"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="21"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="12"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="14" t="s">
+      <c r="A71" s="18"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="16"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="21"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="12"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="14" t="s">
+      <c r="A72" s="18"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="16"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="21"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="12"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="14" t="s">
+      <c r="A73" s="18"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="16"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="21"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="12"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="14" t="s">
+      <c r="A74" s="18"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="16"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="21"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="12"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="14" t="s">
+      <c r="A75" s="18"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="15"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="16"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="21"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="12"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="14" t="s">
+      <c r="A76" s="18"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="16"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="21"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="12"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="9" t="s">
+      <c r="A77" s="18"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="11"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="12"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="9" t="s">
+      <c r="A78" s="18"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="11"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="17"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="12"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="9" t="s">
+      <c r="A79" s="18"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="11"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="12"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="9" t="s">
+      <c r="A80" s="18"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="11"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2104,401 +2108,405 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="12">
+      <c r="A82" s="18">
         <v>46225</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="12"/>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13" t="s">
+      <c r="A83" s="18"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="12"/>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13" t="s">
+      <c r="A84" s="18"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="12"/>
-      <c r="B85" s="13" t="s">
+      <c r="A85" s="18"/>
+      <c r="B85" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="12"/>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13" t="s">
+      <c r="A86" s="18"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="12"/>
-      <c r="B87" s="13"/>
-      <c r="C87" s="13" t="s">
+      <c r="A87" s="18"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="12"/>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13" t="s">
+      <c r="A88" s="18"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="12"/>
-      <c r="B89" s="13"/>
-      <c r="C89" s="14" t="s">
+      <c r="A89" s="18"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="15"/>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
-      <c r="G89" s="16"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="21"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="12"/>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13" t="s">
+      <c r="A90" s="18"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="32">
+      <c r="A91" s="26">
         <v>46227</v>
       </c>
-      <c r="B91" s="29" t="s">
+      <c r="B91" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="34"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="14" t="s">
+      <c r="A92" s="27"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="16"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="21"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="12">
+      <c r="A93" s="18">
         <v>46228</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="12"/>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13" t="s">
+      <c r="A94" s="18"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="12"/>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13" t="s">
+      <c r="A95" s="18"/>
+      <c r="B95" s="14"/>
+      <c r="C95" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="14"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="12"/>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13" t="s">
+      <c r="A96" s="18"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="12"/>
-      <c r="B97" s="13"/>
-      <c r="C97" s="13" t="s">
+      <c r="A97" s="18"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="12"/>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13" t="s">
+      <c r="A98" s="18"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
+      <c r="D98" s="14"/>
+      <c r="E98" s="14"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="12">
+      <c r="A99" s="18">
         <v>46230</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="12"/>
-      <c r="B100" s="13"/>
-      <c r="C100" s="13" t="s">
+      <c r="A100" s="18"/>
+      <c r="B100" s="14"/>
+      <c r="C100" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
+      <c r="D100" s="14"/>
+      <c r="E100" s="14"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="12">
+      <c r="A101" s="18">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="22" t="s">
+      <c r="C101" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="22"/>
-      <c r="E101" s="22"/>
-      <c r="F101" s="22"/>
-      <c r="G101" s="22"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="12"/>
+      <c r="A102" s="18"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="22" t="s">
+      <c r="C102" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="22"/>
-      <c r="E102" s="22"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="22"/>
+      <c r="D102" s="38"/>
+      <c r="E102" s="38"/>
+      <c r="F102" s="38"/>
+      <c r="G102" s="38"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="38" t="s">
+      <c r="A103" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B103" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="25" t="s">
+      <c r="C103" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="25"/>
-      <c r="E103" s="25"/>
-      <c r="F103" s="25"/>
-      <c r="G103" s="25"/>
+      <c r="D103" s="23"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="23"/>
+      <c r="G103" s="23"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="38"/>
-      <c r="B104" s="13"/>
-      <c r="C104" s="13" t="s">
+      <c r="A104" s="22"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
-      <c r="G104" s="13"/>
+      <c r="D104" s="14"/>
+      <c r="E104" s="14"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="38"/>
-      <c r="B105" s="13"/>
-      <c r="C105" s="13" t="s">
+      <c r="A105" s="22"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="13"/>
-      <c r="E105" s="13"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="13"/>
+      <c r="D105" s="14"/>
+      <c r="E105" s="14"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="38"/>
-      <c r="B106" s="13"/>
-      <c r="C106" s="13" t="s">
+      <c r="A106" s="22"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="13"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="38"/>
-      <c r="B107" s="13"/>
-      <c r="C107" s="13" t="s">
+      <c r="A107" s="22"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="13"/>
-      <c r="G107" s="13"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="18">
+        <v>46234</v>
+      </c>
+      <c r="B108" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D108" s="14"/>
+      <c r="E108" s="14"/>
+      <c r="F108" s="14"/>
+      <c r="G108" s="14"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="18"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="143">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
+  <mergeCells count="147">
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="B18:B19"/>
@@ -2523,55 +2531,90 @@
     <mergeCell ref="A20:A34"/>
     <mergeCell ref="B23:B34"/>
     <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
     <mergeCell ref="C101:G101"/>
     <mergeCell ref="C102:G102"/>
     <mergeCell ref="A101:A102"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E5051E-34BB-454A-9E98-0A0156A4405B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1785F7-486A-4839-9926-A947979C8835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CC05D9-F32D-4096-BE78-4F775DDF80FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
   <sheets>
     <sheet name="6-2026" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="113">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -357,6 +357,18 @@
   </si>
   <si>
     <t>Nhận BH Dũng Thu</t>
+  </si>
+  <si>
+    <t>Trả BH Victroy</t>
+  </si>
+  <si>
+    <t>Trả BH  Nam Định</t>
+  </si>
+  <si>
+    <t>Trả  BH Tuyên Hằng</t>
+  </si>
+  <si>
+    <t>Trả BH SEA</t>
   </si>
 </sst>
 </file>
@@ -399,7 +411,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -505,11 +517,82 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -533,6 +616,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -548,81 +658,96 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,15 +1070,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="9">
+      <c r="A1" s="18">
         <v>46174</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -962,16 +1087,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="13">
         <v>46202</v>
       </c>
       <c r="B3" s="14" t="s">
@@ -986,7 +1111,7 @@
       <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14" t="s">
         <v>0</v>
@@ -997,7 +1122,7 @@
       <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="14"/>
       <c r="C5" s="14" t="s">
         <v>3</v>
@@ -1008,7 +1133,7 @@
       <c r="G5" s="14"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="14" t="s">
         <v>4</v>
       </c>
@@ -1021,7 +1146,7 @@
       <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14" t="s">
         <v>10</v>
@@ -1032,7 +1157,7 @@
       <c r="G7" s="14"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14" t="s">
         <v>9</v>
@@ -1043,65 +1168,65 @@
       <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="13">
         <v>46203</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="21"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="14"/>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="14"/>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="14"/>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1111,14 +1236,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1129,6 +1246,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1136,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B04270-3E3B-4748-8F06-1DEA88575B23}">
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1146,15 +1271,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="33">
+      <c r="A1" s="23">
         <v>46204</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1163,16 +1288,16 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="13">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1187,20 +1312,20 @@
       <c r="G3" s="14"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="14"/>
       <c r="C5" s="14" t="s">
         <v>17</v>
@@ -1211,7 +1336,7 @@
       <c r="G5" s="14"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="14"/>
       <c r="C6" s="14" t="s">
         <v>18</v>
@@ -1222,93 +1347,93 @@
       <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="35">
+      <c r="A7" s="26">
         <v>46205</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="21"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="15" t="s">
+      <c r="A8" s="27"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="36"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="15" t="s">
+      <c r="A9" s="27"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="17"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="14"/>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="14"/>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="17"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="14"/>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="17"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+      <c r="A14" s="32">
         <v>46206</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="29" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1320,64 +1445,64 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="19" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="30"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="21"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="19" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="21"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="21"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="19" t="s">
+      <c r="A19" s="34"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="21"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="32">
+      <c r="A20" s="36">
         <v>46209</v>
       </c>
       <c r="B20" s="14" t="s">
@@ -1392,7 +1517,7 @@
       <c r="G20" s="14"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="32"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14" t="s">
         <v>34</v>
@@ -1403,7 +1528,7 @@
       <c r="G21" s="14"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="32"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14" t="s">
         <v>15</v>
@@ -1414,7 +1539,7 @@
       <c r="G22" s="14"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="32"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="14" t="s">
         <v>4</v>
       </c>
@@ -1427,128 +1552,128 @@
       <c r="G23" s="14"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="32"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="14"/>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="21"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="32"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="14"/>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="21"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="32"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="14"/>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="21"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="32"/>
+      <c r="A27" s="36"/>
       <c r="B27" s="14"/>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="21"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="32"/>
+      <c r="A28" s="36"/>
       <c r="B28" s="14"/>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="32"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="14"/>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="21"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="32"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="14"/>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="21"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="32"/>
+      <c r="A31" s="36"/>
       <c r="B31" s="14"/>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="21"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="32"/>
+      <c r="A32" s="36"/>
       <c r="B32" s="14"/>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="21"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="32"/>
+      <c r="A33" s="36"/>
       <c r="B33" s="14"/>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="21"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="32"/>
+      <c r="A34" s="36"/>
       <c r="B34" s="14"/>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="21"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="31">
+      <c r="A35" s="35">
         <v>46210</v>
       </c>
       <c r="B35" s="14" t="s">
@@ -1563,7 +1688,7 @@
       <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="31"/>
+      <c r="A36" s="35"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14" t="s">
         <v>27</v>
@@ -1574,7 +1699,7 @@
       <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="31"/>
+      <c r="A37" s="35"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14" t="s">
         <v>47</v>
@@ -1585,7 +1710,7 @@
       <c r="G37" s="14"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="31"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="14" t="s">
         <v>4</v>
       </c>
@@ -1598,7 +1723,7 @@
       <c r="G38" s="14"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="31"/>
+      <c r="A39" s="35"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14" t="s">
         <v>53</v>
@@ -1609,7 +1734,7 @@
       <c r="G39" s="14"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="31"/>
+      <c r="A40" s="35"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14" t="s">
         <v>48</v>
@@ -1620,7 +1745,7 @@
       <c r="G40" s="14"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="31"/>
+      <c r="A41" s="35"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14" t="s">
         <v>49</v>
@@ -1631,7 +1756,7 @@
       <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="31"/>
+      <c r="A42" s="35"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14" t="s">
         <v>50</v>
@@ -1642,7 +1767,7 @@
       <c r="G42" s="14"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="31"/>
+      <c r="A43" s="35"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14" t="s">
         <v>51</v>
@@ -1653,15 +1778,15 @@
       <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="31"/>
+      <c r="A44" s="35"/>
       <c r="B44" s="14"/>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="21"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1694,66 +1819,66 @@
       <c r="G46" s="14"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="26">
+      <c r="A47" s="32">
         <v>46213</v>
       </c>
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="21"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="30"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="19" t="s">
+      <c r="A48" s="33"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="21"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="30"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="19" t="s">
+      <c r="A49" s="33"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="21"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="30"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="19" t="s">
+      <c r="A50" s="33"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="21"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="19" t="s">
+      <c r="A51" s="34"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="21"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="18">
+      <c r="A52" s="13">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -1768,7 +1893,7 @@
       <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="18"/>
+      <c r="A53" s="13"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
@@ -1781,123 +1906,123 @@
       <c r="G53" s="14"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="18">
+      <c r="A54" s="13">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="21"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="17"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="18"/>
+      <c r="A55" s="13"/>
       <c r="B55" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="C55" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="37"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="18"/>
+      <c r="A56" s="13"/>
       <c r="B56" s="14"/>
-      <c r="C56" s="28" t="s">
+      <c r="C56" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
+      <c r="A57" s="13"/>
       <c r="B57" s="14"/>
-      <c r="C57" s="28" t="s">
+      <c r="C57" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="18"/>
+      <c r="A58" s="13"/>
       <c r="B58" s="14"/>
-      <c r="C58" s="28" t="s">
+      <c r="C58" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="18"/>
+      <c r="A59" s="13"/>
       <c r="B59" s="14"/>
-      <c r="C59" s="28" t="s">
+      <c r="C59" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
+      <c r="A60" s="13"/>
       <c r="B60" s="14"/>
-      <c r="C60" s="28" t="s">
+      <c r="C60" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="18"/>
+      <c r="A61" s="13"/>
       <c r="B61" s="14"/>
-      <c r="C61" s="28" t="s">
+      <c r="C61" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="18"/>
+      <c r="A62" s="13"/>
       <c r="B62" s="14"/>
-      <c r="C62" s="28" t="s">
+      <c r="C62" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="28"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="18"/>
+      <c r="A63" s="13"/>
       <c r="B63" s="14"/>
-      <c r="C63" s="28" t="s">
+      <c r="C63" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="18">
+      <c r="A64" s="13">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -1912,7 +2037,7 @@
       <c r="G64" s="14"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="18"/>
+      <c r="A65" s="13"/>
       <c r="B65" s="14" t="s">
         <v>4</v>
       </c>
@@ -1925,7 +2050,7 @@
       <c r="G65" s="14"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="18"/>
+      <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14" t="s">
         <v>74</v>
@@ -1951,7 +2076,7 @@
       <c r="G67" s="14"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="18">
+      <c r="A68" s="13">
         <v>46220</v>
       </c>
       <c r="B68" s="14" t="s">
@@ -1966,7 +2091,7 @@
       <c r="G68" s="14"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="18"/>
+      <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14" t="s">
         <v>77</v>
@@ -1977,129 +2102,129 @@
       <c r="G69" s="14"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="18">
+      <c r="A70" s="13">
         <v>46223</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C70" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="21"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="18"/>
+      <c r="A71" s="13"/>
       <c r="B71" s="14"/>
-      <c r="C71" s="19" t="s">
+      <c r="C71" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="21"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="17"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="18"/>
+      <c r="A72" s="13"/>
       <c r="B72" s="14"/>
-      <c r="C72" s="19" t="s">
+      <c r="C72" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="21"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="18"/>
+      <c r="A73" s="13"/>
       <c r="B73" s="14"/>
-      <c r="C73" s="19" t="s">
+      <c r="C73" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="21"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="17"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="18"/>
+      <c r="A74" s="13"/>
       <c r="B74" s="14"/>
-      <c r="C74" s="19" t="s">
+      <c r="C74" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="21"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="18"/>
+      <c r="A75" s="13"/>
       <c r="B75" s="14"/>
-      <c r="C75" s="19" t="s">
+      <c r="C75" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="21"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="18"/>
+      <c r="A76" s="13"/>
       <c r="B76" s="14"/>
-      <c r="C76" s="19" t="s">
+      <c r="C76" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="21"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="18"/>
+      <c r="A77" s="13"/>
       <c r="B77" s="14"/>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="17"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="12"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="18"/>
+      <c r="A78" s="13"/>
       <c r="B78" s="14"/>
-      <c r="C78" s="15" t="s">
+      <c r="C78" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="17"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="12"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="18"/>
+      <c r="A79" s="13"/>
       <c r="B79" s="14"/>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="17"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="12"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="18"/>
+      <c r="A80" s="13"/>
       <c r="B80" s="14"/>
-      <c r="C80" s="15" t="s">
+      <c r="C80" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="17"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="12"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2117,7 +2242,7 @@
       <c r="G81" s="14"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="18">
+      <c r="A82" s="13">
         <v>46225</v>
       </c>
       <c r="B82" s="14" t="s">
@@ -2132,7 +2257,7 @@
       <c r="G82" s="14"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="18"/>
+      <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14" t="s">
         <v>90</v>
@@ -2143,7 +2268,7 @@
       <c r="G83" s="14"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="18"/>
+      <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14" t="s">
         <v>93</v>
@@ -2154,7 +2279,7 @@
       <c r="G84" s="14"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="18"/>
+      <c r="A85" s="13"/>
       <c r="B85" s="14" t="s">
         <v>4</v>
       </c>
@@ -2167,7 +2292,7 @@
       <c r="G85" s="14"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="18"/>
+      <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14" t="s">
         <v>72</v>
@@ -2178,7 +2303,7 @@
       <c r="G86" s="14"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="18"/>
+      <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14" t="s">
         <v>89</v>
@@ -2189,7 +2314,7 @@
       <c r="G87" s="14"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="18"/>
+      <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14" t="s">
         <v>35</v>
@@ -2200,18 +2325,18 @@
       <c r="G88" s="14"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="18"/>
+      <c r="A89" s="13"/>
       <c r="B89" s="14"/>
-      <c r="C89" s="19" t="s">
+      <c r="C89" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="20"/>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
-      <c r="G89" s="21"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="17"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="18"/>
+      <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14" t="s">
         <v>92</v>
@@ -2222,10 +2347,10 @@
       <c r="G90" s="14"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="26">
+      <c r="A91" s="32">
         <v>46227</v>
       </c>
-      <c r="B91" s="24" t="s">
+      <c r="B91" s="29" t="s">
         <v>5</v>
       </c>
       <c r="C91" s="14" t="s">
@@ -2237,18 +2362,18 @@
       <c r="G91" s="14"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="27"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="19" t="s">
+      <c r="A92" s="34"/>
+      <c r="B92" s="31"/>
+      <c r="C92" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="20"/>
-      <c r="E92" s="20"/>
-      <c r="F92" s="20"/>
-      <c r="G92" s="21"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="17"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="18">
+      <c r="A93" s="13">
         <v>46228</v>
       </c>
       <c r="B93" s="14" t="s">
@@ -2263,7 +2388,7 @@
       <c r="G93" s="14"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="18"/>
+      <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14" t="s">
         <v>97</v>
@@ -2274,7 +2399,7 @@
       <c r="G94" s="14"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="18"/>
+      <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14" t="s">
         <v>98</v>
@@ -2285,7 +2410,7 @@
       <c r="G95" s="14"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="18"/>
+      <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14" t="s">
         <v>99</v>
@@ -2296,7 +2421,7 @@
       <c r="G96" s="14"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="18"/>
+      <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14" t="s">
         <v>100</v>
@@ -2307,7 +2432,7 @@
       <c r="G97" s="14"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="18"/>
+      <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14" t="s">
         <v>101</v>
@@ -2318,7 +2443,7 @@
       <c r="G98" s="14"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="18">
+      <c r="A99" s="13">
         <v>46230</v>
       </c>
       <c r="B99" s="14" t="s">
@@ -2333,7 +2458,7 @@
       <c r="G99" s="14"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="18"/>
+      <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14" t="s">
         <v>39</v>
@@ -2344,50 +2469,50 @@
       <c r="G100" s="14"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="18">
+      <c r="A101" s="13">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="38" t="s">
+      <c r="C101" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="38"/>
-      <c r="E101" s="38"/>
-      <c r="F101" s="38"/>
-      <c r="G101" s="38"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="39"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="39"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="18"/>
+      <c r="A102" s="13"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="38" t="s">
+      <c r="C102" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="38"/>
-      <c r="E102" s="38"/>
-      <c r="F102" s="38"/>
-      <c r="G102" s="38"/>
+      <c r="D102" s="39"/>
+      <c r="E102" s="39"/>
+      <c r="F102" s="39"/>
+      <c r="G102" s="39"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="22" t="s">
+      <c r="A103" s="38" t="s">
         <v>105</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="23" t="s">
+      <c r="C103" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="23"/>
-      <c r="E103" s="23"/>
-      <c r="F103" s="23"/>
-      <c r="G103" s="23"/>
+      <c r="D103" s="25"/>
+      <c r="E103" s="25"/>
+      <c r="F103" s="25"/>
+      <c r="G103" s="25"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="22"/>
+      <c r="A104" s="38"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14" t="s">
         <v>86</v>
@@ -2398,7 +2523,7 @@
       <c r="G104" s="14"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="22"/>
+      <c r="A105" s="38"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14" t="s">
         <v>60</v>
@@ -2409,7 +2534,7 @@
       <c r="G105" s="14"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="22"/>
+      <c r="A106" s="38"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14" t="s">
         <v>50</v>
@@ -2420,7 +2545,7 @@
       <c r="G106" s="14"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="22"/>
+      <c r="A107" s="38"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14" t="s">
         <v>107</v>
@@ -2431,7 +2556,7 @@
       <c r="G107" s="14"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="18">
+      <c r="A108" s="13">
         <v>46234</v>
       </c>
       <c r="B108" s="14" t="s">
@@ -2446,7 +2571,7 @@
       <c r="G108" s="14"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="18"/>
+      <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14" t="s">
         <v>39</v>
@@ -2456,8 +2581,137 @@
       <c r="F109" s="14"/>
       <c r="G109" s="14"/>
     </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D110" s="40"/>
+      <c r="E110" s="40"/>
+      <c r="F110" s="40"/>
+      <c r="G110" s="40"/>
+    </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2482,129 +2736,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2612,9 +2743,105 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E5051E-34BB-454A-9E98-0A0156A4405B}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="23">
+        <v>46235</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="46">
+        <v>46237</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="49"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="50"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="50"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="52"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="50"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="52"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="A3:A7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CC05D9-F32D-4096-BE78-4F775DDF80FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B6D8B2-7640-4F67-899E-A13905536E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="116">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -369,6 +369,15 @@
   </si>
   <si>
     <t>Trả BH SEA</t>
+  </si>
+  <si>
+    <t>Trả BH Hải Yến</t>
+  </si>
+  <si>
+    <t>Nhận BH SEA</t>
+  </si>
+  <si>
+    <t>Nhận BH A. Tuấn NB</t>
   </si>
 </sst>
 </file>
@@ -592,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -619,6 +628,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -658,6 +679,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -676,14 +706,8 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -695,9 +719,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -709,45 +730,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,15 +1101,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="18">
+      <c r="A1" s="22">
         <v>46174</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1087,146 +1118,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="22"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+      <c r="A3" s="17">
         <v>46202</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
+      <c r="A9" s="17">
         <v>46203</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="17"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="21"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="10" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="10" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="10" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1271,15 +1302,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="23">
+      <c r="A1" s="30">
         <v>46204</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1288,152 +1319,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+      <c r="A3" s="17">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26">
+      <c r="A7" s="33">
         <v>46205</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="17"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="10" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="27"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="10" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="14" t="s">
+      <c r="A10" s="34"/>
+      <c r="B10" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="27"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="10" t="s">
+      <c r="A11" s="34"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="27"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="10" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="10" t="s">
+      <c r="A13" s="35"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="32">
+      <c r="A14" s="37">
         <v>46206</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="27" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1445,348 +1476,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="15" t="s">
+      <c r="A15" s="38"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="17"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="21"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="15" t="s">
+      <c r="A16" s="38"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="17"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="21"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="15" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="38"/>
+      <c r="B18" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="17"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="21"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="15" t="s">
+      <c r="A19" s="39"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="17"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="36">
+      <c r="A20" s="40">
         <v>46209</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="40"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14" t="s">
+      <c r="A22" s="40"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="36"/>
-      <c r="B23" s="14" t="s">
+      <c r="A23" s="40"/>
+      <c r="B23" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="36"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="15" t="s">
+      <c r="A24" s="40"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="17"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="21"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="15" t="s">
+      <c r="A25" s="40"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="15" t="s">
+      <c r="A26" s="40"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="21"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="15" t="s">
+      <c r="A27" s="40"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="17"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="21"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="15" t="s">
+      <c r="A28" s="40"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="17"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="36"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="15" t="s">
+      <c r="A29" s="40"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="15" t="s">
+      <c r="A30" s="40"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="17"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="36"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15" t="s">
+      <c r="A31" s="40"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="17"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="21"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="15" t="s">
+      <c r="A32" s="40"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="17"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="15" t="s">
+      <c r="A33" s="40"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="17"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="21"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15" t="s">
+      <c r="A34" s="40"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="17"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="35">
+      <c r="A35" s="36">
         <v>46210</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="35"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="36"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14" t="s">
+      <c r="A37" s="36"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="35"/>
-      <c r="B38" s="14" t="s">
+      <c r="A38" s="36"/>
+      <c r="B38" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14" t="s">
+      <c r="A39" s="36"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="35"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14" t="s">
+      <c r="A40" s="36"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14" t="s">
+      <c r="A41" s="36"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="35"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14" t="s">
+      <c r="A42" s="36"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="35"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14" t="s">
+      <c r="A43" s="36"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="35"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="15" t="s">
+      <c r="A44" s="36"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="17"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="21"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1795,13 +1826,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1810,255 +1841,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="32">
+      <c r="A47" s="37">
         <v>46213</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="17"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="21"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="33"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="15" t="s">
+      <c r="A48" s="38"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="17"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="21"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="33"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="15" t="s">
+      <c r="A49" s="38"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="17"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="21"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="33"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="15" t="s">
+      <c r="A50" s="38"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="17"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="21"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="34"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="15" t="s">
+      <c r="A51" s="39"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="17"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="13">
+      <c r="A52" s="17">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="13"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="13">
+      <c r="A54" s="17">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="17"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="21"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14" t="s">
+      <c r="A55" s="17"/>
+      <c r="B55" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="37" t="s">
+      <c r="C55" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="37" t="s">
+      <c r="A56" s="17"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="37" t="s">
+      <c r="A57" s="17"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="37" t="s">
+      <c r="A58" s="17"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="37" t="s">
+      <c r="A59" s="17"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="41"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="37" t="s">
+      <c r="A60" s="17"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="41"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="37" t="s">
+      <c r="A61" s="17"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="41"/>
+      <c r="G61" s="41"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="37" t="s">
+      <c r="A62" s="17"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="37" t="s">
+      <c r="A63" s="17"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="13">
+      <c r="A64" s="17">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14" t="s">
+      <c r="A65" s="17"/>
+      <c r="B65" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14" t="s">
+      <c r="A66" s="17"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2067,164 +2098,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="13">
+      <c r="A68" s="17">
         <v>46220</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14" t="s">
+      <c r="A69" s="17"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="13">
+      <c r="A70" s="17">
         <v>46223</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="17"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="21"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="15" t="s">
+      <c r="A71" s="17"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="17"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="21"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="15" t="s">
+      <c r="A72" s="17"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="17"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="21"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="15" t="s">
+      <c r="A73" s="17"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="17"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="21"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="15" t="s">
+      <c r="A74" s="17"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="17"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="21"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="15" t="s">
+      <c r="A75" s="17"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="17"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="21"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="15" t="s">
+      <c r="A76" s="17"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="17"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="21"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="10" t="s">
+      <c r="A77" s="17"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="12"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="16"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="10" t="s">
+      <c r="A78" s="17"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="12"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="16"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="10" t="s">
+      <c r="A79" s="17"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="12"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="16"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="10" t="s">
+      <c r="A80" s="17"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="12"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="16"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2233,359 +2264,359 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="18"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="13">
+      <c r="A82" s="17">
         <v>46225</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14" t="s">
+      <c r="A83" s="17"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14" t="s">
+      <c r="A84" s="17"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14" t="s">
+      <c r="A85" s="17"/>
+      <c r="B85" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="14" t="s">
+      <c r="C85" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="18"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="14" t="s">
+      <c r="A86" s="17"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="18"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="14" t="s">
+      <c r="A87" s="17"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="18"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="14" t="s">
+      <c r="A88" s="17"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="18"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="13"/>
-      <c r="B89" s="14"/>
-      <c r="C89" s="15" t="s">
+      <c r="A89" s="17"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="17"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="21"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="13"/>
-      <c r="B90" s="14"/>
-      <c r="C90" s="14" t="s">
+      <c r="A90" s="17"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
+      <c r="D90" s="18"/>
+      <c r="E90" s="18"/>
+      <c r="F90" s="18"/>
+      <c r="G90" s="18"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="32">
+      <c r="A91" s="37">
         <v>46227</v>
       </c>
-      <c r="B91" s="29" t="s">
+      <c r="B91" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="18"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="34"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="15" t="s">
+      <c r="A92" s="39"/>
+      <c r="B92" s="28"/>
+      <c r="C92" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="16"/>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="17"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="21"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="13">
+      <c r="A93" s="17">
         <v>46228</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="14"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="18"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="13"/>
-      <c r="B94" s="14"/>
-      <c r="C94" s="14" t="s">
+      <c r="A94" s="17"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="18"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="13"/>
-      <c r="B95" s="14"/>
-      <c r="C95" s="14" t="s">
+      <c r="A95" s="17"/>
+      <c r="B95" s="18"/>
+      <c r="C95" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
+      <c r="D95" s="18"/>
+      <c r="E95" s="18"/>
+      <c r="F95" s="18"/>
+      <c r="G95" s="18"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="13"/>
-      <c r="B96" s="14"/>
-      <c r="C96" s="14" t="s">
+      <c r="A96" s="17"/>
+      <c r="B96" s="18"/>
+      <c r="C96" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14"/>
+      <c r="D96" s="18"/>
+      <c r="E96" s="18"/>
+      <c r="F96" s="18"/>
+      <c r="G96" s="18"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="13"/>
-      <c r="B97" s="14"/>
-      <c r="C97" s="14" t="s">
+      <c r="A97" s="17"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="14"/>
-      <c r="E97" s="14"/>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="18"/>
+      <c r="F97" s="18"/>
+      <c r="G97" s="18"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="13"/>
-      <c r="B98" s="14"/>
-      <c r="C98" s="14" t="s">
+      <c r="A98" s="17"/>
+      <c r="B98" s="18"/>
+      <c r="C98" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
+      <c r="D98" s="18"/>
+      <c r="E98" s="18"/>
+      <c r="F98" s="18"/>
+      <c r="G98" s="18"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="13">
+      <c r="A99" s="17">
         <v>46230</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="B99" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="14" t="s">
+      <c r="C99" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="14"/>
-      <c r="E99" s="14"/>
-      <c r="F99" s="14"/>
-      <c r="G99" s="14"/>
+      <c r="D99" s="18"/>
+      <c r="E99" s="18"/>
+      <c r="F99" s="18"/>
+      <c r="G99" s="18"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="13"/>
-      <c r="B100" s="14"/>
-      <c r="C100" s="14" t="s">
+      <c r="A100" s="17"/>
+      <c r="B100" s="18"/>
+      <c r="C100" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="14"/>
-      <c r="E100" s="14"/>
-      <c r="F100" s="14"/>
-      <c r="G100" s="14"/>
+      <c r="D100" s="18"/>
+      <c r="E100" s="18"/>
+      <c r="F100" s="18"/>
+      <c r="G100" s="18"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="13">
+      <c r="A101" s="17">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="39" t="s">
+      <c r="C101" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="39"/>
-      <c r="E101" s="39"/>
-      <c r="F101" s="39"/>
-      <c r="G101" s="39"/>
+      <c r="D101" s="43"/>
+      <c r="E101" s="43"/>
+      <c r="F101" s="43"/>
+      <c r="G101" s="43"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="13"/>
+      <c r="A102" s="17"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="39" t="s">
+      <c r="C102" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="39"/>
-      <c r="E102" s="39"/>
-      <c r="F102" s="39"/>
-      <c r="G102" s="39"/>
+      <c r="D102" s="43"/>
+      <c r="E102" s="43"/>
+      <c r="F102" s="43"/>
+      <c r="G102" s="43"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="38" t="s">
+      <c r="A103" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="25" t="s">
+      <c r="C103" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="25"/>
-      <c r="E103" s="25"/>
-      <c r="F103" s="25"/>
-      <c r="G103" s="25"/>
+      <c r="D103" s="32"/>
+      <c r="E103" s="32"/>
+      <c r="F103" s="32"/>
+      <c r="G103" s="32"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="38"/>
-      <c r="B104" s="14"/>
-      <c r="C104" s="14" t="s">
+      <c r="A104" s="42"/>
+      <c r="B104" s="18"/>
+      <c r="C104" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="14"/>
-      <c r="E104" s="14"/>
-      <c r="F104" s="14"/>
-      <c r="G104" s="14"/>
+      <c r="D104" s="18"/>
+      <c r="E104" s="18"/>
+      <c r="F104" s="18"/>
+      <c r="G104" s="18"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="38"/>
-      <c r="B105" s="14"/>
-      <c r="C105" s="14" t="s">
+      <c r="A105" s="42"/>
+      <c r="B105" s="18"/>
+      <c r="C105" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="14"/>
-      <c r="E105" s="14"/>
-      <c r="F105" s="14"/>
-      <c r="G105" s="14"/>
+      <c r="D105" s="18"/>
+      <c r="E105" s="18"/>
+      <c r="F105" s="18"/>
+      <c r="G105" s="18"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="38"/>
-      <c r="B106" s="14"/>
-      <c r="C106" s="14" t="s">
+      <c r="A106" s="42"/>
+      <c r="B106" s="18"/>
+      <c r="C106" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
+      <c r="D106" s="18"/>
+      <c r="E106" s="18"/>
+      <c r="F106" s="18"/>
+      <c r="G106" s="18"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="38"/>
-      <c r="B107" s="14"/>
-      <c r="C107" s="14" t="s">
+      <c r="A107" s="42"/>
+      <c r="B107" s="18"/>
+      <c r="C107" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="14"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="14"/>
-      <c r="G107" s="14"/>
+      <c r="D107" s="18"/>
+      <c r="E107" s="18"/>
+      <c r="F107" s="18"/>
+      <c r="G107" s="18"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="13">
+      <c r="A108" s="17">
         <v>46234</v>
       </c>
-      <c r="B108" s="14" t="s">
+      <c r="B108" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C108" s="14" t="s">
+      <c r="C108" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="14"/>
-      <c r="E108" s="14"/>
-      <c r="F108" s="14"/>
-      <c r="G108" s="14"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="13"/>
-      <c r="B109" s="14"/>
-      <c r="C109" s="14" t="s">
+      <c r="A109" s="17"/>
+      <c r="B109" s="18"/>
+      <c r="C109" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="14"/>
-      <c r="E109" s="14"/>
-      <c r="F109" s="14"/>
-      <c r="G109" s="14"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D110" s="40"/>
-      <c r="E110" s="40"/>
-      <c r="F110" s="40"/>
-      <c r="G110" s="40"/>
+      <c r="D110" s="10"/>
+      <c r="E110" s="10"/>
+      <c r="F110" s="10"/>
+      <c r="G110" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="147">
@@ -2743,24 +2774,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E5051E-34BB-454A-9E98-0A0156A4405B}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="44"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="23">
+      <c r="A1" s="30">
         <v>46235</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2769,78 +2801,124 @@
       <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="59"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="46">
+      <c r="A3" s="11">
         <v>46237</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="49"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="51" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="50"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="50"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="51" t="s">
+      <c r="A5" s="13"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="52"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="50"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="50"/>
-      <c r="B6" s="41"/>
-      <c r="C6" s="51" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="52"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="55" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="56"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="53"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="45">
+        <v>46238</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="47"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="50"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="48"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="50"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="A3:A7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B6D8B2-7640-4F67-899E-A13905536E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC018119-A3EF-4DB2-92FE-BDD5ADB72B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="117">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>Nhận BH A. Tuấn NB</t>
+  </si>
+  <si>
+    <t>Nhận BH GPS Global</t>
   </si>
 </sst>
 </file>
@@ -601,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -640,96 +643,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -743,7 +656,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -779,6 +692,99 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1101,15 +1107,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="22">
+      <c r="A1" s="31">
         <v>46174</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1118,146 +1124,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="40">
         <v>46202</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18" t="s">
+      <c r="A5" s="40"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="40"/>
+      <c r="B6" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18" t="s">
+      <c r="A7" s="40"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18" t="s">
+      <c r="A8" s="40"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="17">
+      <c r="A9" s="40">
         <v>46203</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="21"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="43"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="40"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="39"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="40"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="39"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="40"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="39"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="39"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1267,6 +1273,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1277,14 +1291,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1302,15 +1308,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="30">
+      <c r="A1" s="56">
         <v>46204</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1319,152 +1325,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+      <c r="A3" s="40">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="40"/>
+      <c r="B4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18" t="s">
+      <c r="A5" s="40"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18" t="s">
+      <c r="A6" s="40"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="33">
+      <c r="A7" s="58">
         <v>46205</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="21"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="43"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="59"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="39"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="59"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="39"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="18" t="s">
+      <c r="A10" s="59"/>
+      <c r="B10" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="39"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="59"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="39"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="59"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="39"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="60"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="39"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="37">
+      <c r="A14" s="49">
         <v>46206</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="47" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1476,348 +1482,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="38"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="19" t="s">
+      <c r="A15" s="52"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="38"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="52"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="21"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="38"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="19" t="s">
+      <c r="A17" s="52"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="21"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="43"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="38"/>
-      <c r="B18" s="27" t="s">
+      <c r="A18" s="52"/>
+      <c r="B18" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="21"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="43"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="39"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="19" t="s">
+      <c r="A19" s="50"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="21"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="43"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="40">
+      <c r="A20" s="53">
         <v>46209</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="40"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18" t="s">
+      <c r="A21" s="53"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="40"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18" t="s">
+      <c r="A22" s="53"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="40"/>
-      <c r="B23" s="18" t="s">
+      <c r="A23" s="53"/>
+      <c r="B23" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="40"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="19" t="s">
+      <c r="A24" s="53"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="21"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="43"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="40"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="19" t="s">
+      <c r="A25" s="53"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="21"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="40"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="19" t="s">
+      <c r="A26" s="53"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="21"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="43"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="40"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="19" t="s">
+      <c r="A27" s="53"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="21"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="43"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="40"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="19" t="s">
+      <c r="A28" s="53"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="21"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="43"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="40"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="19" t="s">
+      <c r="A29" s="53"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="21"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="43"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="40"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="19" t="s">
+      <c r="A30" s="53"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="21"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="40"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="19" t="s">
+      <c r="A31" s="53"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="21"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="43"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="40"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="19" t="s">
+      <c r="A32" s="53"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="21"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="43"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="40"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="19" t="s">
+      <c r="A33" s="53"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="21"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="43"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="40"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="19" t="s">
+      <c r="A34" s="53"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="21"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="43"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="36">
+      <c r="A35" s="51">
         <v>46210</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="36"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18" t="s">
+      <c r="A36" s="51"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="36"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18" t="s">
+      <c r="A37" s="51"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="36"/>
-      <c r="B38" s="18" t="s">
+      <c r="A38" s="51"/>
+      <c r="B38" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="36"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18" t="s">
+      <c r="A39" s="51"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="36"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18" t="s">
+      <c r="A40" s="51"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18" t="s">
+      <c r="A41" s="51"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="36"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18" t="s">
+      <c r="A42" s="51"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="36"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18" t="s">
+      <c r="A43" s="51"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="36"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19" t="s">
+      <c r="A44" s="51"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="21"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="43"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1826,13 +1832,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1841,255 +1847,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="37">
+      <c r="A47" s="49">
         <v>46213</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="21"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="43"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="38"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="19" t="s">
+      <c r="A48" s="52"/>
+      <c r="B48" s="55"/>
+      <c r="C48" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="21"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="43"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="38"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="19" t="s">
+      <c r="A49" s="52"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="21"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="43"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="38"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="19" t="s">
+      <c r="A50" s="52"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="21"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="43"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="39"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="19" t="s">
+      <c r="A51" s="50"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="21"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="43"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
+      <c r="A52" s="40">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
+      <c r="A53" s="40"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="17">
+      <c r="A54" s="40">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="21"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="43"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="18" t="s">
+      <c r="A55" s="40"/>
+      <c r="B55" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="41" t="s">
+      <c r="C55" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="41" t="s">
+      <c r="A56" s="40"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="41" t="s">
+      <c r="A57" s="40"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="17"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="41" t="s">
+      <c r="A58" s="40"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="17"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="41" t="s">
+      <c r="A59" s="40"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="17"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="41" t="s">
+      <c r="A60" s="40"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="41"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="17"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="41" t="s">
+      <c r="A61" s="40"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="41"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="41"/>
-      <c r="G61" s="41"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="17"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="41" t="s">
+      <c r="A62" s="40"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="41"/>
-      <c r="G62" s="41"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="41" t="s">
+      <c r="A63" s="40"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="54"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="17">
+      <c r="A64" s="40">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="36"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
-      <c r="B65" s="18" t="s">
+      <c r="A65" s="40"/>
+      <c r="B65" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="C65" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18" t="s">
+      <c r="A66" s="40"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="36"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2098,164 +2104,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
+      <c r="D67" s="36"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="36"/>
+      <c r="G67" s="36"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="17">
+      <c r="A68" s="40">
         <v>46220</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="B68" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="18" t="s">
+      <c r="C68" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="18"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="36"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="17"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="18" t="s">
+      <c r="A69" s="40"/>
+      <c r="B69" s="36"/>
+      <c r="C69" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="18"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="36"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="17">
+      <c r="A70" s="40">
         <v>46223</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="B70" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C70" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="21"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="43"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="17"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="19" t="s">
+      <c r="A71" s="40"/>
+      <c r="B71" s="36"/>
+      <c r="C71" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="21"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="43"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="17"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="19" t="s">
+      <c r="A72" s="40"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="21"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="43"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="17"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="19" t="s">
+      <c r="A73" s="40"/>
+      <c r="B73" s="36"/>
+      <c r="C73" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="21"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="43"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="17"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="19" t="s">
+      <c r="A74" s="40"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="21"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="43"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="17"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="19" t="s">
+      <c r="A75" s="40"/>
+      <c r="B75" s="36"/>
+      <c r="C75" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="21"/>
+      <c r="D75" s="42"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="42"/>
+      <c r="G75" s="43"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="17"/>
-      <c r="B76" s="18"/>
-      <c r="C76" s="19" t="s">
+      <c r="A76" s="40"/>
+      <c r="B76" s="36"/>
+      <c r="C76" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="21"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="43"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="17"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="14" t="s">
+      <c r="A77" s="40"/>
+      <c r="B77" s="36"/>
+      <c r="C77" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="16"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38"/>
+      <c r="G77" s="39"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="14" t="s">
+      <c r="A78" s="40"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="16"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="39"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="17"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="14" t="s">
+      <c r="A79" s="40"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="16"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="39"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="17"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="14" t="s">
+      <c r="A80" s="40"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="16"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="39"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2264,353 +2270,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
+      <c r="D81" s="36"/>
+      <c r="E81" s="36"/>
+      <c r="F81" s="36"/>
+      <c r="G81" s="36"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="17">
+      <c r="A82" s="40">
         <v>46225</v>
       </c>
-      <c r="B82" s="18" t="s">
+      <c r="B82" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="18" t="s">
+      <c r="C82" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
-      <c r="F82" s="18"/>
-      <c r="G82" s="18"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="36"/>
+      <c r="G82" s="36"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="17"/>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18" t="s">
+      <c r="A83" s="40"/>
+      <c r="B83" s="36"/>
+      <c r="C83" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
-      <c r="F83" s="18"/>
-      <c r="G83" s="18"/>
+      <c r="D83" s="36"/>
+      <c r="E83" s="36"/>
+      <c r="F83" s="36"/>
+      <c r="G83" s="36"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="17"/>
-      <c r="B84" s="18"/>
-      <c r="C84" s="18" t="s">
+      <c r="A84" s="40"/>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="18"/>
-      <c r="E84" s="18"/>
-      <c r="F84" s="18"/>
-      <c r="G84" s="18"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+      <c r="G84" s="36"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="17"/>
-      <c r="B85" s="18" t="s">
+      <c r="A85" s="40"/>
+      <c r="B85" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="18"/>
-      <c r="G85" s="18"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="36"/>
+      <c r="F85" s="36"/>
+      <c r="G85" s="36"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="17"/>
-      <c r="B86" s="18"/>
-      <c r="C86" s="18" t="s">
+      <c r="A86" s="40"/>
+      <c r="B86" s="36"/>
+      <c r="C86" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="18"/>
-      <c r="E86" s="18"/>
-      <c r="F86" s="18"/>
-      <c r="G86" s="18"/>
+      <c r="D86" s="36"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="36"/>
+      <c r="G86" s="36"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="17"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18" t="s">
+      <c r="A87" s="40"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="17"/>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18" t="s">
+      <c r="A88" s="40"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="17"/>
-      <c r="B89" s="18"/>
-      <c r="C89" s="19" t="s">
+      <c r="A89" s="40"/>
+      <c r="B89" s="36"/>
+      <c r="C89" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="20"/>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
-      <c r="G89" s="21"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+      <c r="G89" s="43"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="17"/>
-      <c r="B90" s="18"/>
-      <c r="C90" s="18" t="s">
+      <c r="A90" s="40"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="18"/>
-      <c r="E90" s="18"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="18"/>
+      <c r="D90" s="36"/>
+      <c r="E90" s="36"/>
+      <c r="F90" s="36"/>
+      <c r="G90" s="36"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="37">
+      <c r="A91" s="49">
         <v>46227</v>
       </c>
-      <c r="B91" s="27" t="s">
+      <c r="B91" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="18" t="s">
+      <c r="C91" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="18"/>
+      <c r="D91" s="36"/>
+      <c r="E91" s="36"/>
+      <c r="F91" s="36"/>
+      <c r="G91" s="36"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="39"/>
-      <c r="B92" s="28"/>
-      <c r="C92" s="19" t="s">
+      <c r="A92" s="50"/>
+      <c r="B92" s="48"/>
+      <c r="C92" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="20"/>
-      <c r="E92" s="20"/>
-      <c r="F92" s="20"/>
-      <c r="G92" s="21"/>
+      <c r="D92" s="42"/>
+      <c r="E92" s="42"/>
+      <c r="F92" s="42"/>
+      <c r="G92" s="43"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="17">
+      <c r="A93" s="40">
         <v>46228</v>
       </c>
-      <c r="B93" s="18" t="s">
+      <c r="B93" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="18" t="s">
+      <c r="C93" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
-      <c r="F93" s="18"/>
-      <c r="G93" s="18"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="36"/>
+      <c r="G93" s="36"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="17"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="18" t="s">
+      <c r="A94" s="40"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="18"/>
-      <c r="E94" s="18"/>
-      <c r="F94" s="18"/>
-      <c r="G94" s="18"/>
+      <c r="D94" s="36"/>
+      <c r="E94" s="36"/>
+      <c r="F94" s="36"/>
+      <c r="G94" s="36"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="17"/>
-      <c r="B95" s="18"/>
-      <c r="C95" s="18" t="s">
+      <c r="A95" s="40"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="18"/>
-      <c r="E95" s="18"/>
-      <c r="F95" s="18"/>
-      <c r="G95" s="18"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+      <c r="G95" s="36"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="17"/>
-      <c r="B96" s="18"/>
-      <c r="C96" s="18" t="s">
+      <c r="A96" s="40"/>
+      <c r="B96" s="36"/>
+      <c r="C96" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="18"/>
-      <c r="E96" s="18"/>
-      <c r="F96" s="18"/>
-      <c r="G96" s="18"/>
+      <c r="D96" s="36"/>
+      <c r="E96" s="36"/>
+      <c r="F96" s="36"/>
+      <c r="G96" s="36"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="17"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18" t="s">
+      <c r="A97" s="40"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="18"/>
+      <c r="D97" s="36"/>
+      <c r="E97" s="36"/>
+      <c r="F97" s="36"/>
+      <c r="G97" s="36"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="17"/>
-      <c r="B98" s="18"/>
-      <c r="C98" s="18" t="s">
+      <c r="A98" s="40"/>
+      <c r="B98" s="36"/>
+      <c r="C98" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="18"/>
-      <c r="E98" s="18"/>
-      <c r="F98" s="18"/>
-      <c r="G98" s="18"/>
+      <c r="D98" s="36"/>
+      <c r="E98" s="36"/>
+      <c r="F98" s="36"/>
+      <c r="G98" s="36"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="17">
+      <c r="A99" s="40">
         <v>46230</v>
       </c>
-      <c r="B99" s="18" t="s">
+      <c r="B99" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="18" t="s">
+      <c r="C99" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="18"/>
-      <c r="E99" s="18"/>
-      <c r="F99" s="18"/>
-      <c r="G99" s="18"/>
+      <c r="D99" s="36"/>
+      <c r="E99" s="36"/>
+      <c r="F99" s="36"/>
+      <c r="G99" s="36"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="17"/>
-      <c r="B100" s="18"/>
-      <c r="C100" s="18" t="s">
+      <c r="A100" s="40"/>
+      <c r="B100" s="36"/>
+      <c r="C100" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="18"/>
-      <c r="E100" s="18"/>
-      <c r="F100" s="18"/>
-      <c r="G100" s="18"/>
+      <c r="D100" s="36"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="36"/>
+      <c r="G100" s="36"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="17">
+      <c r="A101" s="40">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="43" t="s">
+      <c r="C101" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="43"/>
-      <c r="E101" s="43"/>
-      <c r="F101" s="43"/>
-      <c r="G101" s="43"/>
+      <c r="D101" s="46"/>
+      <c r="E101" s="46"/>
+      <c r="F101" s="46"/>
+      <c r="G101" s="46"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="17"/>
+      <c r="A102" s="40"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="43" t="s">
+      <c r="C102" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="43"/>
-      <c r="E102" s="43"/>
-      <c r="F102" s="43"/>
-      <c r="G102" s="43"/>
+      <c r="D102" s="46"/>
+      <c r="E102" s="46"/>
+      <c r="F102" s="46"/>
+      <c r="G102" s="46"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="42" t="s">
+      <c r="A103" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="32" t="s">
+      <c r="C103" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="32"/>
-      <c r="E103" s="32"/>
-      <c r="F103" s="32"/>
-      <c r="G103" s="32"/>
+      <c r="D103" s="45"/>
+      <c r="E103" s="45"/>
+      <c r="F103" s="45"/>
+      <c r="G103" s="45"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="42"/>
-      <c r="B104" s="18"/>
-      <c r="C104" s="18" t="s">
+      <c r="A104" s="44"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="18"/>
-      <c r="E104" s="18"/>
-      <c r="F104" s="18"/>
-      <c r="G104" s="18"/>
+      <c r="D104" s="36"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="36"/>
+      <c r="G104" s="36"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="42"/>
-      <c r="B105" s="18"/>
-      <c r="C105" s="18" t="s">
+      <c r="A105" s="44"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="18"/>
-      <c r="E105" s="18"/>
-      <c r="F105" s="18"/>
-      <c r="G105" s="18"/>
+      <c r="D105" s="36"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="36"/>
+      <c r="G105" s="36"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="42"/>
-      <c r="B106" s="18"/>
-      <c r="C106" s="18" t="s">
+      <c r="A106" s="44"/>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="18"/>
-      <c r="E106" s="18"/>
-      <c r="F106" s="18"/>
-      <c r="G106" s="18"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+      <c r="G106" s="36"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="42"/>
-      <c r="B107" s="18"/>
-      <c r="C107" s="18" t="s">
+      <c r="A107" s="44"/>
+      <c r="B107" s="36"/>
+      <c r="C107" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="18"/>
-      <c r="E107" s="18"/>
-      <c r="F107" s="18"/>
-      <c r="G107" s="18"/>
+      <c r="D107" s="36"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="36"/>
+      <c r="G107" s="36"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="17">
+      <c r="A108" s="40">
         <v>46234</v>
       </c>
-      <c r="B108" s="18" t="s">
+      <c r="B108" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C108" s="18" t="s">
+      <c r="C108" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="18"/>
-      <c r="E108" s="18"/>
-      <c r="F108" s="18"/>
-      <c r="G108" s="18"/>
+      <c r="D108" s="36"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="36"/>
+      <c r="G108" s="36"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="17"/>
-      <c r="B109" s="18"/>
-      <c r="C109" s="18" t="s">
+      <c r="A109" s="40"/>
+      <c r="B109" s="36"/>
+      <c r="C109" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="18"/>
-      <c r="E109" s="18"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="18"/>
+      <c r="D109" s="36"/>
+      <c r="E109" s="36"/>
+      <c r="F109" s="36"/>
+      <c r="G109" s="36"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2620,68 +2626,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2706,67 +2711,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2774,25 +2780,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E5051E-34BB-454A-9E98-0A0156A4405B}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="44" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="44" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="44"/>
+    <col min="1" max="1" width="9.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="30">
+      <c r="A1" s="56">
         <v>46235</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2801,120 +2807,135 @@
       <c r="B2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="59"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>46237</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="48" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="50"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="48" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="50"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="13"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="51" t="s">
+      <c r="B7" s="26"/>
+      <c r="C7" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="53"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="45">
+      <c r="A8" s="15">
         <v>46238</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="47"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="50"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="50"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="51"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51" t="s">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="53"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="63">
+        <v>46239</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC018119-A3EF-4DB2-92FE-BDD5ADB72B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7DB260-FBC0-43B5-9FB7-4E309080A4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="117">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -604,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -692,6 +692,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -707,84 +733,71 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1107,15 +1120,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="31">
+      <c r="A1" s="41">
         <v>46174</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1124,146 +1137,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="35"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="40">
+      <c r="A3" s="36">
         <v>46202</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="40"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36" t="s">
+      <c r="A5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="36"/>
+      <c r="B6" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36" t="s">
+      <c r="A7" s="36"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="40"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36" t="s">
+      <c r="A8" s="36"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="40">
+      <c r="A9" s="36">
         <v>46203</v>
       </c>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="43"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="40"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="37" t="s">
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="39"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="35"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="40"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37" t="s">
+      <c r="A11" s="36"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="39"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="40"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37" t="s">
+      <c r="A12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="39"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="35"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="40"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1273,14 +1286,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1291,6 +1296,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1308,15 +1321,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="56">
+      <c r="A1" s="49">
         <v>46204</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1325,152 +1338,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="40">
+      <c r="A3" s="36">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
-      <c r="B4" s="36" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="40"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36" t="s">
+      <c r="A5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36" t="s">
+      <c r="A6" s="36"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="58">
+      <c r="A7" s="52">
         <v>46205</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="43"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="40"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="59"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="37" t="s">
+      <c r="A8" s="53"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="39"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="35"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="59"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="37" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="39"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="35"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="59"/>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="53"/>
+      <c r="B10" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="39"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="35"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="59"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="39"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="59"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37" t="s">
+      <c r="A12" s="53"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="39"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="35"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="60"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37" t="s">
+      <c r="A13" s="54"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="49">
+      <c r="A14" s="56">
         <v>46206</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="B14" s="46" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1482,348 +1495,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="41" t="s">
+      <c r="A15" s="57"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="41" t="s">
+      <c r="A16" s="57"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="43"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="41" t="s">
+      <c r="A17" s="57"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="43"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="52"/>
-      <c r="B18" s="47" t="s">
+      <c r="A18" s="57"/>
+      <c r="B18" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="43"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="41" t="s">
+      <c r="A19" s="58"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="43"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="40"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="53">
+      <c r="A20" s="59">
         <v>46209</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="53"/>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36" t="s">
+      <c r="A21" s="59"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="53"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36" t="s">
+      <c r="A22" s="59"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="53"/>
-      <c r="B23" s="36" t="s">
+      <c r="A23" s="59"/>
+      <c r="B23" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="41" t="s">
+      <c r="A24" s="59"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="43"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="40"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="53"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="41" t="s">
+      <c r="A25" s="59"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="40"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="53"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="41" t="s">
+      <c r="A26" s="59"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="43"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="40"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="53"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="41" t="s">
+      <c r="A27" s="59"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="43"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="40"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="53"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="41" t="s">
+      <c r="A28" s="59"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="43"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="40"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="53"/>
-      <c r="B29" s="36"/>
-      <c r="C29" s="41" t="s">
+      <c r="A29" s="59"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="43"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="53"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="41" t="s">
+      <c r="A30" s="59"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="43"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="40"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="53"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="41" t="s">
+      <c r="A31" s="59"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="43"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="40"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="53"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="41" t="s">
+      <c r="A32" s="59"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="43"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="40"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="53"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="41" t="s">
+      <c r="A33" s="59"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="43"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="40"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="53"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="41" t="s">
+      <c r="A34" s="59"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="43"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="40"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="51">
+      <c r="A35" s="55">
         <v>46210</v>
       </c>
-      <c r="B35" s="36" t="s">
+      <c r="B35" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="51"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36" t="s">
+      <c r="A36" s="55"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="51"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36" t="s">
+      <c r="A37" s="55"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="51"/>
-      <c r="B38" s="36" t="s">
+      <c r="A38" s="55"/>
+      <c r="B38" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="36" t="s">
+      <c r="C38" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="51"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="36" t="s">
+      <c r="A39" s="55"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="51"/>
-      <c r="B40" s="36"/>
-      <c r="C40" s="36" t="s">
+      <c r="A40" s="55"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="51"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36" t="s">
+      <c r="A41" s="55"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="51"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="36" t="s">
+      <c r="A42" s="55"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="51"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="36" t="s">
+      <c r="A43" s="55"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="51"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="41" t="s">
+      <c r="A44" s="55"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="43"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="40"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1832,13 +1845,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="36" t="s">
+      <c r="C45" s="37" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1847,255 +1860,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="C46" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="49">
+      <c r="A47" s="56">
         <v>46213</v>
       </c>
-      <c r="B47" s="47" t="s">
+      <c r="B47" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="41" t="s">
+      <c r="C47" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="43"/>
+      <c r="D47" s="39"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="40"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="52"/>
-      <c r="B48" s="55"/>
-      <c r="C48" s="41" t="s">
+      <c r="A48" s="57"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="42"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="43"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="40"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="52"/>
-      <c r="B49" s="55"/>
-      <c r="C49" s="41" t="s">
+      <c r="A49" s="57"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="43"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="40"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="52"/>
-      <c r="B50" s="55"/>
-      <c r="C50" s="41" t="s">
+      <c r="A50" s="57"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="42"/>
-      <c r="E50" s="42"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="43"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="40"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="50"/>
-      <c r="B51" s="48"/>
-      <c r="C51" s="41" t="s">
+      <c r="A51" s="58"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="42"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="43"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="40"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="40">
+      <c r="A52" s="36">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="36" t="s">
+      <c r="C52" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="36"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="40"/>
+      <c r="A53" s="36"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="36" t="s">
+      <c r="C53" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="37"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="40">
+      <c r="A54" s="36">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="41" t="s">
+      <c r="C54" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="42"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="43"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="40"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="40"/>
-      <c r="B55" s="36" t="s">
+      <c r="A55" s="36"/>
+      <c r="B55" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="54" t="s">
+      <c r="C55" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
+      <c r="D55" s="60"/>
+      <c r="E55" s="60"/>
+      <c r="F55" s="60"/>
+      <c r="G55" s="60"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="40"/>
-      <c r="B56" s="36"/>
-      <c r="C56" s="54" t="s">
+      <c r="A56" s="36"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
+      <c r="D56" s="60"/>
+      <c r="E56" s="60"/>
+      <c r="F56" s="60"/>
+      <c r="G56" s="60"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="40"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="54" t="s">
+      <c r="A57" s="36"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="54"/>
-      <c r="E57" s="54"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="54"/>
+      <c r="D57" s="60"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="40"/>
-      <c r="B58" s="36"/>
-      <c r="C58" s="54" t="s">
+      <c r="A58" s="36"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="54"/>
-      <c r="E58" s="54"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="60"/>
+      <c r="F58" s="60"/>
+      <c r="G58" s="60"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="40"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="54" t="s">
+      <c r="A59" s="36"/>
+      <c r="B59" s="37"/>
+      <c r="C59" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="54"/>
-      <c r="E59" s="54"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="54"/>
+      <c r="D59" s="60"/>
+      <c r="E59" s="60"/>
+      <c r="F59" s="60"/>
+      <c r="G59" s="60"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="40"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="54" t="s">
+      <c r="A60" s="36"/>
+      <c r="B60" s="37"/>
+      <c r="C60" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="54"/>
+      <c r="D60" s="60"/>
+      <c r="E60" s="60"/>
+      <c r="F60" s="60"/>
+      <c r="G60" s="60"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="40"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="54" t="s">
+      <c r="A61" s="36"/>
+      <c r="B61" s="37"/>
+      <c r="C61" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="54"/>
-      <c r="E61" s="54"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="40"/>
-      <c r="B62" s="36"/>
-      <c r="C62" s="54" t="s">
+      <c r="A62" s="36"/>
+      <c r="B62" s="37"/>
+      <c r="C62" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="54"/>
-      <c r="E62" s="54"/>
-      <c r="F62" s="54"/>
-      <c r="G62" s="54"/>
+      <c r="D62" s="60"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="60"/>
+      <c r="G62" s="60"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="40"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="54" t="s">
+      <c r="A63" s="36"/>
+      <c r="B63" s="37"/>
+      <c r="C63" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="54"/>
-      <c r="E63" s="54"/>
-      <c r="F63" s="54"/>
-      <c r="G63" s="54"/>
+      <c r="D63" s="60"/>
+      <c r="E63" s="60"/>
+      <c r="F63" s="60"/>
+      <c r="G63" s="60"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="40">
+      <c r="A64" s="36">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="36" t="s">
+      <c r="C64" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="36"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-      <c r="G64" s="36"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="40"/>
-      <c r="B65" s="36" t="s">
+      <c r="A65" s="36"/>
+      <c r="B65" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="36" t="s">
+      <c r="C65" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="36"/>
-      <c r="E65" s="36"/>
-      <c r="F65" s="36"/>
-      <c r="G65" s="36"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="40"/>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36" t="s">
+      <c r="A66" s="36"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-      <c r="G66" s="36"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="37"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2104,164 +2117,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="36" t="s">
+      <c r="C67" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="36"/>
-      <c r="E67" s="36"/>
-      <c r="F67" s="36"/>
-      <c r="G67" s="36"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="37"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="40">
+      <c r="A68" s="36">
         <v>46220</v>
       </c>
-      <c r="B68" s="36" t="s">
+      <c r="B68" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="36" t="s">
+      <c r="C68" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="40"/>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36" t="s">
+      <c r="A69" s="36"/>
+      <c r="B69" s="37"/>
+      <c r="C69" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="37"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="37"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="40">
+      <c r="A70" s="36">
         <v>46223</v>
       </c>
-      <c r="B70" s="36" t="s">
+      <c r="B70" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="41" t="s">
+      <c r="C70" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="42"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="43"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="40"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="40"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="41" t="s">
+      <c r="A71" s="36"/>
+      <c r="B71" s="37"/>
+      <c r="C71" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="42"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="42"/>
-      <c r="G71" s="43"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="40"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="40"/>
-      <c r="B72" s="36"/>
-      <c r="C72" s="41" t="s">
+      <c r="A72" s="36"/>
+      <c r="B72" s="37"/>
+      <c r="C72" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="42"/>
-      <c r="E72" s="42"/>
-      <c r="F72" s="42"/>
-      <c r="G72" s="43"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="40"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="40"/>
-      <c r="B73" s="36"/>
-      <c r="C73" s="41" t="s">
+      <c r="A73" s="36"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="42"/>
-      <c r="E73" s="42"/>
-      <c r="F73" s="42"/>
-      <c r="G73" s="43"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="40"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="40"/>
-      <c r="B74" s="36"/>
-      <c r="C74" s="41" t="s">
+      <c r="A74" s="36"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="42"/>
-      <c r="E74" s="42"/>
-      <c r="F74" s="42"/>
-      <c r="G74" s="43"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="40"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="40"/>
-      <c r="B75" s="36"/>
-      <c r="C75" s="41" t="s">
+      <c r="A75" s="36"/>
+      <c r="B75" s="37"/>
+      <c r="C75" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="42"/>
-      <c r="E75" s="42"/>
-      <c r="F75" s="42"/>
-      <c r="G75" s="43"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="40"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="40"/>
-      <c r="B76" s="36"/>
-      <c r="C76" s="41" t="s">
+      <c r="A76" s="36"/>
+      <c r="B76" s="37"/>
+      <c r="C76" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="42"/>
-      <c r="E76" s="42"/>
-      <c r="F76" s="42"/>
-      <c r="G76" s="43"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="40"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="40"/>
-      <c r="B77" s="36"/>
-      <c r="C77" s="37" t="s">
+      <c r="A77" s="36"/>
+      <c r="B77" s="37"/>
+      <c r="C77" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="38"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="38"/>
-      <c r="G77" s="39"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="35"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="40"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="37" t="s">
+      <c r="A78" s="36"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="39"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="34"/>
+      <c r="F78" s="34"/>
+      <c r="G78" s="35"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="40"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="37" t="s">
+      <c r="A79" s="36"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="39"/>
+      <c r="D79" s="34"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="34"/>
+      <c r="G79" s="35"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="40"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="37" t="s">
+      <c r="A80" s="36"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="39"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="34"/>
+      <c r="G80" s="35"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2270,353 +2283,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="36" t="s">
+      <c r="C81" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="36"/>
-      <c r="E81" s="36"/>
-      <c r="F81" s="36"/>
-      <c r="G81" s="36"/>
+      <c r="D81" s="37"/>
+      <c r="E81" s="37"/>
+      <c r="F81" s="37"/>
+      <c r="G81" s="37"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="40">
+      <c r="A82" s="36">
         <v>46225</v>
       </c>
-      <c r="B82" s="36" t="s">
+      <c r="B82" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="36" t="s">
+      <c r="C82" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="36"/>
-      <c r="E82" s="36"/>
-      <c r="F82" s="36"/>
-      <c r="G82" s="36"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="40"/>
-      <c r="B83" s="36"/>
-      <c r="C83" s="36" t="s">
+      <c r="A83" s="36"/>
+      <c r="B83" s="37"/>
+      <c r="C83" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="36"/>
-      <c r="E83" s="36"/>
-      <c r="F83" s="36"/>
-      <c r="G83" s="36"/>
+      <c r="D83" s="37"/>
+      <c r="E83" s="37"/>
+      <c r="F83" s="37"/>
+      <c r="G83" s="37"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="40"/>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36" t="s">
+      <c r="A84" s="36"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-      <c r="G84" s="36"/>
+      <c r="D84" s="37"/>
+      <c r="E84" s="37"/>
+      <c r="F84" s="37"/>
+      <c r="G84" s="37"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="40"/>
-      <c r="B85" s="36" t="s">
+      <c r="A85" s="36"/>
+      <c r="B85" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="36" t="s">
+      <c r="C85" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="36"/>
-      <c r="E85" s="36"/>
-      <c r="F85" s="36"/>
-      <c r="G85" s="36"/>
+      <c r="D85" s="37"/>
+      <c r="E85" s="37"/>
+      <c r="F85" s="37"/>
+      <c r="G85" s="37"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="40"/>
-      <c r="B86" s="36"/>
-      <c r="C86" s="36" t="s">
+      <c r="A86" s="36"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="36"/>
-      <c r="E86" s="36"/>
-      <c r="F86" s="36"/>
-      <c r="G86" s="36"/>
+      <c r="D86" s="37"/>
+      <c r="E86" s="37"/>
+      <c r="F86" s="37"/>
+      <c r="G86" s="37"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="40"/>
-      <c r="B87" s="36"/>
-      <c r="C87" s="36" t="s">
+      <c r="A87" s="36"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="36"/>
-      <c r="E87" s="36"/>
-      <c r="F87" s="36"/>
-      <c r="G87" s="36"/>
+      <c r="D87" s="37"/>
+      <c r="E87" s="37"/>
+      <c r="F87" s="37"/>
+      <c r="G87" s="37"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="40"/>
-      <c r="B88" s="36"/>
-      <c r="C88" s="36" t="s">
+      <c r="A88" s="36"/>
+      <c r="B88" s="37"/>
+      <c r="C88" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="36"/>
-      <c r="E88" s="36"/>
-      <c r="F88" s="36"/>
-      <c r="G88" s="36"/>
+      <c r="D88" s="37"/>
+      <c r="E88" s="37"/>
+      <c r="F88" s="37"/>
+      <c r="G88" s="37"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="40"/>
-      <c r="B89" s="36"/>
-      <c r="C89" s="41" t="s">
+      <c r="A89" s="36"/>
+      <c r="B89" s="37"/>
+      <c r="C89" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="42"/>
-      <c r="E89" s="42"/>
-      <c r="F89" s="42"/>
-      <c r="G89" s="43"/>
+      <c r="D89" s="39"/>
+      <c r="E89" s="39"/>
+      <c r="F89" s="39"/>
+      <c r="G89" s="40"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="40"/>
-      <c r="B90" s="36"/>
-      <c r="C90" s="36" t="s">
+      <c r="A90" s="36"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="36"/>
-      <c r="E90" s="36"/>
-      <c r="F90" s="36"/>
-      <c r="G90" s="36"/>
+      <c r="D90" s="37"/>
+      <c r="E90" s="37"/>
+      <c r="F90" s="37"/>
+      <c r="G90" s="37"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="49">
+      <c r="A91" s="56">
         <v>46227</v>
       </c>
-      <c r="B91" s="47" t="s">
+      <c r="B91" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="36" t="s">
+      <c r="C91" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="36"/>
-      <c r="E91" s="36"/>
-      <c r="F91" s="36"/>
-      <c r="G91" s="36"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="37"/>
+      <c r="G91" s="37"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="50"/>
-      <c r="B92" s="48"/>
-      <c r="C92" s="41" t="s">
+      <c r="A92" s="58"/>
+      <c r="B92" s="47"/>
+      <c r="C92" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="42"/>
-      <c r="E92" s="42"/>
-      <c r="F92" s="42"/>
-      <c r="G92" s="43"/>
+      <c r="D92" s="39"/>
+      <c r="E92" s="39"/>
+      <c r="F92" s="39"/>
+      <c r="G92" s="40"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="40">
+      <c r="A93" s="36">
         <v>46228</v>
       </c>
-      <c r="B93" s="36" t="s">
+      <c r="B93" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="36" t="s">
+      <c r="C93" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="36"/>
-      <c r="E93" s="36"/>
-      <c r="F93" s="36"/>
-      <c r="G93" s="36"/>
+      <c r="D93" s="37"/>
+      <c r="E93" s="37"/>
+      <c r="F93" s="37"/>
+      <c r="G93" s="37"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="40"/>
-      <c r="B94" s="36"/>
-      <c r="C94" s="36" t="s">
+      <c r="A94" s="36"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="36"/>
-      <c r="E94" s="36"/>
-      <c r="F94" s="36"/>
-      <c r="G94" s="36"/>
+      <c r="D94" s="37"/>
+      <c r="E94" s="37"/>
+      <c r="F94" s="37"/>
+      <c r="G94" s="37"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="40"/>
-      <c r="B95" s="36"/>
-      <c r="C95" s="36" t="s">
+      <c r="A95" s="36"/>
+      <c r="B95" s="37"/>
+      <c r="C95" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="36"/>
-      <c r="E95" s="36"/>
-      <c r="F95" s="36"/>
-      <c r="G95" s="36"/>
+      <c r="D95" s="37"/>
+      <c r="E95" s="37"/>
+      <c r="F95" s="37"/>
+      <c r="G95" s="37"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="40"/>
-      <c r="B96" s="36"/>
-      <c r="C96" s="36" t="s">
+      <c r="A96" s="36"/>
+      <c r="B96" s="37"/>
+      <c r="C96" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="36"/>
-      <c r="E96" s="36"/>
-      <c r="F96" s="36"/>
-      <c r="G96" s="36"/>
+      <c r="D96" s="37"/>
+      <c r="E96" s="37"/>
+      <c r="F96" s="37"/>
+      <c r="G96" s="37"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="40"/>
-      <c r="B97" s="36"/>
-      <c r="C97" s="36" t="s">
+      <c r="A97" s="36"/>
+      <c r="B97" s="37"/>
+      <c r="C97" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="36"/>
-      <c r="E97" s="36"/>
-      <c r="F97" s="36"/>
-      <c r="G97" s="36"/>
+      <c r="D97" s="37"/>
+      <c r="E97" s="37"/>
+      <c r="F97" s="37"/>
+      <c r="G97" s="37"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="40"/>
-      <c r="B98" s="36"/>
-      <c r="C98" s="36" t="s">
+      <c r="A98" s="36"/>
+      <c r="B98" s="37"/>
+      <c r="C98" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="36"/>
-      <c r="E98" s="36"/>
-      <c r="F98" s="36"/>
-      <c r="G98" s="36"/>
+      <c r="D98" s="37"/>
+      <c r="E98" s="37"/>
+      <c r="F98" s="37"/>
+      <c r="G98" s="37"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="40">
+      <c r="A99" s="36">
         <v>46230</v>
       </c>
-      <c r="B99" s="36" t="s">
+      <c r="B99" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="36" t="s">
+      <c r="C99" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="36"/>
-      <c r="E99" s="36"/>
-      <c r="F99" s="36"/>
-      <c r="G99" s="36"/>
+      <c r="D99" s="37"/>
+      <c r="E99" s="37"/>
+      <c r="F99" s="37"/>
+      <c r="G99" s="37"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="40"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36" t="s">
+      <c r="A100" s="36"/>
+      <c r="B100" s="37"/>
+      <c r="C100" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="36"/>
-      <c r="E100" s="36"/>
-      <c r="F100" s="36"/>
-      <c r="G100" s="36"/>
+      <c r="D100" s="37"/>
+      <c r="E100" s="37"/>
+      <c r="F100" s="37"/>
+      <c r="G100" s="37"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="40">
+      <c r="A101" s="36">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="46" t="s">
+      <c r="C101" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="46"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="46"/>
-      <c r="G101" s="46"/>
+      <c r="D101" s="62"/>
+      <c r="E101" s="62"/>
+      <c r="F101" s="62"/>
+      <c r="G101" s="62"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="40"/>
+      <c r="A102" s="36"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="46" t="s">
+      <c r="C102" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="46"/>
-      <c r="E102" s="46"/>
-      <c r="F102" s="46"/>
-      <c r="G102" s="46"/>
+      <c r="D102" s="62"/>
+      <c r="E102" s="62"/>
+      <c r="F102" s="62"/>
+      <c r="G102" s="62"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="44" t="s">
+      <c r="A103" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="36" t="s">
+      <c r="B103" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="45" t="s">
+      <c r="C103" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="45"/>
-      <c r="E103" s="45"/>
-      <c r="F103" s="45"/>
-      <c r="G103" s="45"/>
+      <c r="D103" s="51"/>
+      <c r="E103" s="51"/>
+      <c r="F103" s="51"/>
+      <c r="G103" s="51"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="44"/>
-      <c r="B104" s="36"/>
-      <c r="C104" s="36" t="s">
+      <c r="A104" s="61"/>
+      <c r="B104" s="37"/>
+      <c r="C104" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="36"/>
-      <c r="E104" s="36"/>
-      <c r="F104" s="36"/>
-      <c r="G104" s="36"/>
+      <c r="D104" s="37"/>
+      <c r="E104" s="37"/>
+      <c r="F104" s="37"/>
+      <c r="G104" s="37"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="44"/>
-      <c r="B105" s="36"/>
-      <c r="C105" s="36" t="s">
+      <c r="A105" s="61"/>
+      <c r="B105" s="37"/>
+      <c r="C105" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="36"/>
-      <c r="E105" s="36"/>
-      <c r="F105" s="36"/>
-      <c r="G105" s="36"/>
+      <c r="D105" s="37"/>
+      <c r="E105" s="37"/>
+      <c r="F105" s="37"/>
+      <c r="G105" s="37"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="44"/>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36" t="s">
+      <c r="A106" s="61"/>
+      <c r="B106" s="37"/>
+      <c r="C106" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-      <c r="G106" s="36"/>
+      <c r="D106" s="37"/>
+      <c r="E106" s="37"/>
+      <c r="F106" s="37"/>
+      <c r="G106" s="37"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="44"/>
-      <c r="B107" s="36"/>
-      <c r="C107" s="36" t="s">
+      <c r="A107" s="61"/>
+      <c r="B107" s="37"/>
+      <c r="C107" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="36"/>
-      <c r="E107" s="36"/>
-      <c r="F107" s="36"/>
-      <c r="G107" s="36"/>
+      <c r="D107" s="37"/>
+      <c r="E107" s="37"/>
+      <c r="F107" s="37"/>
+      <c r="G107" s="37"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="40">
+      <c r="A108" s="36">
         <v>46234</v>
       </c>
-      <c r="B108" s="36" t="s">
+      <c r="B108" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C108" s="36" t="s">
+      <c r="C108" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="36"/>
-      <c r="E108" s="36"/>
-      <c r="F108" s="36"/>
-      <c r="G108" s="36"/>
+      <c r="D108" s="37"/>
+      <c r="E108" s="37"/>
+      <c r="F108" s="37"/>
+      <c r="G108" s="37"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="40"/>
-      <c r="B109" s="36"/>
-      <c r="C109" s="36" t="s">
+      <c r="A109" s="36"/>
+      <c r="B109" s="37"/>
+      <c r="C109" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="36"/>
-      <c r="E109" s="36"/>
-      <c r="F109" s="36"/>
-      <c r="G109" s="36"/>
+      <c r="D109" s="37"/>
+      <c r="E109" s="37"/>
+      <c r="F109" s="37"/>
+      <c r="G109" s="37"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2626,6 +2639,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2650,129 +2786,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2780,25 +2793,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E5051E-34BB-454A-9E98-0A0156A4405B}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="14" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="56">
+      <c r="A1" s="49">
         <v>46235</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2912,7 +2925,7 @@
       <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21" t="s">
         <v>115</v>
@@ -2923,19 +2936,56 @@
       <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="63">
+      <c r="A12" s="6">
         <v>46239</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="62"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="32"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="63">
+        <v>46240</v>
+      </c>
+      <c r="B13" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="65"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="66"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="69"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="70" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7DB260-FBC0-43B5-9FB7-4E309080A4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C564266E-219A-4638-AAA7-9596AAFC1338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="119">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>Nhận BH GPS Global</t>
+  </si>
+  <si>
+    <t>Trả BH Gia Thành</t>
+  </si>
+  <si>
+    <t>Trả BH GPS Global</t>
   </si>
 </sst>
 </file>
@@ -604,7 +610,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -694,103 +700,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -798,6 +713,96 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,15 +1125,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="41">
+      <c r="A1" s="44">
         <v>46174</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1137,146 +1142,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="45"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="36">
+      <c r="A3" s="53">
         <v>46202</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37" t="s">
+      <c r="A5" s="53"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="36"/>
-      <c r="B6" s="37" t="s">
+      <c r="A6" s="53"/>
+      <c r="B6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="36"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37" t="s">
+      <c r="A7" s="53"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37" t="s">
+      <c r="A8" s="53"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="36">
+      <c r="A9" s="53">
         <v>46203</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="56"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="33" t="s">
+      <c r="A10" s="53"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="35"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="33" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="52"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="36"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="33" t="s">
+      <c r="A12" s="53"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="35"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="52"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="35"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="52"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1286,6 +1291,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1296,14 +1309,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1321,15 +1326,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="49">
+      <c r="A1" s="69">
         <v>46204</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1338,152 +1343,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="36">
+      <c r="A3" s="53">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="37" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37" t="s">
+      <c r="A5" s="53"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="36"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37" t="s">
+      <c r="A6" s="53"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="52">
+      <c r="A7" s="71">
         <v>46205</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="56"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="33" t="s">
+      <c r="A8" s="72"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="35"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="52"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="53"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="33" t="s">
+      <c r="A9" s="72"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="35"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="52"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="53"/>
-      <c r="B10" s="37" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="35"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="52"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="53"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="33" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="52"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="53"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="33" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="35"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="52"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="54"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="33" t="s">
+      <c r="A13" s="73"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="35"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="52"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="56">
+      <c r="A14" s="62">
         <v>46206</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="60" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1495,348 +1500,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="57"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="38" t="s">
+      <c r="A15" s="65"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="40"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="56"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="57"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="38" t="s">
+      <c r="A16" s="65"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="40"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="56"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="57"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="38" t="s">
+      <c r="A17" s="65"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="56"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="57"/>
-      <c r="B18" s="46" t="s">
+      <c r="A18" s="65"/>
+      <c r="B18" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="40"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="56"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="58"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="38" t="s">
+      <c r="A19" s="63"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="40"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="56"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="59">
+      <c r="A20" s="66">
         <v>46209</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="59"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37" t="s">
+      <c r="A21" s="66"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="59"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37" t="s">
+      <c r="A22" s="66"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="59"/>
-      <c r="B23" s="37" t="s">
+      <c r="A23" s="66"/>
+      <c r="B23" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="59"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="38" t="s">
+      <c r="A24" s="66"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="40"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="59"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="38" t="s">
+      <c r="A25" s="66"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="40"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="56"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="59"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="38" t="s">
+      <c r="A26" s="66"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="40"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="56"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="38" t="s">
+      <c r="A27" s="66"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="40"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="56"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="59"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="38" t="s">
+      <c r="A28" s="66"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="40"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="56"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="59"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="38" t="s">
+      <c r="A29" s="66"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="56"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="59"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="38" t="s">
+      <c r="A30" s="66"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="40"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="56"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="59"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="38" t="s">
+      <c r="A31" s="66"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="40"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="56"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="59"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="38" t="s">
+      <c r="A32" s="66"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="59"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="38" t="s">
+      <c r="A33" s="66"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="40"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="59"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="38" t="s">
+      <c r="A34" s="66"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="40"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="56"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="55">
+      <c r="A35" s="64">
         <v>46210</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="55"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37" t="s">
+      <c r="A36" s="64"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
+      <c r="D36" s="49"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="49"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="55"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37" t="s">
+      <c r="A37" s="64"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="55"/>
-      <c r="B38" s="37" t="s">
+      <c r="A38" s="64"/>
+      <c r="B38" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="55"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="37" t="s">
+      <c r="A39" s="64"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="49"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="55"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37" t="s">
+      <c r="A40" s="64"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="55"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37" t="s">
+      <c r="A41" s="64"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="55"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="55"/>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37" t="s">
+      <c r="A43" s="64"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="55"/>
-      <c r="B44" s="37"/>
-      <c r="C44" s="38" t="s">
+      <c r="A44" s="64"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="40"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="56"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1845,13 +1850,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="37" t="s">
+      <c r="C45" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1860,255 +1865,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="37" t="s">
+      <c r="C46" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="49"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="56">
+      <c r="A47" s="62">
         <v>46213</v>
       </c>
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="38" t="s">
+      <c r="C47" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="39"/>
-      <c r="E47" s="39"/>
-      <c r="F47" s="39"/>
-      <c r="G47" s="40"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="56"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="57"/>
-      <c r="B48" s="48"/>
-      <c r="C48" s="38" t="s">
+      <c r="A48" s="65"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
-      <c r="G48" s="40"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="56"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="57"/>
-      <c r="B49" s="48"/>
-      <c r="C49" s="38" t="s">
+      <c r="A49" s="65"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="39"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
-      <c r="G49" s="40"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="56"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="57"/>
-      <c r="B50" s="48"/>
-      <c r="C50" s="38" t="s">
+      <c r="A50" s="65"/>
+      <c r="B50" s="68"/>
+      <c r="C50" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="39"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="40"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="56"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="58"/>
-      <c r="B51" s="47"/>
-      <c r="C51" s="38" t="s">
+      <c r="A51" s="63"/>
+      <c r="B51" s="61"/>
+      <c r="C51" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="39"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="40"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="56"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="36">
+      <c r="A52" s="53">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="37" t="s">
+      <c r="C52" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="49"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="36"/>
+      <c r="A53" s="53"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="37" t="s">
+      <c r="C53" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="37"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="49"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="36">
+      <c r="A54" s="53">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="38" t="s">
+      <c r="C54" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="39"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="40"/>
+      <c r="D54" s="55"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="56"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="36"/>
-      <c r="B55" s="37" t="s">
+      <c r="A55" s="53"/>
+      <c r="B55" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="60" t="s">
+      <c r="C55" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="60"/>
-      <c r="E55" s="60"/>
-      <c r="F55" s="60"/>
-      <c r="G55" s="60"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="67"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="36"/>
-      <c r="B56" s="37"/>
-      <c r="C56" s="60" t="s">
+      <c r="A56" s="53"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="60"/>
-      <c r="E56" s="60"/>
-      <c r="F56" s="60"/>
-      <c r="G56" s="60"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="67"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="36"/>
-      <c r="B57" s="37"/>
-      <c r="C57" s="60" t="s">
+      <c r="A57" s="53"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="60"/>
-      <c r="E57" s="60"/>
-      <c r="F57" s="60"/>
-      <c r="G57" s="60"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="67"/>
+      <c r="G57" s="67"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="36"/>
-      <c r="B58" s="37"/>
-      <c r="C58" s="60" t="s">
+      <c r="A58" s="53"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="60"/>
-      <c r="E58" s="60"/>
-      <c r="F58" s="60"/>
-      <c r="G58" s="60"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="67"/>
+      <c r="F58" s="67"/>
+      <c r="G58" s="67"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="36"/>
-      <c r="B59" s="37"/>
-      <c r="C59" s="60" t="s">
+      <c r="A59" s="53"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="60"/>
-      <c r="E59" s="60"/>
-      <c r="F59" s="60"/>
-      <c r="G59" s="60"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="67"/>
+      <c r="F59" s="67"/>
+      <c r="G59" s="67"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="36"/>
-      <c r="B60" s="37"/>
-      <c r="C60" s="60" t="s">
+      <c r="A60" s="53"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="60"/>
-      <c r="E60" s="60"/>
-      <c r="F60" s="60"/>
-      <c r="G60" s="60"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="67"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="36"/>
-      <c r="B61" s="37"/>
-      <c r="C61" s="60" t="s">
+      <c r="A61" s="53"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="60"/>
-      <c r="E61" s="60"/>
-      <c r="F61" s="60"/>
-      <c r="G61" s="60"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="36"/>
-      <c r="B62" s="37"/>
-      <c r="C62" s="60" t="s">
+      <c r="A62" s="53"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="60"/>
-      <c r="E62" s="60"/>
-      <c r="F62" s="60"/>
-      <c r="G62" s="60"/>
+      <c r="D62" s="67"/>
+      <c r="E62" s="67"/>
+      <c r="F62" s="67"/>
+      <c r="G62" s="67"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="36"/>
-      <c r="B63" s="37"/>
-      <c r="C63" s="60" t="s">
+      <c r="A63" s="53"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="60"/>
-      <c r="E63" s="60"/>
-      <c r="F63" s="60"/>
-      <c r="G63" s="60"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="67"/>
+      <c r="F63" s="67"/>
+      <c r="G63" s="67"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="36">
+      <c r="A64" s="53">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="37" t="s">
+      <c r="C64" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
+      <c r="D64" s="49"/>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="49"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="36"/>
-      <c r="B65" s="37" t="s">
+      <c r="A65" s="53"/>
+      <c r="B65" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="37" t="s">
+      <c r="C65" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="37"/>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="49"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="36"/>
-      <c r="B66" s="37"/>
-      <c r="C66" s="37" t="s">
+      <c r="A66" s="53"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="37"/>
+      <c r="D66" s="49"/>
+      <c r="E66" s="49"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="49"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2117,164 +2122,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="37" t="s">
+      <c r="C67" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="37"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="37"/>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="49"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="36">
+      <c r="A68" s="53">
         <v>46220</v>
       </c>
-      <c r="B68" s="37" t="s">
+      <c r="B68" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="37" t="s">
+      <c r="C68" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
+      <c r="D68" s="49"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="36"/>
-      <c r="B69" s="37"/>
-      <c r="C69" s="37" t="s">
+      <c r="A69" s="53"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="37"/>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="36">
+      <c r="A70" s="53">
         <v>46223</v>
       </c>
-      <c r="B70" s="37" t="s">
+      <c r="B70" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="38" t="s">
+      <c r="C70" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="39"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="40"/>
+      <c r="D70" s="55"/>
+      <c r="E70" s="55"/>
+      <c r="F70" s="55"/>
+      <c r="G70" s="56"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="36"/>
-      <c r="B71" s="37"/>
-      <c r="C71" s="38" t="s">
+      <c r="A71" s="53"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="39"/>
-      <c r="E71" s="39"/>
-      <c r="F71" s="39"/>
-      <c r="G71" s="40"/>
+      <c r="D71" s="55"/>
+      <c r="E71" s="55"/>
+      <c r="F71" s="55"/>
+      <c r="G71" s="56"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="36"/>
-      <c r="B72" s="37"/>
-      <c r="C72" s="38" t="s">
+      <c r="A72" s="53"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="39"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="40"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="55"/>
+      <c r="G72" s="56"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="36"/>
-      <c r="B73" s="37"/>
-      <c r="C73" s="38" t="s">
+      <c r="A73" s="53"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="40"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="55"/>
+      <c r="G73" s="56"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="36"/>
-      <c r="B74" s="37"/>
-      <c r="C74" s="38" t="s">
+      <c r="A74" s="53"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="39"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="40"/>
+      <c r="D74" s="55"/>
+      <c r="E74" s="55"/>
+      <c r="F74" s="55"/>
+      <c r="G74" s="56"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="36"/>
-      <c r="B75" s="37"/>
-      <c r="C75" s="38" t="s">
+      <c r="A75" s="53"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="39"/>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-      <c r="G75" s="40"/>
+      <c r="D75" s="55"/>
+      <c r="E75" s="55"/>
+      <c r="F75" s="55"/>
+      <c r="G75" s="56"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="36"/>
-      <c r="B76" s="37"/>
-      <c r="C76" s="38" t="s">
+      <c r="A76" s="53"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="39"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="39"/>
-      <c r="G76" s="40"/>
+      <c r="D76" s="55"/>
+      <c r="E76" s="55"/>
+      <c r="F76" s="55"/>
+      <c r="G76" s="56"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="36"/>
-      <c r="B77" s="37"/>
-      <c r="C77" s="33" t="s">
+      <c r="A77" s="53"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="34"/>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
-      <c r="G77" s="35"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
+      <c r="F77" s="51"/>
+      <c r="G77" s="52"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="36"/>
-      <c r="B78" s="37"/>
-      <c r="C78" s="33" t="s">
+      <c r="A78" s="53"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="34"/>
-      <c r="E78" s="34"/>
-      <c r="F78" s="34"/>
-      <c r="G78" s="35"/>
+      <c r="D78" s="51"/>
+      <c r="E78" s="51"/>
+      <c r="F78" s="51"/>
+      <c r="G78" s="52"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="36"/>
-      <c r="B79" s="37"/>
-      <c r="C79" s="33" t="s">
+      <c r="A79" s="53"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="34"/>
-      <c r="E79" s="34"/>
-      <c r="F79" s="34"/>
-      <c r="G79" s="35"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="51"/>
+      <c r="F79" s="51"/>
+      <c r="G79" s="52"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="36"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="33" t="s">
+      <c r="A80" s="53"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="34"/>
-      <c r="E80" s="34"/>
-      <c r="F80" s="34"/>
-      <c r="G80" s="35"/>
+      <c r="D80" s="51"/>
+      <c r="E80" s="51"/>
+      <c r="F80" s="51"/>
+      <c r="G80" s="52"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2283,353 +2288,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="37" t="s">
+      <c r="C81" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
-      <c r="G81" s="37"/>
+      <c r="D81" s="49"/>
+      <c r="E81" s="49"/>
+      <c r="F81" s="49"/>
+      <c r="G81" s="49"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="36">
+      <c r="A82" s="53">
         <v>46225</v>
       </c>
-      <c r="B82" s="37" t="s">
+      <c r="B82" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="37" t="s">
+      <c r="C82" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="37"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="37"/>
+      <c r="D82" s="49"/>
+      <c r="E82" s="49"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="49"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="36"/>
-      <c r="B83" s="37"/>
-      <c r="C83" s="37" t="s">
+      <c r="A83" s="53"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="37"/>
-      <c r="E83" s="37"/>
-      <c r="F83" s="37"/>
-      <c r="G83" s="37"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="49"/>
+      <c r="G83" s="49"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="36"/>
-      <c r="B84" s="37"/>
-      <c r="C84" s="37" t="s">
+      <c r="A84" s="53"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="37"/>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="37"/>
+      <c r="D84" s="49"/>
+      <c r="E84" s="49"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="49"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="36"/>
-      <c r="B85" s="37" t="s">
+      <c r="A85" s="53"/>
+      <c r="B85" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="37" t="s">
+      <c r="C85" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="37"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37"/>
+      <c r="D85" s="49"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="49"/>
+      <c r="G85" s="49"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="36"/>
-      <c r="B86" s="37"/>
-      <c r="C86" s="37" t="s">
+      <c r="A86" s="53"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="37"/>
-      <c r="E86" s="37"/>
-      <c r="F86" s="37"/>
-      <c r="G86" s="37"/>
+      <c r="D86" s="49"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="49"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="36"/>
-      <c r="B87" s="37"/>
-      <c r="C87" s="37" t="s">
+      <c r="A87" s="53"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="37"/>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="49"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="36"/>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37" t="s">
+      <c r="A88" s="53"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="36"/>
-      <c r="B89" s="37"/>
-      <c r="C89" s="38" t="s">
+      <c r="A89" s="53"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="39"/>
-      <c r="E89" s="39"/>
-      <c r="F89" s="39"/>
-      <c r="G89" s="40"/>
+      <c r="D89" s="55"/>
+      <c r="E89" s="55"/>
+      <c r="F89" s="55"/>
+      <c r="G89" s="56"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="36"/>
-      <c r="B90" s="37"/>
-      <c r="C90" s="37" t="s">
+      <c r="A90" s="53"/>
+      <c r="B90" s="49"/>
+      <c r="C90" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="37"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="37"/>
+      <c r="D90" s="49"/>
+      <c r="E90" s="49"/>
+      <c r="F90" s="49"/>
+      <c r="G90" s="49"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="56">
+      <c r="A91" s="62">
         <v>46227</v>
       </c>
-      <c r="B91" s="46" t="s">
+      <c r="B91" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="37" t="s">
+      <c r="C91" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="37"/>
-      <c r="G91" s="37"/>
+      <c r="D91" s="49"/>
+      <c r="E91" s="49"/>
+      <c r="F91" s="49"/>
+      <c r="G91" s="49"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="58"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="38" t="s">
+      <c r="A92" s="63"/>
+      <c r="B92" s="61"/>
+      <c r="C92" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="39"/>
-      <c r="E92" s="39"/>
-      <c r="F92" s="39"/>
-      <c r="G92" s="40"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="55"/>
+      <c r="G92" s="56"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="36">
+      <c r="A93" s="53">
         <v>46228</v>
       </c>
-      <c r="B93" s="37" t="s">
+      <c r="B93" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="37" t="s">
+      <c r="C93" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="37"/>
-      <c r="E93" s="37"/>
-      <c r="F93" s="37"/>
-      <c r="G93" s="37"/>
+      <c r="D93" s="49"/>
+      <c r="E93" s="49"/>
+      <c r="F93" s="49"/>
+      <c r="G93" s="49"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="36"/>
-      <c r="B94" s="37"/>
-      <c r="C94" s="37" t="s">
+      <c r="A94" s="53"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="37"/>
-      <c r="E94" s="37"/>
-      <c r="F94" s="37"/>
-      <c r="G94" s="37"/>
+      <c r="D94" s="49"/>
+      <c r="E94" s="49"/>
+      <c r="F94" s="49"/>
+      <c r="G94" s="49"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="36"/>
-      <c r="B95" s="37"/>
-      <c r="C95" s="37" t="s">
+      <c r="A95" s="53"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="37"/>
-      <c r="E95" s="37"/>
-      <c r="F95" s="37"/>
-      <c r="G95" s="37"/>
+      <c r="D95" s="49"/>
+      <c r="E95" s="49"/>
+      <c r="F95" s="49"/>
+      <c r="G95" s="49"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="36"/>
-      <c r="B96" s="37"/>
-      <c r="C96" s="37" t="s">
+      <c r="A96" s="53"/>
+      <c r="B96" s="49"/>
+      <c r="C96" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="37"/>
-      <c r="E96" s="37"/>
-      <c r="F96" s="37"/>
-      <c r="G96" s="37"/>
+      <c r="D96" s="49"/>
+      <c r="E96" s="49"/>
+      <c r="F96" s="49"/>
+      <c r="G96" s="49"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="36"/>
-      <c r="B97" s="37"/>
-      <c r="C97" s="37" t="s">
+      <c r="A97" s="53"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="37"/>
-      <c r="E97" s="37"/>
-      <c r="F97" s="37"/>
-      <c r="G97" s="37"/>
+      <c r="D97" s="49"/>
+      <c r="E97" s="49"/>
+      <c r="F97" s="49"/>
+      <c r="G97" s="49"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="36"/>
-      <c r="B98" s="37"/>
-      <c r="C98" s="37" t="s">
+      <c r="A98" s="53"/>
+      <c r="B98" s="49"/>
+      <c r="C98" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="37"/>
-      <c r="E98" s="37"/>
-      <c r="F98" s="37"/>
-      <c r="G98" s="37"/>
+      <c r="D98" s="49"/>
+      <c r="E98" s="49"/>
+      <c r="F98" s="49"/>
+      <c r="G98" s="49"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="36">
+      <c r="A99" s="53">
         <v>46230</v>
       </c>
-      <c r="B99" s="37" t="s">
+      <c r="B99" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="37" t="s">
+      <c r="C99" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="37"/>
-      <c r="E99" s="37"/>
-      <c r="F99" s="37"/>
-      <c r="G99" s="37"/>
+      <c r="D99" s="49"/>
+      <c r="E99" s="49"/>
+      <c r="F99" s="49"/>
+      <c r="G99" s="49"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="36"/>
-      <c r="B100" s="37"/>
-      <c r="C100" s="37" t="s">
+      <c r="A100" s="53"/>
+      <c r="B100" s="49"/>
+      <c r="C100" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="37"/>
-      <c r="E100" s="37"/>
-      <c r="F100" s="37"/>
-      <c r="G100" s="37"/>
+      <c r="D100" s="49"/>
+      <c r="E100" s="49"/>
+      <c r="F100" s="49"/>
+      <c r="G100" s="49"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="36">
+      <c r="A101" s="53">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="62" t="s">
+      <c r="C101" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="62"/>
-      <c r="E101" s="62"/>
-      <c r="F101" s="62"/>
-      <c r="G101" s="62"/>
+      <c r="D101" s="59"/>
+      <c r="E101" s="59"/>
+      <c r="F101" s="59"/>
+      <c r="G101" s="59"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="36"/>
+      <c r="A102" s="53"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="62" t="s">
+      <c r="C102" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="62"/>
-      <c r="E102" s="62"/>
-      <c r="F102" s="62"/>
-      <c r="G102" s="62"/>
+      <c r="D102" s="59"/>
+      <c r="E102" s="59"/>
+      <c r="F102" s="59"/>
+      <c r="G102" s="59"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="61" t="s">
+      <c r="A103" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="37" t="s">
+      <c r="B103" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="51" t="s">
+      <c r="C103" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="51"/>
-      <c r="E103" s="51"/>
-      <c r="F103" s="51"/>
-      <c r="G103" s="51"/>
+      <c r="D103" s="58"/>
+      <c r="E103" s="58"/>
+      <c r="F103" s="58"/>
+      <c r="G103" s="58"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="61"/>
-      <c r="B104" s="37"/>
-      <c r="C104" s="37" t="s">
+      <c r="A104" s="57"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="37"/>
-      <c r="E104" s="37"/>
-      <c r="F104" s="37"/>
-      <c r="G104" s="37"/>
+      <c r="D104" s="49"/>
+      <c r="E104" s="49"/>
+      <c r="F104" s="49"/>
+      <c r="G104" s="49"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="61"/>
-      <c r="B105" s="37"/>
-      <c r="C105" s="37" t="s">
+      <c r="A105" s="57"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="37"/>
-      <c r="E105" s="37"/>
-      <c r="F105" s="37"/>
-      <c r="G105" s="37"/>
+      <c r="D105" s="49"/>
+      <c r="E105" s="49"/>
+      <c r="F105" s="49"/>
+      <c r="G105" s="49"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="61"/>
-      <c r="B106" s="37"/>
-      <c r="C106" s="37" t="s">
+      <c r="A106" s="57"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="37"/>
-      <c r="E106" s="37"/>
-      <c r="F106" s="37"/>
-      <c r="G106" s="37"/>
+      <c r="D106" s="49"/>
+      <c r="E106" s="49"/>
+      <c r="F106" s="49"/>
+      <c r="G106" s="49"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="61"/>
-      <c r="B107" s="37"/>
-      <c r="C107" s="37" t="s">
+      <c r="A107" s="57"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="37"/>
-      <c r="E107" s="37"/>
-      <c r="F107" s="37"/>
-      <c r="G107" s="37"/>
+      <c r="D107" s="49"/>
+      <c r="E107" s="49"/>
+      <c r="F107" s="49"/>
+      <c r="G107" s="49"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="36">
+      <c r="A108" s="53">
         <v>46234</v>
       </c>
-      <c r="B108" s="37" t="s">
+      <c r="B108" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C108" s="37" t="s">
+      <c r="C108" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="37"/>
-      <c r="E108" s="37"/>
-      <c r="F108" s="37"/>
-      <c r="G108" s="37"/>
+      <c r="D108" s="49"/>
+      <c r="E108" s="49"/>
+      <c r="F108" s="49"/>
+      <c r="G108" s="49"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="36"/>
-      <c r="B109" s="37"/>
-      <c r="C109" s="37" t="s">
+      <c r="A109" s="53"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="37"/>
-      <c r="E109" s="37"/>
-      <c r="F109" s="37"/>
-      <c r="G109" s="37"/>
+      <c r="D109" s="49"/>
+      <c r="E109" s="49"/>
+      <c r="F109" s="49"/>
+      <c r="G109" s="49"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2639,68 +2644,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="A14:A19"/>
@@ -2725,67 +2729,68 @@
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="B47:B51"/>
     <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C109:G109"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2793,7 +2798,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E5051E-34BB-454A-9E98-0A0156A4405B}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="14" bestFit="1" customWidth="1"/>
@@ -2803,15 +2808,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="49">
+      <c r="A1" s="69">
         <v>46235</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2951,41 +2956,64 @@
       <c r="G12" s="32"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="63">
+      <c r="A13" s="33">
         <v>46240</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="64" t="s">
+      <c r="C13" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="65"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="66"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="67" t="s">
+      <c r="A14" s="36"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="68"/>
+      <c r="G14" s="37"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="69"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="70" t="s">
+      <c r="A15" s="38"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="71"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
+        <v>46241</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="35"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C564266E-219A-4638-AAA7-9596AAFC1338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC7E068-B783-4E5D-B583-1DC9108554EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="124">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -387,6 +387,21 @@
   </si>
   <si>
     <t>Trả BH GPS Global</t>
+  </si>
+  <si>
+    <t>Trả BH Sao Việt</t>
+  </si>
+  <si>
+    <t>Nhập kho 20 VNSH03</t>
+  </si>
+  <si>
+    <t>Nâng cấp 1 thiết bị 2G=&gt;4G (HTA)</t>
+  </si>
+  <si>
+    <t>Nhận BH ĐL. Hoàng Anh Nghệ An</t>
+  </si>
+  <si>
+    <t>Nhận BH HTA</t>
   </si>
 </sst>
 </file>
@@ -610,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -713,6 +728,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -802,6 +826,24 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1125,15 +1167,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="44">
+      <c r="A1" s="47">
         <v>46174</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1142,146 +1184,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="53">
+      <c r="A3" s="56">
         <v>46202</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49" t="s">
+      <c r="A4" s="56"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="53"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49" t="s">
+      <c r="A5" s="56"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="53"/>
-      <c r="B6" s="49" t="s">
+      <c r="A6" s="56"/>
+      <c r="B6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49" t="s">
+      <c r="A7" s="56"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49" t="s">
+      <c r="A8" s="56"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="53">
+      <c r="A9" s="56">
         <v>46203</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="56"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="59"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="53"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="50" t="s">
+      <c r="A10" s="56"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="52"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="53"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50" t="s">
+      <c r="A11" s="56"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="52"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="55"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50" t="s">
+      <c r="A12" s="56"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="52"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="55"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="53"/>
+      <c r="A13" s="56"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="52"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="55"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1326,15 +1368,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="69">
+      <c r="A1" s="72">
         <v>46204</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1343,152 +1385,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="53">
+      <c r="A3" s="56">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53"/>
-      <c r="B4" s="49" t="s">
+      <c r="A4" s="56"/>
+      <c r="B4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="53"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49" t="s">
+      <c r="A5" s="56"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="53"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49" t="s">
+      <c r="A6" s="56"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="71">
+      <c r="A7" s="74">
         <v>46205</v>
       </c>
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="56"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="59"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="50" t="s">
+      <c r="A8" s="75"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="52"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="55"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="50" t="s">
+      <c r="A9" s="75"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="52"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="55"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="49" t="s">
+      <c r="A10" s="75"/>
+      <c r="B10" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="52"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="50" t="s">
+      <c r="A11" s="75"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="52"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="55"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="50" t="s">
+      <c r="A12" s="75"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="52"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="55"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="73"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50" t="s">
+      <c r="A13" s="76"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="52"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="55"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="62">
+      <c r="A14" s="65">
         <v>46206</v>
       </c>
-      <c r="B14" s="60" t="s">
+      <c r="B14" s="63" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1500,348 +1542,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="65"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="54" t="s">
+      <c r="A15" s="68"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="56"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="59"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="65"/>
-      <c r="B16" s="68"/>
-      <c r="C16" s="54" t="s">
+      <c r="A16" s="68"/>
+      <c r="B16" s="71"/>
+      <c r="C16" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="56"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="59"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="65"/>
-      <c r="B17" s="61"/>
-      <c r="C17" s="54" t="s">
+      <c r="A17" s="68"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="59"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="65"/>
-      <c r="B18" s="60" t="s">
+      <c r="A18" s="68"/>
+      <c r="B18" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="59"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="63"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="54" t="s">
+      <c r="A19" s="66"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="56"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="59"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="66">
+      <c r="A20" s="69">
         <v>46209</v>
       </c>
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="66"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49" t="s">
+      <c r="A21" s="69"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="66"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49" t="s">
+      <c r="A22" s="69"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="66"/>
-      <c r="B23" s="49" t="s">
+      <c r="A23" s="69"/>
+      <c r="B23" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="66"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="54" t="s">
+      <c r="A24" s="69"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="59"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="66"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="54" t="s">
+      <c r="A25" s="69"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="56"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="59"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="66"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="54" t="s">
+      <c r="A26" s="69"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="56"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="59"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="66"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="54" t="s">
+      <c r="A27" s="69"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="56"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="59"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="66"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="54" t="s">
+      <c r="A28" s="69"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="56"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="59"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="66"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="54" t="s">
+      <c r="A29" s="69"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="56"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="59"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="66"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="54" t="s">
+      <c r="A30" s="69"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="56"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="59"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="66"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="54" t="s">
+      <c r="A31" s="69"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="56"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="59"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="66"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="54" t="s">
+      <c r="A32" s="69"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="55"/>
-      <c r="E32" s="55"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="59"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="66"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="54" t="s">
+      <c r="A33" s="69"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="59"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="66"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="54" t="s">
+      <c r="A34" s="69"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="55"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="56"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="59"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="64">
+      <c r="A35" s="67">
         <v>46210</v>
       </c>
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="64"/>
-      <c r="B36" s="49"/>
-      <c r="C36" s="49" t="s">
+      <c r="A36" s="67"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="64"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="49" t="s">
+      <c r="A37" s="67"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="49"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="64"/>
-      <c r="B38" s="49" t="s">
+      <c r="A38" s="67"/>
+      <c r="B38" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="49" t="s">
+      <c r="C38" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="64"/>
-      <c r="B39" s="49"/>
-      <c r="C39" s="49" t="s">
+      <c r="A39" s="67"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="64"/>
-      <c r="B40" s="49"/>
-      <c r="C40" s="49" t="s">
+      <c r="A40" s="67"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="49"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="64"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49" t="s">
+      <c r="A41" s="67"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="49"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="52"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="64"/>
-      <c r="B42" s="49"/>
-      <c r="C42" s="49" t="s">
+      <c r="A42" s="67"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="49"/>
-      <c r="G42" s="49"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="64"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="49" t="s">
+      <c r="A43" s="67"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="52"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="64"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="54" t="s">
+      <c r="A44" s="67"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="56"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="59"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1850,13 +1892,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="49" t="s">
+      <c r="C45" s="52" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1865,255 +1907,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="49" t="s">
+      <c r="C46" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="49"/>
-      <c r="E46" s="49"/>
-      <c r="F46" s="49"/>
-      <c r="G46" s="49"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="62">
+      <c r="A47" s="65">
         <v>46213</v>
       </c>
-      <c r="B47" s="60" t="s">
+      <c r="B47" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="54" t="s">
+      <c r="C47" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="55"/>
-      <c r="G47" s="56"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="59"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="65"/>
-      <c r="B48" s="68"/>
-      <c r="C48" s="54" t="s">
+      <c r="A48" s="68"/>
+      <c r="B48" s="71"/>
+      <c r="C48" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="56"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="58"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="59"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="65"/>
-      <c r="B49" s="68"/>
-      <c r="C49" s="54" t="s">
+      <c r="A49" s="68"/>
+      <c r="B49" s="71"/>
+      <c r="C49" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="56"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="59"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="65"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="54" t="s">
+      <c r="A50" s="68"/>
+      <c r="B50" s="71"/>
+      <c r="C50" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="55"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="55"/>
-      <c r="G50" s="56"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="59"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="63"/>
-      <c r="B51" s="61"/>
-      <c r="C51" s="54" t="s">
+      <c r="A51" s="66"/>
+      <c r="B51" s="64"/>
+      <c r="C51" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="55"/>
-      <c r="E51" s="55"/>
-      <c r="F51" s="55"/>
-      <c r="G51" s="56"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="59"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="53">
+      <c r="A52" s="56">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="49" t="s">
+      <c r="C52" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="49"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
-      <c r="G52" s="49"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="53"/>
+      <c r="A53" s="56"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="49" t="s">
+      <c r="C53" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="49"/>
-      <c r="E53" s="49"/>
-      <c r="F53" s="49"/>
-      <c r="G53" s="49"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="52"/>
+      <c r="G53" s="52"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="53">
+      <c r="A54" s="56">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="54" t="s">
+      <c r="C54" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="55"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="56"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="59"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="53"/>
-      <c r="B55" s="49" t="s">
+      <c r="A55" s="56"/>
+      <c r="B55" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="67" t="s">
+      <c r="C55" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="67"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="53"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="67" t="s">
+      <c r="A56" s="56"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="67"/>
-      <c r="E56" s="67"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="67"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="53"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="67" t="s">
+      <c r="A57" s="56"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="67"/>
-      <c r="E57" s="67"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="67"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="53"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="67" t="s">
+      <c r="A58" s="56"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="67"/>
-      <c r="E58" s="67"/>
-      <c r="F58" s="67"/>
-      <c r="G58" s="67"/>
+      <c r="D58" s="70"/>
+      <c r="E58" s="70"/>
+      <c r="F58" s="70"/>
+      <c r="G58" s="70"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="53"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="67" t="s">
+      <c r="A59" s="56"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="67"/>
-      <c r="E59" s="67"/>
-      <c r="F59" s="67"/>
-      <c r="G59" s="67"/>
+      <c r="D59" s="70"/>
+      <c r="E59" s="70"/>
+      <c r="F59" s="70"/>
+      <c r="G59" s="70"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="53"/>
-      <c r="B60" s="49"/>
-      <c r="C60" s="67" t="s">
+      <c r="A60" s="56"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="67"/>
-      <c r="E60" s="67"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="67"/>
+      <c r="D60" s="70"/>
+      <c r="E60" s="70"/>
+      <c r="F60" s="70"/>
+      <c r="G60" s="70"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="53"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="67" t="s">
+      <c r="A61" s="56"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="53"/>
-      <c r="B62" s="49"/>
-      <c r="C62" s="67" t="s">
+      <c r="A62" s="56"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="67"/>
-      <c r="E62" s="67"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="67"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="70"/>
+      <c r="F62" s="70"/>
+      <c r="G62" s="70"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="53"/>
-      <c r="B63" s="49"/>
-      <c r="C63" s="67" t="s">
+      <c r="A63" s="56"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="67"/>
-      <c r="E63" s="67"/>
-      <c r="F63" s="67"/>
-      <c r="G63" s="67"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="53">
+      <c r="A64" s="56">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="49" t="s">
+      <c r="C64" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="49"/>
-      <c r="E64" s="49"/>
-      <c r="F64" s="49"/>
-      <c r="G64" s="49"/>
+      <c r="D64" s="52"/>
+      <c r="E64" s="52"/>
+      <c r="F64" s="52"/>
+      <c r="G64" s="52"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="53"/>
-      <c r="B65" s="49" t="s">
+      <c r="A65" s="56"/>
+      <c r="B65" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="49" t="s">
+      <c r="C65" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="49"/>
-      <c r="E65" s="49"/>
-      <c r="F65" s="49"/>
-      <c r="G65" s="49"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="52"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="52"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="53"/>
-      <c r="B66" s="49"/>
-      <c r="C66" s="49" t="s">
+      <c r="A66" s="56"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="49"/>
-      <c r="E66" s="49"/>
-      <c r="F66" s="49"/>
-      <c r="G66" s="49"/>
+      <c r="D66" s="52"/>
+      <c r="E66" s="52"/>
+      <c r="F66" s="52"/>
+      <c r="G66" s="52"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2122,164 +2164,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="49" t="s">
+      <c r="C67" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="49"/>
-      <c r="E67" s="49"/>
-      <c r="F67" s="49"/>
-      <c r="G67" s="49"/>
+      <c r="D67" s="52"/>
+      <c r="E67" s="52"/>
+      <c r="F67" s="52"/>
+      <c r="G67" s="52"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="53">
+      <c r="A68" s="56">
         <v>46220</v>
       </c>
-      <c r="B68" s="49" t="s">
+      <c r="B68" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="49" t="s">
+      <c r="C68" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="49"/>
-      <c r="E68" s="49"/>
-      <c r="F68" s="49"/>
-      <c r="G68" s="49"/>
+      <c r="D68" s="52"/>
+      <c r="E68" s="52"/>
+      <c r="F68" s="52"/>
+      <c r="G68" s="52"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="53"/>
-      <c r="B69" s="49"/>
-      <c r="C69" s="49" t="s">
+      <c r="A69" s="56"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="49"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="49"/>
-      <c r="G69" s="49"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="52"/>
+      <c r="F69" s="52"/>
+      <c r="G69" s="52"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="53">
+      <c r="A70" s="56">
         <v>46223</v>
       </c>
-      <c r="B70" s="49" t="s">
+      <c r="B70" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="54" t="s">
+      <c r="C70" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="55"/>
-      <c r="E70" s="55"/>
-      <c r="F70" s="55"/>
-      <c r="G70" s="56"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="59"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="53"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="54" t="s">
+      <c r="A71" s="56"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="55"/>
-      <c r="E71" s="55"/>
-      <c r="F71" s="55"/>
-      <c r="G71" s="56"/>
+      <c r="D71" s="58"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="58"/>
+      <c r="G71" s="59"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="53"/>
-      <c r="B72" s="49"/>
-      <c r="C72" s="54" t="s">
+      <c r="A72" s="56"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="55"/>
-      <c r="G72" s="56"/>
+      <c r="D72" s="58"/>
+      <c r="E72" s="58"/>
+      <c r="F72" s="58"/>
+      <c r="G72" s="59"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="53"/>
-      <c r="B73" s="49"/>
-      <c r="C73" s="54" t="s">
+      <c r="A73" s="56"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="55"/>
-      <c r="E73" s="55"/>
-      <c r="F73" s="55"/>
-      <c r="G73" s="56"/>
+      <c r="D73" s="58"/>
+      <c r="E73" s="58"/>
+      <c r="F73" s="58"/>
+      <c r="G73" s="59"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="53"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="54" t="s">
+      <c r="A74" s="56"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="55"/>
-      <c r="E74" s="55"/>
-      <c r="F74" s="55"/>
-      <c r="G74" s="56"/>
+      <c r="D74" s="58"/>
+      <c r="E74" s="58"/>
+      <c r="F74" s="58"/>
+      <c r="G74" s="59"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="53"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="54" t="s">
+      <c r="A75" s="56"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="55"/>
-      <c r="E75" s="55"/>
-      <c r="F75" s="55"/>
-      <c r="G75" s="56"/>
+      <c r="D75" s="58"/>
+      <c r="E75" s="58"/>
+      <c r="F75" s="58"/>
+      <c r="G75" s="59"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="53"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="54" t="s">
+      <c r="A76" s="56"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="55"/>
-      <c r="E76" s="55"/>
-      <c r="F76" s="55"/>
-      <c r="G76" s="56"/>
+      <c r="D76" s="58"/>
+      <c r="E76" s="58"/>
+      <c r="F76" s="58"/>
+      <c r="G76" s="59"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="53"/>
-      <c r="B77" s="49"/>
-      <c r="C77" s="50" t="s">
+      <c r="A77" s="56"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="51"/>
-      <c r="E77" s="51"/>
-      <c r="F77" s="51"/>
-      <c r="G77" s="52"/>
+      <c r="D77" s="54"/>
+      <c r="E77" s="54"/>
+      <c r="F77" s="54"/>
+      <c r="G77" s="55"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="53"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="50" t="s">
+      <c r="A78" s="56"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="51"/>
-      <c r="E78" s="51"/>
-      <c r="F78" s="51"/>
-      <c r="G78" s="52"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="54"/>
+      <c r="G78" s="55"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="53"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="50" t="s">
+      <c r="A79" s="56"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="51"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="51"/>
-      <c r="G79" s="52"/>
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="55"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="53"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="50" t="s">
+      <c r="A80" s="56"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="51"/>
-      <c r="E80" s="51"/>
-      <c r="F80" s="51"/>
-      <c r="G80" s="52"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="55"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2288,353 +2330,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="49" t="s">
+      <c r="C81" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="49"/>
-      <c r="E81" s="49"/>
-      <c r="F81" s="49"/>
-      <c r="G81" s="49"/>
+      <c r="D81" s="52"/>
+      <c r="E81" s="52"/>
+      <c r="F81" s="52"/>
+      <c r="G81" s="52"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="53">
+      <c r="A82" s="56">
         <v>46225</v>
       </c>
-      <c r="B82" s="49" t="s">
+      <c r="B82" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="49" t="s">
+      <c r="C82" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="49"/>
-      <c r="E82" s="49"/>
-      <c r="F82" s="49"/>
-      <c r="G82" s="49"/>
+      <c r="D82" s="52"/>
+      <c r="E82" s="52"/>
+      <c r="F82" s="52"/>
+      <c r="G82" s="52"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="53"/>
-      <c r="B83" s="49"/>
-      <c r="C83" s="49" t="s">
+      <c r="A83" s="56"/>
+      <c r="B83" s="52"/>
+      <c r="C83" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="49"/>
-      <c r="E83" s="49"/>
-      <c r="F83" s="49"/>
-      <c r="G83" s="49"/>
+      <c r="D83" s="52"/>
+      <c r="E83" s="52"/>
+      <c r="F83" s="52"/>
+      <c r="G83" s="52"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="53"/>
-      <c r="B84" s="49"/>
-      <c r="C84" s="49" t="s">
+      <c r="A84" s="56"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="49"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="49"/>
-      <c r="G84" s="49"/>
+      <c r="D84" s="52"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="52"/>
+      <c r="G84" s="52"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="53"/>
-      <c r="B85" s="49" t="s">
+      <c r="A85" s="56"/>
+      <c r="B85" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="49" t="s">
+      <c r="C85" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="49"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="49"/>
-      <c r="G85" s="49"/>
+      <c r="D85" s="52"/>
+      <c r="E85" s="52"/>
+      <c r="F85" s="52"/>
+      <c r="G85" s="52"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="53"/>
-      <c r="B86" s="49"/>
-      <c r="C86" s="49" t="s">
+      <c r="A86" s="56"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="49"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="49"/>
-      <c r="G86" s="49"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="53"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49" t="s">
+      <c r="A87" s="56"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="49"/>
-      <c r="G87" s="49"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="53"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49" t="s">
+      <c r="A88" s="56"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="53"/>
-      <c r="B89" s="49"/>
-      <c r="C89" s="54" t="s">
+      <c r="A89" s="56"/>
+      <c r="B89" s="52"/>
+      <c r="C89" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="55"/>
-      <c r="E89" s="55"/>
-      <c r="F89" s="55"/>
-      <c r="G89" s="56"/>
+      <c r="D89" s="58"/>
+      <c r="E89" s="58"/>
+      <c r="F89" s="58"/>
+      <c r="G89" s="59"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="53"/>
-      <c r="B90" s="49"/>
-      <c r="C90" s="49" t="s">
+      <c r="A90" s="56"/>
+      <c r="B90" s="52"/>
+      <c r="C90" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="49"/>
-      <c r="E90" s="49"/>
-      <c r="F90" s="49"/>
-      <c r="G90" s="49"/>
+      <c r="D90" s="52"/>
+      <c r="E90" s="52"/>
+      <c r="F90" s="52"/>
+      <c r="G90" s="52"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="62">
+      <c r="A91" s="65">
         <v>46227</v>
       </c>
-      <c r="B91" s="60" t="s">
+      <c r="B91" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="49" t="s">
+      <c r="C91" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="49"/>
-      <c r="E91" s="49"/>
-      <c r="F91" s="49"/>
-      <c r="G91" s="49"/>
+      <c r="D91" s="52"/>
+      <c r="E91" s="52"/>
+      <c r="F91" s="52"/>
+      <c r="G91" s="52"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="63"/>
-      <c r="B92" s="61"/>
-      <c r="C92" s="54" t="s">
+      <c r="A92" s="66"/>
+      <c r="B92" s="64"/>
+      <c r="C92" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="55"/>
-      <c r="E92" s="55"/>
-      <c r="F92" s="55"/>
-      <c r="G92" s="56"/>
+      <c r="D92" s="58"/>
+      <c r="E92" s="58"/>
+      <c r="F92" s="58"/>
+      <c r="G92" s="59"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="53">
+      <c r="A93" s="56">
         <v>46228</v>
       </c>
-      <c r="B93" s="49" t="s">
+      <c r="B93" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="49" t="s">
+      <c r="C93" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="49"/>
-      <c r="E93" s="49"/>
-      <c r="F93" s="49"/>
-      <c r="G93" s="49"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="52"/>
+      <c r="F93" s="52"/>
+      <c r="G93" s="52"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="53"/>
-      <c r="B94" s="49"/>
-      <c r="C94" s="49" t="s">
+      <c r="A94" s="56"/>
+      <c r="B94" s="52"/>
+      <c r="C94" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="49"/>
-      <c r="E94" s="49"/>
-      <c r="F94" s="49"/>
-      <c r="G94" s="49"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="52"/>
+      <c r="F94" s="52"/>
+      <c r="G94" s="52"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="53"/>
-      <c r="B95" s="49"/>
-      <c r="C95" s="49" t="s">
+      <c r="A95" s="56"/>
+      <c r="B95" s="52"/>
+      <c r="C95" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="49"/>
-      <c r="E95" s="49"/>
-      <c r="F95" s="49"/>
-      <c r="G95" s="49"/>
+      <c r="D95" s="52"/>
+      <c r="E95" s="52"/>
+      <c r="F95" s="52"/>
+      <c r="G95" s="52"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="53"/>
-      <c r="B96" s="49"/>
-      <c r="C96" s="49" t="s">
+      <c r="A96" s="56"/>
+      <c r="B96" s="52"/>
+      <c r="C96" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="49"/>
-      <c r="E96" s="49"/>
-      <c r="F96" s="49"/>
-      <c r="G96" s="49"/>
+      <c r="D96" s="52"/>
+      <c r="E96" s="52"/>
+      <c r="F96" s="52"/>
+      <c r="G96" s="52"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="53"/>
-      <c r="B97" s="49"/>
-      <c r="C97" s="49" t="s">
+      <c r="A97" s="56"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="49"/>
-      <c r="E97" s="49"/>
-      <c r="F97" s="49"/>
-      <c r="G97" s="49"/>
+      <c r="D97" s="52"/>
+      <c r="E97" s="52"/>
+      <c r="F97" s="52"/>
+      <c r="G97" s="52"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="53"/>
-      <c r="B98" s="49"/>
-      <c r="C98" s="49" t="s">
+      <c r="A98" s="56"/>
+      <c r="B98" s="52"/>
+      <c r="C98" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="49"/>
-      <c r="E98" s="49"/>
-      <c r="F98" s="49"/>
-      <c r="G98" s="49"/>
+      <c r="D98" s="52"/>
+      <c r="E98" s="52"/>
+      <c r="F98" s="52"/>
+      <c r="G98" s="52"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="53">
+      <c r="A99" s="56">
         <v>46230</v>
       </c>
-      <c r="B99" s="49" t="s">
+      <c r="B99" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="49" t="s">
+      <c r="C99" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="49"/>
-      <c r="E99" s="49"/>
-      <c r="F99" s="49"/>
-      <c r="G99" s="49"/>
+      <c r="D99" s="52"/>
+      <c r="E99" s="52"/>
+      <c r="F99" s="52"/>
+      <c r="G99" s="52"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="53"/>
-      <c r="B100" s="49"/>
-      <c r="C100" s="49" t="s">
+      <c r="A100" s="56"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="49"/>
-      <c r="E100" s="49"/>
-      <c r="F100" s="49"/>
-      <c r="G100" s="49"/>
+      <c r="D100" s="52"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="53">
+      <c r="A101" s="56">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="59" t="s">
+      <c r="C101" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="59"/>
-      <c r="E101" s="59"/>
-      <c r="F101" s="59"/>
-      <c r="G101" s="59"/>
+      <c r="D101" s="62"/>
+      <c r="E101" s="62"/>
+      <c r="F101" s="62"/>
+      <c r="G101" s="62"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="53"/>
+      <c r="A102" s="56"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="59" t="s">
+      <c r="C102" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="59"/>
-      <c r="E102" s="59"/>
-      <c r="F102" s="59"/>
-      <c r="G102" s="59"/>
+      <c r="D102" s="62"/>
+      <c r="E102" s="62"/>
+      <c r="F102" s="62"/>
+      <c r="G102" s="62"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="57" t="s">
+      <c r="A103" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="49" t="s">
+      <c r="B103" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="58" t="s">
+      <c r="C103" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="58"/>
-      <c r="E103" s="58"/>
-      <c r="F103" s="58"/>
-      <c r="G103" s="58"/>
+      <c r="D103" s="61"/>
+      <c r="E103" s="61"/>
+      <c r="F103" s="61"/>
+      <c r="G103" s="61"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="57"/>
-      <c r="B104" s="49"/>
-      <c r="C104" s="49" t="s">
+      <c r="A104" s="60"/>
+      <c r="B104" s="52"/>
+      <c r="C104" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="49"/>
-      <c r="E104" s="49"/>
-      <c r="F104" s="49"/>
-      <c r="G104" s="49"/>
+      <c r="D104" s="52"/>
+      <c r="E104" s="52"/>
+      <c r="F104" s="52"/>
+      <c r="G104" s="52"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="57"/>
-      <c r="B105" s="49"/>
-      <c r="C105" s="49" t="s">
+      <c r="A105" s="60"/>
+      <c r="B105" s="52"/>
+      <c r="C105" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="49"/>
-      <c r="E105" s="49"/>
-      <c r="F105" s="49"/>
-      <c r="G105" s="49"/>
+      <c r="D105" s="52"/>
+      <c r="E105" s="52"/>
+      <c r="F105" s="52"/>
+      <c r="G105" s="52"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="57"/>
-      <c r="B106" s="49"/>
-      <c r="C106" s="49" t="s">
+      <c r="A106" s="60"/>
+      <c r="B106" s="52"/>
+      <c r="C106" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="49"/>
-      <c r="E106" s="49"/>
-      <c r="F106" s="49"/>
-      <c r="G106" s="49"/>
+      <c r="D106" s="52"/>
+      <c r="E106" s="52"/>
+      <c r="F106" s="52"/>
+      <c r="G106" s="52"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="57"/>
-      <c r="B107" s="49"/>
-      <c r="C107" s="49" t="s">
+      <c r="A107" s="60"/>
+      <c r="B107" s="52"/>
+      <c r="C107" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="49"/>
-      <c r="E107" s="49"/>
-      <c r="F107" s="49"/>
-      <c r="G107" s="49"/>
+      <c r="D107" s="52"/>
+      <c r="E107" s="52"/>
+      <c r="F107" s="52"/>
+      <c r="G107" s="52"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="53">
+      <c r="A108" s="56">
         <v>46234</v>
       </c>
-      <c r="B108" s="49" t="s">
+      <c r="B108" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C108" s="49" t="s">
+      <c r="C108" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="49"/>
-      <c r="E108" s="49"/>
-      <c r="F108" s="49"/>
-      <c r="G108" s="49"/>
+      <c r="D108" s="52"/>
+      <c r="E108" s="52"/>
+      <c r="F108" s="52"/>
+      <c r="G108" s="52"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="53"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="49" t="s">
+      <c r="A109" s="56"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="49"/>
-      <c r="E109" s="49"/>
-      <c r="F109" s="49"/>
-      <c r="G109" s="49"/>
+      <c r="D109" s="52"/>
+      <c r="E109" s="52"/>
+      <c r="F109" s="52"/>
+      <c r="G109" s="52"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2798,7 +2840,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E5051E-34BB-454A-9E98-0A0156A4405B}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="14" bestFit="1" customWidth="1"/>
@@ -2808,15 +2850,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="69">
+      <c r="A1" s="72">
         <v>46235</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3004,7 +3046,7 @@
       <c r="F16" s="34"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="21"/>
       <c r="B17" s="42"/>
       <c r="C17" s="39" t="s">
@@ -3014,6 +3056,106 @@
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
       <c r="G17" s="40"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="33">
+        <v>46244</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="26"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
+        <v>46245</v>
+      </c>
+      <c r="B20" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="78"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="80"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="46"/>
+      <c r="B22" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="78"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="46"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="82"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="82"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="45"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC7E068-B783-4E5D-B583-1DC9108554EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D142825-4500-4EF6-BE48-5D1772AB7328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="125">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>Nhận BH HTA</t>
+  </si>
+  <si>
+    <t>Nhập kho 23 LE UPG</t>
   </si>
 </sst>
 </file>
@@ -737,6 +740,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -752,99 +794,58 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1167,15 +1168,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="47">
+      <c r="A1" s="60">
         <v>46174</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1184,91 +1185,91 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="51"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="64"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="56">
+      <c r="A3" s="55">
         <v>46202</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="56"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52" t="s">
+      <c r="A4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="56"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52" t="s">
+      <c r="A5" s="55"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="56"/>
-      <c r="B6" s="52" t="s">
+      <c r="A6" s="55"/>
+      <c r="B6" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="56"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52" t="s">
+      <c r="A7" s="55"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="56"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="56">
+      <c r="A9" s="55">
         <v>46203</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="56" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="57" t="s">
@@ -1280,50 +1281,50 @@
       <c r="G9" s="59"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="56"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="53" t="s">
+      <c r="A10" s="55"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="55"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="54"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="56"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="53" t="s">
+      <c r="A11" s="55"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="55"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="54"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="56"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="53" t="s">
+      <c r="A12" s="55"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="55"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="54"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="56"/>
+      <c r="A13" s="55"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="55"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1333,14 +1334,6 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1351,6 +1344,14 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1368,15 +1369,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="72">
+      <c r="A1" s="68">
         <v>46204</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1385,69 +1386,69 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="56">
+      <c r="A3" s="55">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="56"/>
-      <c r="B4" s="52" t="s">
+      <c r="A4" s="55"/>
+      <c r="B4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="56"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52" t="s">
+      <c r="A5" s="55"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="56"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52" t="s">
+      <c r="A6" s="55"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="74">
+      <c r="A7" s="71">
         <v>46205</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="65" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="57" t="s">
@@ -1459,78 +1460,78 @@
       <c r="G7" s="59"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="75"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="53" t="s">
+      <c r="A8" s="72"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="55"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="54"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="75"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="53" t="s">
+      <c r="A9" s="72"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="55"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="54"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
-      <c r="B10" s="52" t="s">
+      <c r="A10" s="72"/>
+      <c r="B10" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="55"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="54"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="75"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="53" t="s">
+      <c r="A11" s="72"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="55"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="54"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="75"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="53" t="s">
+      <c r="A12" s="72"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="55"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="54"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="76"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="53" t="s">
+      <c r="A13" s="73"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="55"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="65">
+      <c r="A14" s="75">
         <v>46206</v>
       </c>
-      <c r="B14" s="63" t="s">
+      <c r="B14" s="65" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1542,8 +1543,8 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="68"/>
-      <c r="B15" s="71"/>
+      <c r="A15" s="76"/>
+      <c r="B15" s="67"/>
       <c r="C15" s="57" t="s">
         <v>26</v>
       </c>
@@ -1553,8 +1554,8 @@
       <c r="G15" s="59"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="68"/>
-      <c r="B16" s="71"/>
+      <c r="A16" s="76"/>
+      <c r="B16" s="67"/>
       <c r="C16" s="57" t="s">
         <v>28</v>
       </c>
@@ -1564,8 +1565,8 @@
       <c r="G16" s="59"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="68"/>
-      <c r="B17" s="64"/>
+      <c r="A17" s="76"/>
+      <c r="B17" s="66"/>
       <c r="C17" s="57" t="s">
         <v>27</v>
       </c>
@@ -1575,8 +1576,8 @@
       <c r="G17" s="59"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="68"/>
-      <c r="B18" s="63" t="s">
+      <c r="A18" s="76"/>
+      <c r="B18" s="65" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="57" t="s">
@@ -1588,8 +1589,8 @@
       <c r="G18" s="59"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="66"/>
-      <c r="B19" s="64"/>
+      <c r="A19" s="77"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="57" t="s">
         <v>31</v>
       </c>
@@ -1599,58 +1600,58 @@
       <c r="G19" s="59"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="69">
+      <c r="A20" s="78">
         <v>46209</v>
       </c>
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="69"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52" t="s">
+      <c r="A21" s="78"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="69"/>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52" t="s">
+      <c r="A22" s="78"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="69"/>
-      <c r="B23" s="52" t="s">
+      <c r="A23" s="78"/>
+      <c r="B23" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="69"/>
-      <c r="B24" s="52"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="56"/>
       <c r="C24" s="57" t="s">
         <v>35</v>
       </c>
@@ -1660,8 +1661,8 @@
       <c r="G24" s="59"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="69"/>
-      <c r="B25" s="52"/>
+      <c r="A25" s="78"/>
+      <c r="B25" s="56"/>
       <c r="C25" s="57" t="s">
         <v>36</v>
       </c>
@@ -1671,8 +1672,8 @@
       <c r="G25" s="59"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="69"/>
-      <c r="B26" s="52"/>
+      <c r="A26" s="78"/>
+      <c r="B26" s="56"/>
       <c r="C26" s="57" t="s">
         <v>37</v>
       </c>
@@ -1682,8 +1683,8 @@
       <c r="G26" s="59"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="69"/>
-      <c r="B27" s="52"/>
+      <c r="A27" s="78"/>
+      <c r="B27" s="56"/>
       <c r="C27" s="57" t="s">
         <v>38</v>
       </c>
@@ -1693,8 +1694,8 @@
       <c r="G27" s="59"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="69"/>
-      <c r="B28" s="52"/>
+      <c r="A28" s="78"/>
+      <c r="B28" s="56"/>
       <c r="C28" s="57" t="s">
         <v>39</v>
       </c>
@@ -1704,8 +1705,8 @@
       <c r="G28" s="59"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="69"/>
-      <c r="B29" s="52"/>
+      <c r="A29" s="78"/>
+      <c r="B29" s="56"/>
       <c r="C29" s="57" t="s">
         <v>40</v>
       </c>
@@ -1715,8 +1716,8 @@
       <c r="G29" s="59"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="69"/>
-      <c r="B30" s="52"/>
+      <c r="A30" s="78"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="57" t="s">
         <v>45</v>
       </c>
@@ -1726,8 +1727,8 @@
       <c r="G30" s="59"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="69"/>
-      <c r="B31" s="52"/>
+      <c r="A31" s="78"/>
+      <c r="B31" s="56"/>
       <c r="C31" s="57" t="s">
         <v>41</v>
       </c>
@@ -1737,8 +1738,8 @@
       <c r="G31" s="59"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="69"/>
-      <c r="B32" s="52"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="56"/>
       <c r="C32" s="57" t="s">
         <v>42</v>
       </c>
@@ -1748,8 +1749,8 @@
       <c r="G32" s="59"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="69"/>
-      <c r="B33" s="52"/>
+      <c r="A33" s="78"/>
+      <c r="B33" s="56"/>
       <c r="C33" s="57" t="s">
         <v>43</v>
       </c>
@@ -1759,8 +1760,8 @@
       <c r="G33" s="59"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="69"/>
-      <c r="B34" s="52"/>
+      <c r="A34" s="78"/>
+      <c r="B34" s="56"/>
       <c r="C34" s="57" t="s">
         <v>44</v>
       </c>
@@ -1770,113 +1771,113 @@
       <c r="G34" s="59"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="67">
+      <c r="A35" s="74">
         <v>46210</v>
       </c>
-      <c r="B35" s="52" t="s">
+      <c r="B35" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="52" t="s">
+      <c r="C35" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="67"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52" t="s">
+      <c r="A36" s="74"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="67"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52" t="s">
+      <c r="A37" s="74"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="67"/>
-      <c r="B38" s="52" t="s">
+      <c r="A38" s="74"/>
+      <c r="B38" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="52" t="s">
+      <c r="C38" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="67"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52" t="s">
+      <c r="A39" s="74"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="67"/>
-      <c r="B40" s="52"/>
-      <c r="C40" s="52" t="s">
+      <c r="A40" s="74"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="67"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="52" t="s">
+      <c r="A41" s="74"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="52"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="67"/>
-      <c r="B42" s="52"/>
-      <c r="C42" s="52" t="s">
+      <c r="A42" s="74"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="67"/>
-      <c r="B43" s="52"/>
-      <c r="C43" s="52" t="s">
+      <c r="A43" s="74"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="52"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="67"/>
-      <c r="B44" s="52"/>
+      <c r="A44" s="74"/>
+      <c r="B44" s="56"/>
       <c r="C44" s="57" t="s">
         <v>54</v>
       </c>
@@ -1892,13 +1893,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="52" t="s">
+      <c r="C45" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="52"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1907,19 +1908,19 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="52" t="s">
+      <c r="C46" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="65">
+      <c r="A47" s="75">
         <v>46213</v>
       </c>
-      <c r="B47" s="63" t="s">
+      <c r="B47" s="65" t="s">
         <v>4</v>
       </c>
       <c r="C47" s="57" t="s">
@@ -1931,8 +1932,8 @@
       <c r="G47" s="59"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="68"/>
-      <c r="B48" s="71"/>
+      <c r="A48" s="76"/>
+      <c r="B48" s="67"/>
       <c r="C48" s="57" t="s">
         <v>57</v>
       </c>
@@ -1942,8 +1943,8 @@
       <c r="G48" s="59"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="68"/>
-      <c r="B49" s="71"/>
+      <c r="A49" s="76"/>
+      <c r="B49" s="67"/>
       <c r="C49" s="57" t="s">
         <v>58</v>
       </c>
@@ -1953,8 +1954,8 @@
       <c r="G49" s="59"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="68"/>
-      <c r="B50" s="71"/>
+      <c r="A50" s="76"/>
+      <c r="B50" s="67"/>
       <c r="C50" s="57" t="s">
         <v>60</v>
       </c>
@@ -1964,8 +1965,8 @@
       <c r="G50" s="59"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="66"/>
-      <c r="B51" s="64"/>
+      <c r="A51" s="77"/>
+      <c r="B51" s="66"/>
       <c r="C51" s="57" t="s">
         <v>61</v>
       </c>
@@ -1975,35 +1976,35 @@
       <c r="G51" s="59"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="56">
+      <c r="A52" s="55">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="52" t="s">
+      <c r="C52" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="56"/>
+      <c r="A53" s="55"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="52" t="s">
+      <c r="C53" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="56">
+      <c r="A54" s="55">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -2018,144 +2019,144 @@
       <c r="G54" s="59"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="56"/>
-      <c r="B55" s="52" t="s">
+      <c r="A55" s="55"/>
+      <c r="B55" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="70" t="s">
+      <c r="C55" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
+      <c r="D55" s="79"/>
+      <c r="E55" s="79"/>
+      <c r="F55" s="79"/>
+      <c r="G55" s="79"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="56"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="70" t="s">
+      <c r="A56" s="55"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="70"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
+      <c r="D56" s="79"/>
+      <c r="E56" s="79"/>
+      <c r="F56" s="79"/>
+      <c r="G56" s="79"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="56"/>
-      <c r="B57" s="52"/>
-      <c r="C57" s="70" t="s">
+      <c r="A57" s="55"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="70"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="70"/>
-      <c r="G57" s="70"/>
+      <c r="D57" s="79"/>
+      <c r="E57" s="79"/>
+      <c r="F57" s="79"/>
+      <c r="G57" s="79"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="56"/>
-      <c r="B58" s="52"/>
-      <c r="C58" s="70" t="s">
+      <c r="A58" s="55"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="70"/>
-      <c r="E58" s="70"/>
-      <c r="F58" s="70"/>
-      <c r="G58" s="70"/>
+      <c r="D58" s="79"/>
+      <c r="E58" s="79"/>
+      <c r="F58" s="79"/>
+      <c r="G58" s="79"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="56"/>
-      <c r="B59" s="52"/>
-      <c r="C59" s="70" t="s">
+      <c r="A59" s="55"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="70"/>
-      <c r="E59" s="70"/>
-      <c r="F59" s="70"/>
-      <c r="G59" s="70"/>
+      <c r="D59" s="79"/>
+      <c r="E59" s="79"/>
+      <c r="F59" s="79"/>
+      <c r="G59" s="79"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="56"/>
-      <c r="B60" s="52"/>
-      <c r="C60" s="70" t="s">
+      <c r="A60" s="55"/>
+      <c r="B60" s="56"/>
+      <c r="C60" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="70"/>
-      <c r="E60" s="70"/>
-      <c r="F60" s="70"/>
-      <c r="G60" s="70"/>
+      <c r="D60" s="79"/>
+      <c r="E60" s="79"/>
+      <c r="F60" s="79"/>
+      <c r="G60" s="79"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="56"/>
-      <c r="B61" s="52"/>
-      <c r="C61" s="70" t="s">
+      <c r="A61" s="55"/>
+      <c r="B61" s="56"/>
+      <c r="C61" s="79" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="70"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="70"/>
+      <c r="D61" s="79"/>
+      <c r="E61" s="79"/>
+      <c r="F61" s="79"/>
+      <c r="G61" s="79"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="56"/>
-      <c r="B62" s="52"/>
-      <c r="C62" s="70" t="s">
+      <c r="A62" s="55"/>
+      <c r="B62" s="56"/>
+      <c r="C62" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="70"/>
-      <c r="E62" s="70"/>
-      <c r="F62" s="70"/>
-      <c r="G62" s="70"/>
+      <c r="D62" s="79"/>
+      <c r="E62" s="79"/>
+      <c r="F62" s="79"/>
+      <c r="G62" s="79"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="56"/>
-      <c r="B63" s="52"/>
-      <c r="C63" s="70" t="s">
+      <c r="A63" s="55"/>
+      <c r="B63" s="56"/>
+      <c r="C63" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="70"/>
-      <c r="E63" s="70"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="70"/>
+      <c r="D63" s="79"/>
+      <c r="E63" s="79"/>
+      <c r="F63" s="79"/>
+      <c r="G63" s="79"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="56">
+      <c r="A64" s="55">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="52" t="s">
+      <c r="C64" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="52"/>
-      <c r="E64" s="52"/>
-      <c r="F64" s="52"/>
-      <c r="G64" s="52"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="56"/>
-      <c r="B65" s="52" t="s">
+      <c r="A65" s="55"/>
+      <c r="B65" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="52" t="s">
+      <c r="C65" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="56"/>
+      <c r="F65" s="56"/>
+      <c r="G65" s="56"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="56"/>
-      <c r="B66" s="52"/>
-      <c r="C66" s="52" t="s">
+      <c r="A66" s="55"/>
+      <c r="B66" s="56"/>
+      <c r="C66" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="52"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="52"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="56"/>
+      <c r="F66" s="56"/>
+      <c r="G66" s="56"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2164,45 +2165,45 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="52" t="s">
+      <c r="C67" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="52"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="52"/>
-      <c r="G67" s="52"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="56"/>
+      <c r="F67" s="56"/>
+      <c r="G67" s="56"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="56">
+      <c r="A68" s="55">
         <v>46220</v>
       </c>
-      <c r="B68" s="52" t="s">
+      <c r="B68" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="52" t="s">
+      <c r="C68" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="52"/>
-      <c r="E68" s="52"/>
-      <c r="F68" s="52"/>
-      <c r="G68" s="52"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="56"/>
+      <c r="F68" s="56"/>
+      <c r="G68" s="56"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="56"/>
-      <c r="B69" s="52"/>
-      <c r="C69" s="52" t="s">
+      <c r="A69" s="55"/>
+      <c r="B69" s="56"/>
+      <c r="C69" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="52"/>
-      <c r="E69" s="52"/>
-      <c r="F69" s="52"/>
-      <c r="G69" s="52"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="56"/>
+      <c r="F69" s="56"/>
+      <c r="G69" s="56"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="56">
+      <c r="A70" s="55">
         <v>46223</v>
       </c>
-      <c r="B70" s="52" t="s">
+      <c r="B70" s="56" t="s">
         <v>4</v>
       </c>
       <c r="C70" s="57" t="s">
@@ -2214,8 +2215,8 @@
       <c r="G70" s="59"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="56"/>
-      <c r="B71" s="52"/>
+      <c r="A71" s="55"/>
+      <c r="B71" s="56"/>
       <c r="C71" s="57" t="s">
         <v>79</v>
       </c>
@@ -2225,8 +2226,8 @@
       <c r="G71" s="59"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="56"/>
-      <c r="B72" s="52"/>
+      <c r="A72" s="55"/>
+      <c r="B72" s="56"/>
       <c r="C72" s="57" t="s">
         <v>80</v>
       </c>
@@ -2236,8 +2237,8 @@
       <c r="G72" s="59"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="56"/>
-      <c r="B73" s="52"/>
+      <c r="A73" s="55"/>
+      <c r="B73" s="56"/>
       <c r="C73" s="57" t="s">
         <v>81</v>
       </c>
@@ -2247,8 +2248,8 @@
       <c r="G73" s="59"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="56"/>
-      <c r="B74" s="52"/>
+      <c r="A74" s="55"/>
+      <c r="B74" s="56"/>
       <c r="C74" s="57" t="s">
         <v>39</v>
       </c>
@@ -2258,8 +2259,8 @@
       <c r="G74" s="59"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="56"/>
-      <c r="B75" s="52"/>
+      <c r="A75" s="55"/>
+      <c r="B75" s="56"/>
       <c r="C75" s="57" t="s">
         <v>82</v>
       </c>
@@ -2269,8 +2270,8 @@
       <c r="G75" s="59"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="56"/>
-      <c r="B76" s="52"/>
+      <c r="A76" s="55"/>
+      <c r="B76" s="56"/>
       <c r="C76" s="57" t="s">
         <v>72</v>
       </c>
@@ -2280,48 +2281,48 @@
       <c r="G76" s="59"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="56"/>
-      <c r="B77" s="52"/>
-      <c r="C77" s="53" t="s">
+      <c r="A77" s="55"/>
+      <c r="B77" s="56"/>
+      <c r="C77" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="54"/>
-      <c r="E77" s="54"/>
-      <c r="F77" s="54"/>
-      <c r="G77" s="55"/>
+      <c r="D77" s="53"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="54"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="56"/>
-      <c r="B78" s="52"/>
-      <c r="C78" s="53" t="s">
+      <c r="A78" s="55"/>
+      <c r="B78" s="56"/>
+      <c r="C78" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="54"/>
-      <c r="E78" s="54"/>
-      <c r="F78" s="54"/>
-      <c r="G78" s="55"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="54"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="56"/>
-      <c r="B79" s="52"/>
-      <c r="C79" s="53" t="s">
+      <c r="A79" s="55"/>
+      <c r="B79" s="56"/>
+      <c r="C79" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="54"/>
-      <c r="E79" s="54"/>
-      <c r="F79" s="54"/>
-      <c r="G79" s="55"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="54"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="56"/>
-      <c r="B80" s="52"/>
-      <c r="C80" s="53" t="s">
+      <c r="A80" s="55"/>
+      <c r="B80" s="56"/>
+      <c r="C80" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="54"/>
-      <c r="E80" s="54"/>
-      <c r="F80" s="54"/>
-      <c r="G80" s="55"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="54"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2330,100 +2331,100 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="52" t="s">
+      <c r="C81" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="52"/>
-      <c r="G81" s="52"/>
+      <c r="D81" s="56"/>
+      <c r="E81" s="56"/>
+      <c r="F81" s="56"/>
+      <c r="G81" s="56"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="56">
+      <c r="A82" s="55">
         <v>46225</v>
       </c>
-      <c r="B82" s="52" t="s">
+      <c r="B82" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="52" t="s">
+      <c r="C82" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="52"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="52"/>
-      <c r="G82" s="52"/>
+      <c r="D82" s="56"/>
+      <c r="E82" s="56"/>
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="56"/>
-      <c r="B83" s="52"/>
-      <c r="C83" s="52" t="s">
+      <c r="A83" s="55"/>
+      <c r="B83" s="56"/>
+      <c r="C83" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="52"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="52"/>
-      <c r="G83" s="52"/>
+      <c r="D83" s="56"/>
+      <c r="E83" s="56"/>
+      <c r="F83" s="56"/>
+      <c r="G83" s="56"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="56"/>
-      <c r="B84" s="52"/>
-      <c r="C84" s="52" t="s">
+      <c r="A84" s="55"/>
+      <c r="B84" s="56"/>
+      <c r="C84" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="52"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="52"/>
-      <c r="G84" s="52"/>
+      <c r="D84" s="56"/>
+      <c r="E84" s="56"/>
+      <c r="F84" s="56"/>
+      <c r="G84" s="56"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="56"/>
-      <c r="B85" s="52" t="s">
+      <c r="A85" s="55"/>
+      <c r="B85" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="52" t="s">
+      <c r="C85" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="52"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="52"/>
-      <c r="G85" s="52"/>
+      <c r="D85" s="56"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="56"/>
-      <c r="B86" s="52"/>
-      <c r="C86" s="52" t="s">
+      <c r="A86" s="55"/>
+      <c r="B86" s="56"/>
+      <c r="C86" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="52"/>
+      <c r="D86" s="56"/>
+      <c r="E86" s="56"/>
+      <c r="F86" s="56"/>
+      <c r="G86" s="56"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="56"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52" t="s">
+      <c r="A87" s="55"/>
+      <c r="B87" s="56"/>
+      <c r="C87" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
+      <c r="D87" s="56"/>
+      <c r="E87" s="56"/>
+      <c r="F87" s="56"/>
+      <c r="G87" s="56"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="56"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52" t="s">
+      <c r="A88" s="55"/>
+      <c r="B88" s="56"/>
+      <c r="C88" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
+      <c r="D88" s="56"/>
+      <c r="E88" s="56"/>
+      <c r="F88" s="56"/>
+      <c r="G88" s="56"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="56"/>
-      <c r="B89" s="52"/>
+      <c r="A89" s="55"/>
+      <c r="B89" s="56"/>
       <c r="C89" s="57" t="s">
         <v>39</v>
       </c>
@@ -2433,34 +2434,34 @@
       <c r="G89" s="59"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="56"/>
-      <c r="B90" s="52"/>
-      <c r="C90" s="52" t="s">
+      <c r="A90" s="55"/>
+      <c r="B90" s="56"/>
+      <c r="C90" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="52"/>
-      <c r="E90" s="52"/>
-      <c r="F90" s="52"/>
-      <c r="G90" s="52"/>
+      <c r="D90" s="56"/>
+      <c r="E90" s="56"/>
+      <c r="F90" s="56"/>
+      <c r="G90" s="56"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="65">
+      <c r="A91" s="75">
         <v>46227</v>
       </c>
-      <c r="B91" s="63" t="s">
+      <c r="B91" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="52" t="s">
+      <c r="C91" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="52"/>
-      <c r="E91" s="52"/>
-      <c r="F91" s="52"/>
-      <c r="G91" s="52"/>
+      <c r="D91" s="56"/>
+      <c r="E91" s="56"/>
+      <c r="F91" s="56"/>
+      <c r="G91" s="56"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="66"/>
-      <c r="B92" s="64"/>
+      <c r="A92" s="77"/>
+      <c r="B92" s="66"/>
       <c r="C92" s="57" t="s">
         <v>95</v>
       </c>
@@ -2470,213 +2471,213 @@
       <c r="G92" s="59"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="56">
+      <c r="A93" s="55">
         <v>46228</v>
       </c>
-      <c r="B93" s="52" t="s">
+      <c r="B93" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="52" t="s">
+      <c r="C93" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="52"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="52"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="56"/>
+      <c r="F93" s="56"/>
+      <c r="G93" s="56"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="56"/>
-      <c r="B94" s="52"/>
-      <c r="C94" s="52" t="s">
+      <c r="A94" s="55"/>
+      <c r="B94" s="56"/>
+      <c r="C94" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="52"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="52"/>
-      <c r="G94" s="52"/>
+      <c r="D94" s="56"/>
+      <c r="E94" s="56"/>
+      <c r="F94" s="56"/>
+      <c r="G94" s="56"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="56"/>
-      <c r="B95" s="52"/>
-      <c r="C95" s="52" t="s">
+      <c r="A95" s="55"/>
+      <c r="B95" s="56"/>
+      <c r="C95" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="52"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="56"/>
+      <c r="F95" s="56"/>
+      <c r="G95" s="56"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="56"/>
-      <c r="B96" s="52"/>
-      <c r="C96" s="52" t="s">
+      <c r="A96" s="55"/>
+      <c r="B96" s="56"/>
+      <c r="C96" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="52"/>
-      <c r="E96" s="52"/>
-      <c r="F96" s="52"/>
-      <c r="G96" s="52"/>
+      <c r="D96" s="56"/>
+      <c r="E96" s="56"/>
+      <c r="F96" s="56"/>
+      <c r="G96" s="56"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="56"/>
-      <c r="B97" s="52"/>
-      <c r="C97" s="52" t="s">
+      <c r="A97" s="55"/>
+      <c r="B97" s="56"/>
+      <c r="C97" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="52"/>
-      <c r="E97" s="52"/>
-      <c r="F97" s="52"/>
-      <c r="G97" s="52"/>
+      <c r="D97" s="56"/>
+      <c r="E97" s="56"/>
+      <c r="F97" s="56"/>
+      <c r="G97" s="56"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="56"/>
-      <c r="B98" s="52"/>
-      <c r="C98" s="52" t="s">
+      <c r="A98" s="55"/>
+      <c r="B98" s="56"/>
+      <c r="C98" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="52"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="52"/>
+      <c r="D98" s="56"/>
+      <c r="E98" s="56"/>
+      <c r="F98" s="56"/>
+      <c r="G98" s="56"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="56">
+      <c r="A99" s="55">
         <v>46230</v>
       </c>
-      <c r="B99" s="52" t="s">
+      <c r="B99" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="52" t="s">
+      <c r="C99" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="52"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="52"/>
-      <c r="G99" s="52"/>
+      <c r="D99" s="56"/>
+      <c r="E99" s="56"/>
+      <c r="F99" s="56"/>
+      <c r="G99" s="56"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="56"/>
-      <c r="B100" s="52"/>
-      <c r="C100" s="52" t="s">
+      <c r="A100" s="55"/>
+      <c r="B100" s="56"/>
+      <c r="C100" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="52"/>
-      <c r="E100" s="52"/>
-      <c r="F100" s="52"/>
-      <c r="G100" s="52"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="56"/>
+      <c r="F100" s="56"/>
+      <c r="G100" s="56"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="56">
+      <c r="A101" s="55">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="62" t="s">
+      <c r="C101" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="62"/>
-      <c r="E101" s="62"/>
-      <c r="F101" s="62"/>
-      <c r="G101" s="62"/>
+      <c r="D101" s="81"/>
+      <c r="E101" s="81"/>
+      <c r="F101" s="81"/>
+      <c r="G101" s="81"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="56"/>
+      <c r="A102" s="55"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="62" t="s">
+      <c r="C102" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="62"/>
-      <c r="E102" s="62"/>
-      <c r="F102" s="62"/>
-      <c r="G102" s="62"/>
+      <c r="D102" s="81"/>
+      <c r="E102" s="81"/>
+      <c r="F102" s="81"/>
+      <c r="G102" s="81"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="60" t="s">
+      <c r="A103" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="52" t="s">
+      <c r="B103" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="61" t="s">
+      <c r="C103" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="61"/>
-      <c r="E103" s="61"/>
-      <c r="F103" s="61"/>
-      <c r="G103" s="61"/>
+      <c r="D103" s="70"/>
+      <c r="E103" s="70"/>
+      <c r="F103" s="70"/>
+      <c r="G103" s="70"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="60"/>
-      <c r="B104" s="52"/>
-      <c r="C104" s="52" t="s">
+      <c r="A104" s="80"/>
+      <c r="B104" s="56"/>
+      <c r="C104" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="52"/>
-      <c r="E104" s="52"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="52"/>
+      <c r="D104" s="56"/>
+      <c r="E104" s="56"/>
+      <c r="F104" s="56"/>
+      <c r="G104" s="56"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="60"/>
-      <c r="B105" s="52"/>
-      <c r="C105" s="52" t="s">
+      <c r="A105" s="80"/>
+      <c r="B105" s="56"/>
+      <c r="C105" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="52"/>
-      <c r="E105" s="52"/>
-      <c r="F105" s="52"/>
-      <c r="G105" s="52"/>
+      <c r="D105" s="56"/>
+      <c r="E105" s="56"/>
+      <c r="F105" s="56"/>
+      <c r="G105" s="56"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="60"/>
-      <c r="B106" s="52"/>
-      <c r="C106" s="52" t="s">
+      <c r="A106" s="80"/>
+      <c r="B106" s="56"/>
+      <c r="C106" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="52"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52"/>
-      <c r="G106" s="52"/>
+      <c r="D106" s="56"/>
+      <c r="E106" s="56"/>
+      <c r="F106" s="56"/>
+      <c r="G106" s="56"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="60"/>
-      <c r="B107" s="52"/>
-      <c r="C107" s="52" t="s">
+      <c r="A107" s="80"/>
+      <c r="B107" s="56"/>
+      <c r="C107" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="52"/>
-      <c r="E107" s="52"/>
-      <c r="F107" s="52"/>
-      <c r="G107" s="52"/>
+      <c r="D107" s="56"/>
+      <c r="E107" s="56"/>
+      <c r="F107" s="56"/>
+      <c r="G107" s="56"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="56">
+      <c r="A108" s="55">
         <v>46234</v>
       </c>
-      <c r="B108" s="52" t="s">
+      <c r="B108" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C108" s="52" t="s">
+      <c r="C108" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="52"/>
-      <c r="E108" s="52"/>
-      <c r="F108" s="52"/>
-      <c r="G108" s="52"/>
+      <c r="D108" s="56"/>
+      <c r="E108" s="56"/>
+      <c r="F108" s="56"/>
+      <c r="G108" s="56"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="56"/>
-      <c r="B109" s="52"/>
-      <c r="C109" s="52" t="s">
+      <c r="A109" s="55"/>
+      <c r="B109" s="56"/>
+      <c r="C109" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="52"/>
-      <c r="E109" s="52"/>
-      <c r="F109" s="52"/>
-      <c r="G109" s="52"/>
+      <c r="D109" s="56"/>
+      <c r="E109" s="56"/>
+      <c r="F109" s="56"/>
+      <c r="G109" s="56"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2686,6 +2687,129 @@
     </row>
   </sheetData>
   <mergeCells count="147">
+    <mergeCell ref="A103:A107"/>
+    <mergeCell ref="B103:B107"/>
+    <mergeCell ref="C103:G103"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C107:G107"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:G99"/>
+    <mergeCell ref="C100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="C93:G93"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="C91:G91"/>
+    <mergeCell ref="C92:G92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A82:A90"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C89:G89"/>
+    <mergeCell ref="C82:G82"/>
+    <mergeCell ref="C83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="C85:G85"/>
+    <mergeCell ref="C86:G86"/>
+    <mergeCell ref="C87:G87"/>
+    <mergeCell ref="C88:G88"/>
+    <mergeCell ref="C90:G90"/>
+    <mergeCell ref="B85:B90"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="C69:G69"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="C65:G65"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="C64:G64"/>
+    <mergeCell ref="C81:G81"/>
+    <mergeCell ref="B70:B80"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="C70:G70"/>
+    <mergeCell ref="C71:G71"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="C73:G73"/>
+    <mergeCell ref="C74:G74"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="C77:G77"/>
+    <mergeCell ref="C78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A20:A34"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="A54:A63"/>
+    <mergeCell ref="B55:B63"/>
+    <mergeCell ref="C55:G55"/>
+    <mergeCell ref="C56:G56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="C61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="C63:G63"/>
+    <mergeCell ref="C54:G54"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="C53:G53"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="B108:B109"/>
     <mergeCell ref="C108:G108"/>
@@ -2710,129 +2834,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C40:G40"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="C53:G53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A35:A44"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="A20:A34"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="B55:B63"/>
-    <mergeCell ref="C55:G55"/>
-    <mergeCell ref="C56:G56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="C61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="C63:G63"/>
-    <mergeCell ref="C54:G54"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2840,7 +2841,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E5051E-34BB-454A-9E98-0A0156A4405B}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="14" bestFit="1" customWidth="1"/>
@@ -2850,15 +2851,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="72">
+      <c r="A1" s="68">
         <v>46235</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3064,52 +3065,52 @@
       <c r="B18" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="77" t="s">
+      <c r="C18" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="78"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="48"/>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="26"/>
       <c r="B19" s="45"/>
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="80"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="50"/>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>46245</v>
       </c>
-      <c r="B20" s="78" t="s">
+      <c r="B20" s="48" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="78"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="48"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
-      <c r="B21" s="80"/>
+      <c r="B21" s="50"/>
       <c r="C21" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="80"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="50"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="46"/>
@@ -3119,10 +3120,10 @@
       <c r="C22" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="78"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="48"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="46"/>
@@ -3130,10 +3131,10 @@
       <c r="C23" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="82"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="51"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="46"/>
@@ -3141,10 +3142,10 @@
       <c r="C24" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="82"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="51"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="45"/>
@@ -3152,10 +3153,21 @@
       <c r="C25" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="80"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="50"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="82">
+        <v>46246</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/5. Other/Nội dung công việc hàng ngày.xlsx
+++ b/5. Other/Nội dung công việc hàng ngày.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D142825-4500-4EF6-BE48-5D1772AB7328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEF0CCD-930B-40A2-BE76-5A81A89843ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{F20CEA29-D7AE-4CD4-9104-84E191A61AC3}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="128">
   <si>
     <t>Hoàn thiện 73 dây nguồn VNSH03</t>
   </si>
@@ -405,6 +405,15 @@
   </si>
   <si>
     <t>Nhập kho 23 LE UPG</t>
+  </si>
+  <si>
+    <t>Trả BH Minh Huy</t>
+  </si>
+  <si>
+    <t>Trả BH Nhật Quang</t>
+  </si>
+  <si>
+    <t>Trả BH HTA</t>
   </si>
 </sst>
 </file>
@@ -628,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -755,6 +764,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -767,38 +794,47 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -809,9 +845,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -821,31 +854,9 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1168,15 +1179,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="60">
+      <c r="A1" s="52">
         <v>46174</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1185,146 +1196,146 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="64"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="56"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="55">
+      <c r="A3" s="61">
         <v>46202</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56" t="s">
+      <c r="A4" s="61"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="55"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56" t="s">
+      <c r="A5" s="61"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="56" t="s">
+      <c r="A6" s="61"/>
+      <c r="B6" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="56" t="s">
+      <c r="A7" s="61"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56" t="s">
+      <c r="A8" s="61"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="55">
+      <c r="A9" s="61">
         <v>46203</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="59"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="64"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="52" t="s">
+      <c r="A10" s="61"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="54"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="60"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="52" t="s">
+      <c r="A11" s="61"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="54"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="60"/>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55"/>
-      <c r="B12" s="56"/>
-      <c r="C12" s="52" t="s">
+      <c r="A12" s="61"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="54"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="60"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="55"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="54"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="60"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:G8" xr:uid="{5B424F82-FB95-405B-80D1-35D47957B3B0}">
@@ -1334,6 +1345,14 @@
     <filterColumn colId="5" showButton="0"/>
   </autoFilter>
   <mergeCells count="18">
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B6:B8"/>
@@ -1344,14 +1363,6 @@
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1369,15 +1380,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="68">
+      <c r="A1" s="77">
         <v>46204</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1386,152 +1397,152 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="55">
+      <c r="A3" s="61">
         <v>46204</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
-      <c r="B4" s="56" t="s">
+      <c r="A4" s="61"/>
+      <c r="B4" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="55"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56" t="s">
+      <c r="A5" s="61"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="56" t="s">
+      <c r="A6" s="61"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="71">
+      <c r="A7" s="79">
         <v>46205</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="59"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="64"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="52" t="s">
+      <c r="A8" s="80"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="54"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="60"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="52" t="s">
+      <c r="A9" s="80"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="60"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="56" t="s">
+      <c r="A10" s="80"/>
+      <c r="B10" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="54"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="60"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="52" t="s">
+      <c r="A11" s="80"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="54"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="60"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="56"/>
-      <c r="C12" s="52" t="s">
+      <c r="A12" s="80"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="54"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="60"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="73"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="52" t="s">
+      <c r="A13" s="81"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="54"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="60"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="75">
+      <c r="A14" s="70">
         <v>46206</v>
       </c>
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="68" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1543,348 +1554,348 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="76"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="57" t="s">
+      <c r="A15" s="73"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="59"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="64"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="76"/>
-      <c r="B16" s="67"/>
-      <c r="C16" s="57" t="s">
+      <c r="A16" s="73"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="59"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="64"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="76"/>
-      <c r="B17" s="66"/>
-      <c r="C17" s="57" t="s">
+      <c r="A17" s="73"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="59"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="64"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="76"/>
-      <c r="B18" s="65" t="s">
+      <c r="A18" s="73"/>
+      <c r="B18" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="59"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="64"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="77"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="57" t="s">
+      <c r="A19" s="71"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="59"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="64"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="78">
+      <c r="A20" s="74">
         <v>46209</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="78"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56" t="s">
+      <c r="A21" s="74"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="78"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="56" t="s">
+      <c r="A22" s="74"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="78"/>
-      <c r="B23" s="56" t="s">
+      <c r="A23" s="74"/>
+      <c r="B23" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="56" t="s">
+      <c r="C23" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="78"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="57" t="s">
+      <c r="A24" s="74"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="59"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="64"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="78"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="57" t="s">
+      <c r="A25" s="74"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="59"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="64"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="78"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="57" t="s">
+      <c r="A26" s="74"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="59"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="64"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="78"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="57" t="s">
+      <c r="A27" s="74"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="59"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="64"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="78"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="57" t="s">
+      <c r="A28" s="74"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="59"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="64"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="78"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="57" t="s">
+      <c r="A29" s="74"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="59"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="64"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="78"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="57" t="s">
+      <c r="A30" s="74"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="59"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="64"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="78"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="57" t="s">
+      <c r="A31" s="74"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="59"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="64"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="78"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="57" t="s">
+      <c r="A32" s="74"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="59"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="64"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="78"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="57" t="s">
+      <c r="A33" s="74"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="59"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="64"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="78"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="57" t="s">
+      <c r="A34" s="74"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="59"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="64"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="74">
+      <c r="A35" s="72">
         <v>46210</v>
       </c>
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="56" t="s">
+      <c r="C35" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="74"/>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56" t="s">
+      <c r="A36" s="72"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="74"/>
-      <c r="B37" s="56"/>
-      <c r="C37" s="56" t="s">
+      <c r="A37" s="72"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="74"/>
-      <c r="B38" s="56" t="s">
+      <c r="A38" s="72"/>
+      <c r="B38" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="56" t="s">
+      <c r="C38" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="74"/>
-      <c r="B39" s="56"/>
-      <c r="C39" s="56" t="s">
+      <c r="A39" s="72"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="74"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56" t="s">
+      <c r="A40" s="72"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="74"/>
-      <c r="B41" s="56"/>
-      <c r="C41" s="56" t="s">
+      <c r="A41" s="72"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="74"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56" t="s">
+      <c r="A42" s="72"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="74"/>
-      <c r="B43" s="56"/>
-      <c r="C43" s="56" t="s">
+      <c r="A43" s="72"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="74"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="57" t="s">
+      <c r="A44" s="72"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="59"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="64"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
@@ -1893,13 +1904,13 @@
       <c r="B45" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="56" t="s">
+      <c r="C45" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
@@ -1908,255 +1919,255 @@
       <c r="B46" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C46" s="56" t="s">
+      <c r="C46" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="75">
+      <c r="A47" s="70">
         <v>46213</v>
       </c>
-      <c r="B47" s="65" t="s">
+      <c r="B47" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="C47" s="57" t="s">
+      <c r="C47" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="59"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="64"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="76"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="57" t="s">
+      <c r="A48" s="73"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="59"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="64"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="76"/>
-      <c r="B49" s="67"/>
-      <c r="C49" s="57" t="s">
+      <c r="A49" s="73"/>
+      <c r="B49" s="76"/>
+      <c r="C49" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="59"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="64"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="76"/>
-      <c r="B50" s="67"/>
-      <c r="C50" s="57" t="s">
+      <c r="A50" s="73"/>
+      <c r="B50" s="76"/>
+      <c r="C50" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="59"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="64"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="77"/>
-      <c r="B51" s="66"/>
-      <c r="C51" s="57" t="s">
+      <c r="A51" s="71"/>
+      <c r="B51" s="69"/>
+      <c r="C51" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="59"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="64"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="55">
+      <c r="A52" s="61">
         <v>46214</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="56" t="s">
+      <c r="C52" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="56"/>
-      <c r="G52" s="56"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="55"/>
+      <c r="A53" s="61"/>
       <c r="B53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C53" s="56" t="s">
+      <c r="C53" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="55">
+      <c r="A54" s="61">
         <v>46216</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="57" t="s">
+      <c r="C54" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="59"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="64"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="55"/>
-      <c r="B55" s="56" t="s">
+      <c r="A55" s="61"/>
+      <c r="B55" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="79" t="s">
+      <c r="C55" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="79"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="79"/>
-      <c r="G55" s="79"/>
+      <c r="D55" s="75"/>
+      <c r="E55" s="75"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="75"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="55"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="79" t="s">
+      <c r="A56" s="61"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="79"/>
-      <c r="E56" s="79"/>
-      <c r="F56" s="79"/>
-      <c r="G56" s="79"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="75"/>
+      <c r="G56" s="75"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="55"/>
-      <c r="B57" s="56"/>
-      <c r="C57" s="79" t="s">
+      <c r="A57" s="61"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="D57" s="79"/>
-      <c r="E57" s="79"/>
-      <c r="F57" s="79"/>
-      <c r="G57" s="79"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="55"/>
-      <c r="B58" s="56"/>
-      <c r="C58" s="79" t="s">
+      <c r="A58" s="61"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="D58" s="79"/>
-      <c r="E58" s="79"/>
-      <c r="F58" s="79"/>
-      <c r="G58" s="79"/>
+      <c r="D58" s="75"/>
+      <c r="E58" s="75"/>
+      <c r="F58" s="75"/>
+      <c r="G58" s="75"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="55"/>
-      <c r="B59" s="56"/>
-      <c r="C59" s="79" t="s">
+      <c r="A59" s="61"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="79"/>
-      <c r="E59" s="79"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="79"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="75"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="55"/>
-      <c r="B60" s="56"/>
-      <c r="C60" s="79" t="s">
+      <c r="A60" s="61"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="79"/>
-      <c r="E60" s="79"/>
-      <c r="F60" s="79"/>
-      <c r="G60" s="79"/>
+      <c r="D60" s="75"/>
+      <c r="E60" s="75"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="75"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="55"/>
-      <c r="B61" s="56"/>
-      <c r="C61" s="79" t="s">
+      <c r="A61" s="61"/>
+      <c r="B61" s="57"/>
+      <c r="C61" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="D61" s="79"/>
-      <c r="E61" s="79"/>
-      <c r="F61" s="79"/>
-      <c r="G61" s="79"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="75"/>
+      <c r="G61" s="75"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="55"/>
-      <c r="B62" s="56"/>
-      <c r="C62" s="79" t="s">
+      <c r="A62" s="61"/>
+      <c r="B62" s="57"/>
+      <c r="C62" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D62" s="79"/>
-      <c r="E62" s="79"/>
-      <c r="F62" s="79"/>
-      <c r="G62" s="79"/>
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
+      <c r="F62" s="75"/>
+      <c r="G62" s="75"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="55"/>
-      <c r="B63" s="56"/>
-      <c r="C63" s="79" t="s">
+      <c r="A63" s="61"/>
+      <c r="B63" s="57"/>
+      <c r="C63" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="D63" s="79"/>
-      <c r="E63" s="79"/>
-      <c r="F63" s="79"/>
-      <c r="G63" s="79"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
+      <c r="F63" s="75"/>
+      <c r="G63" s="75"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="55">
+      <c r="A64" s="61">
         <v>46217</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="56" t="s">
+      <c r="C64" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D64" s="56"/>
-      <c r="E64" s="56"/>
-      <c r="F64" s="56"/>
-      <c r="G64" s="56"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="55"/>
-      <c r="B65" s="56" t="s">
+      <c r="A65" s="61"/>
+      <c r="B65" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="56" t="s">
+      <c r="C65" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="55"/>
-      <c r="B66" s="56"/>
-      <c r="C66" s="56" t="s">
+      <c r="A66" s="61"/>
+      <c r="B66" s="57"/>
+      <c r="C66" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="D66" s="56"/>
-      <c r="E66" s="56"/>
-      <c r="F66" s="56"/>
-      <c r="G66" s="56"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
@@ -2165,164 +2176,164 @@
       <c r="B67" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="56" t="s">
+      <c r="C67" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="D67" s="56"/>
-      <c r="E67" s="56"/>
-      <c r="F67" s="56"/>
-      <c r="G67" s="56"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="55">
+      <c r="A68" s="61">
         <v>46220</v>
       </c>
-      <c r="B68" s="56" t="s">
+      <c r="B68" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="56" t="s">
+      <c r="C68" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="D68" s="56"/>
-      <c r="E68" s="56"/>
-      <c r="F68" s="56"/>
-      <c r="G68" s="56"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="55"/>
-      <c r="B69" s="56"/>
-      <c r="C69" s="56" t="s">
+      <c r="A69" s="61"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="56"/>
-      <c r="E69" s="56"/>
-      <c r="F69" s="56"/>
-      <c r="G69" s="56"/>
+      <c r="D69" s="57"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="57"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="55">
+      <c r="A70" s="61">
         <v>46223</v>
       </c>
-      <c r="B70" s="56" t="s">
+      <c r="B70" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C70" s="57" t="s">
+      <c r="C70" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="D70" s="58"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="59"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="64"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="55"/>
-      <c r="B71" s="56"/>
-      <c r="C71" s="57" t="s">
+      <c r="A71" s="61"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="D71" s="58"/>
-      <c r="E71" s="58"/>
-      <c r="F71" s="58"/>
-      <c r="G71" s="59"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="63"/>
+      <c r="F71" s="63"/>
+      <c r="G71" s="64"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="55"/>
-      <c r="B72" s="56"/>
-      <c r="C72" s="57" t="s">
+      <c r="A72" s="61"/>
+      <c r="B72" s="57"/>
+      <c r="C72" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="D72" s="58"/>
-      <c r="E72" s="58"/>
-      <c r="F72" s="58"/>
-      <c r="G72" s="59"/>
+      <c r="D72" s="63"/>
+      <c r="E72" s="63"/>
+      <c r="F72" s="63"/>
+      <c r="G72" s="64"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="55"/>
-      <c r="B73" s="56"/>
-      <c r="C73" s="57" t="s">
+      <c r="A73" s="61"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="59"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="63"/>
+      <c r="F73" s="63"/>
+      <c r="G73" s="64"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="55"/>
-      <c r="B74" s="56"/>
-      <c r="C74" s="57" t="s">
+      <c r="A74" s="61"/>
+      <c r="B74" s="57"/>
+      <c r="C74" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="58"/>
-      <c r="E74" s="58"/>
-      <c r="F74" s="58"/>
-      <c r="G74" s="59"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="63"/>
+      <c r="F74" s="63"/>
+      <c r="G74" s="64"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="55"/>
-      <c r="B75" s="56"/>
-      <c r="C75" s="57" t="s">
+      <c r="A75" s="61"/>
+      <c r="B75" s="57"/>
+      <c r="C75" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="D75" s="58"/>
-      <c r="E75" s="58"/>
-      <c r="F75" s="58"/>
-      <c r="G75" s="59"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="63"/>
+      <c r="F75" s="63"/>
+      <c r="G75" s="64"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="55"/>
-      <c r="B76" s="56"/>
-      <c r="C76" s="57" t="s">
+      <c r="A76" s="61"/>
+      <c r="B76" s="57"/>
+      <c r="C76" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="D76" s="58"/>
-      <c r="E76" s="58"/>
-      <c r="F76" s="58"/>
-      <c r="G76" s="59"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="63"/>
+      <c r="F76" s="63"/>
+      <c r="G76" s="64"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="55"/>
-      <c r="B77" s="56"/>
-      <c r="C77" s="52" t="s">
+      <c r="A77" s="61"/>
+      <c r="B77" s="57"/>
+      <c r="C77" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="D77" s="53"/>
-      <c r="E77" s="53"/>
-      <c r="F77" s="53"/>
-      <c r="G77" s="54"/>
+      <c r="D77" s="59"/>
+      <c r="E77" s="59"/>
+      <c r="F77" s="59"/>
+      <c r="G77" s="60"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="55"/>
-      <c r="B78" s="56"/>
-      <c r="C78" s="52" t="s">
+      <c r="A78" s="61"/>
+      <c r="B78" s="57"/>
+      <c r="C78" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="D78" s="53"/>
-      <c r="E78" s="53"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="54"/>
+      <c r="D78" s="59"/>
+      <c r="E78" s="59"/>
+      <c r="F78" s="59"/>
+      <c r="G78" s="60"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="55"/>
-      <c r="B79" s="56"/>
-      <c r="C79" s="52" t="s">
+      <c r="A79" s="61"/>
+      <c r="B79" s="57"/>
+      <c r="C79" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="54"/>
+      <c r="D79" s="59"/>
+      <c r="E79" s="59"/>
+      <c r="F79" s="59"/>
+      <c r="G79" s="60"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="55"/>
-      <c r="B80" s="56"/>
-      <c r="C80" s="52" t="s">
+      <c r="A80" s="61"/>
+      <c r="B80" s="57"/>
+      <c r="C80" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="54"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="60"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
@@ -2331,353 +2342,353 @@
       <c r="B81" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C81" s="56" t="s">
+      <c r="C81" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="D81" s="56"/>
-      <c r="E81" s="56"/>
-      <c r="F81" s="56"/>
-      <c r="G81" s="56"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="57"/>
+      <c r="G81" s="57"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="55">
+      <c r="A82" s="61">
         <v>46225</v>
       </c>
-      <c r="B82" s="56" t="s">
+      <c r="B82" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C82" s="56" t="s">
+      <c r="C82" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="D82" s="56"/>
-      <c r="E82" s="56"/>
-      <c r="F82" s="56"/>
-      <c r="G82" s="56"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="57"/>
+      <c r="G82" s="57"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="55"/>
-      <c r="B83" s="56"/>
-      <c r="C83" s="56" t="s">
+      <c r="A83" s="61"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="56"/>
-      <c r="E83" s="56"/>
-      <c r="F83" s="56"/>
-      <c r="G83" s="56"/>
+      <c r="D83" s="57"/>
+      <c r="E83" s="57"/>
+      <c r="F83" s="57"/>
+      <c r="G83" s="57"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="55"/>
-      <c r="B84" s="56"/>
-      <c r="C84" s="56" t="s">
+      <c r="A84" s="61"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="56"/>
-      <c r="E84" s="56"/>
-      <c r="F84" s="56"/>
-      <c r="G84" s="56"/>
+      <c r="D84" s="57"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="57"/>
+      <c r="G84" s="57"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="55"/>
-      <c r="B85" s="56" t="s">
+      <c r="A85" s="61"/>
+      <c r="B85" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="56" t="s">
+      <c r="C85" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="56"/>
-      <c r="E85" s="56"/>
-      <c r="F85" s="56"/>
-      <c r="G85" s="56"/>
+      <c r="D85" s="57"/>
+      <c r="E85" s="57"/>
+      <c r="F85" s="57"/>
+      <c r="G85" s="57"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="55"/>
-      <c r="B86" s="56"/>
-      <c r="C86" s="56" t="s">
+      <c r="A86" s="61"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="D86" s="56"/>
-      <c r="E86" s="56"/>
-      <c r="F86" s="56"/>
-      <c r="G86" s="56"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="55"/>
-      <c r="B87" s="56"/>
-      <c r="C87" s="56" t="s">
+      <c r="A87" s="61"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="56"/>
-      <c r="E87" s="56"/>
-      <c r="F87" s="56"/>
-      <c r="G87" s="56"/>
+      <c r="D87" s="57"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="57"/>
+      <c r="G87" s="57"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="55"/>
-      <c r="B88" s="56"/>
-      <c r="C88" s="56" t="s">
+      <c r="A88" s="61"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="D88" s="56"/>
-      <c r="E88" s="56"/>
-      <c r="F88" s="56"/>
-      <c r="G88" s="56"/>
+      <c r="D88" s="57"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="57"/>
+      <c r="G88" s="57"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="55"/>
-      <c r="B89" s="56"/>
-      <c r="C89" s="57" t="s">
+      <c r="A89" s="61"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="D89" s="58"/>
-      <c r="E89" s="58"/>
-      <c r="F89" s="58"/>
-      <c r="G89" s="59"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="63"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="64"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="55"/>
-      <c r="B90" s="56"/>
-      <c r="C90" s="56" t="s">
+      <c r="A90" s="61"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="56"/>
-      <c r="E90" s="56"/>
-      <c r="F90" s="56"/>
-      <c r="G90" s="56"/>
+      <c r="D90" s="57"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="57"/>
+      <c r="G90" s="57"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="75">
+      <c r="A91" s="70">
         <v>46227</v>
       </c>
-      <c r="B91" s="65" t="s">
+      <c r="B91" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="56" t="s">
+      <c r="C91" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="56"/>
-      <c r="E91" s="56"/>
-      <c r="F91" s="56"/>
-      <c r="G91" s="56"/>
+      <c r="D91" s="57"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="57"/>
+      <c r="G91" s="57"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="77"/>
-      <c r="B92" s="66"/>
-      <c r="C92" s="57" t="s">
+      <c r="A92" s="71"/>
+      <c r="B92" s="69"/>
+      <c r="C92" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="D92" s="58"/>
-      <c r="E92" s="58"/>
-      <c r="F92" s="58"/>
-      <c r="G92" s="59"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="63"/>
+      <c r="G92" s="64"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="55">
+      <c r="A93" s="61">
         <v>46228</v>
       </c>
-      <c r="B93" s="56" t="s">
+      <c r="B93" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C93" s="56" t="s">
+      <c r="C93" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="56"/>
-      <c r="E93" s="56"/>
-      <c r="F93" s="56"/>
-      <c r="G93" s="56"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="55"/>
-      <c r="B94" s="56"/>
-      <c r="C94" s="56" t="s">
+      <c r="A94" s="61"/>
+      <c r="B94" s="57"/>
+      <c r="C94" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="56"/>
-      <c r="E94" s="56"/>
-      <c r="F94" s="56"/>
-      <c r="G94" s="56"/>
+      <c r="D94" s="57"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="57"/>
+      <c r="G94" s="57"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="55"/>
-      <c r="B95" s="56"/>
-      <c r="C95" s="56" t="s">
+      <c r="A95" s="61"/>
+      <c r="B95" s="57"/>
+      <c r="C95" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="D95" s="56"/>
-      <c r="E95" s="56"/>
-      <c r="F95" s="56"/>
-      <c r="G95" s="56"/>
+      <c r="D95" s="57"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="57"/>
+      <c r="G95" s="57"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="55"/>
-      <c r="B96" s="56"/>
-      <c r="C96" s="56" t="s">
+      <c r="A96" s="61"/>
+      <c r="B96" s="57"/>
+      <c r="C96" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="D96" s="56"/>
-      <c r="E96" s="56"/>
-      <c r="F96" s="56"/>
-      <c r="G96" s="56"/>
+      <c r="D96" s="57"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="57"/>
+      <c r="G96" s="57"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="55"/>
-      <c r="B97" s="56"/>
-      <c r="C97" s="56" t="s">
+      <c r="A97" s="61"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="D97" s="56"/>
-      <c r="E97" s="56"/>
-      <c r="F97" s="56"/>
-      <c r="G97" s="56"/>
+      <c r="D97" s="57"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="57"/>
+      <c r="G97" s="57"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="55"/>
-      <c r="B98" s="56"/>
-      <c r="C98" s="56" t="s">
+      <c r="A98" s="61"/>
+      <c r="B98" s="57"/>
+      <c r="C98" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="D98" s="56"/>
-      <c r="E98" s="56"/>
-      <c r="F98" s="56"/>
-      <c r="G98" s="56"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="57"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="55">
+      <c r="A99" s="61">
         <v>46230</v>
       </c>
-      <c r="B99" s="56" t="s">
+      <c r="B99" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C99" s="56" t="s">
+      <c r="C99" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="D99" s="56"/>
-      <c r="E99" s="56"/>
-      <c r="F99" s="56"/>
-      <c r="G99" s="56"/>
+      <c r="D99" s="57"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="57"/>
+      <c r="G99" s="57"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="55"/>
-      <c r="B100" s="56"/>
-      <c r="C100" s="56" t="s">
+      <c r="A100" s="61"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D100" s="56"/>
-      <c r="E100" s="56"/>
-      <c r="F100" s="56"/>
-      <c r="G100" s="56"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="55">
+      <c r="A101" s="61">
         <v>46231</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="81" t="s">
+      <c r="C101" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="D101" s="81"/>
-      <c r="E101" s="81"/>
-      <c r="F101" s="81"/>
-      <c r="G101" s="81"/>
+      <c r="D101" s="67"/>
+      <c r="E101" s="67"/>
+      <c r="F101" s="67"/>
+      <c r="G101" s="67"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="55"/>
+      <c r="A102" s="61"/>
       <c r="B102" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C102" s="81" t="s">
+      <c r="C102" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="D102" s="81"/>
-      <c r="E102" s="81"/>
-      <c r="F102" s="81"/>
-      <c r="G102" s="81"/>
+      <c r="D102" s="67"/>
+      <c r="E102" s="67"/>
+      <c r="F102" s="67"/>
+      <c r="G102" s="67"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="80" t="s">
+      <c r="A103" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="56" t="s">
+      <c r="B103" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C103" s="70" t="s">
+      <c r="C103" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="D103" s="70"/>
-      <c r="E103" s="70"/>
-      <c r="F103" s="70"/>
-      <c r="G103" s="70"/>
+      <c r="D103" s="66"/>
+      <c r="E103" s="66"/>
+      <c r="F103" s="66"/>
+      <c r="G103" s="66"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="80"/>
-      <c r="B104" s="56"/>
-      <c r="C104" s="56" t="s">
+      <c r="A104" s="65"/>
+      <c r="B104" s="57"/>
+      <c r="C104" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="D104" s="56"/>
-      <c r="E104" s="56"/>
-      <c r="F104" s="56"/>
-      <c r="G104" s="56"/>
+      <c r="D104" s="57"/>
+      <c r="E104" s="57"/>
+      <c r="F104" s="57"/>
+      <c r="G104" s="57"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="80"/>
-      <c r="B105" s="56"/>
-      <c r="C105" s="56" t="s">
+      <c r="A105" s="65"/>
+      <c r="B105" s="57"/>
+      <c r="C105" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="D105" s="56"/>
-      <c r="E105" s="56"/>
-      <c r="F105" s="56"/>
-      <c r="G105" s="56"/>
+      <c r="D105" s="57"/>
+      <c r="E105" s="57"/>
+      <c r="F105" s="57"/>
+      <c r="G105" s="57"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="80"/>
-      <c r="B106" s="56"/>
-      <c r="C106" s="56" t="s">
+      <c r="A106" s="65"/>
+      <c r="B106" s="57"/>
+      <c r="C106" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="D106" s="56"/>
-      <c r="E106" s="56"/>
-      <c r="F106" s="56"/>
-      <c r="G106" s="56"/>
+      <c r="D106" s="57"/>
+      <c r="E106" s="57"/>
+      <c r="F106" s="57"/>
+      <c r="G106" s="57"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="80"/>
-      <c r="B107" s="56"/>
-      <c r="C107" s="56" t="s">
+      <c r="A107" s="65"/>
+      <c r="B107" s="57"/>
+      <c r="C107" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="56"/>
-      <c r="E107" s="56"/>
-      <c r="F107" s="56"/>
-      <c r="G107" s="56"/>
+      <c r="D107" s="57"/>
+      <c r="E107" s="57"/>
+      <c r="F107" s="57"/>
+      <c r="G107" s="57"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="55">
+      <c r="A108" s="61">
         <v>46234</v>
       </c>
-      <c r="B108" s="56" t="s">
+      <c r="B108" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C108" s="56" t="s">
+      <c r="C108" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="D108" s="56"/>
-      <c r="E108" s="56"/>
-      <c r="F108" s="56"/>
-      <c r="G108" s="56"/>
+      <c r="D108" s="57"/>
+      <c r="E108" s="57"/>
+      <c r="F108" s="57"/>
+      <c r="G108" s="57"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="55"/>
-      <c r="B109" s="56"/>
-      <c r="C109" s="56" t="s">
+      <c r="A109" s="61"/>
+      <c r="B109" s="57"/>
+      <c r="C109" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D109" s="56"/>
-      <c r="E109" s="56"/>
-      <c r="F109" s="56"/>
-      <c r="G109" s="56"/>
+      <c r="D109" s="57"/>
+      <c r="E109" s="57"/>
+      <c r="F109" s="57"/>
+      <c r="G109" s="57"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="10"/>
@@ -2687,68 +2698,67 @@
     </row>
   </sheetData>
   <mergeCells count="147">
-    <mergeCell ref="A103:A107"/>
-    <mergeCell ref="B103:B107"/>
-    <mergeCell ref="C103:G103"/>
-    <mergeCell ref="C104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C106:G106"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:G99"/>
-    <mergeCell ref="C100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="C102:G102"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="A93:A98"/>
-    <mergeCell ref="C93:G93"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="C91:G91"/>
-    <mergeCell ref="C92:G92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C89:G89"/>
-    <mergeCell ref="C82:G82"/>
-    <mergeCell ref="C83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="C85:G85"/>
-    <mergeCell ref="C86:G86"/>
-    <mergeCell ref="C87:G87"/>
-    <mergeCell ref="C88:G88"/>
-    <mergeCell ref="C90:G90"/>
-    <mergeCell ref="B85:B90"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="C69:G69"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="C65:G65"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="C64:G64"/>
-    <mergeCell ref="C81:G81"/>
-    <mergeCell ref="B70:B80"/>
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="C70:G70"/>
-    <mergeCell ref="C71:G71"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="C73:G73"/>
-    <mergeCell ref="C74:G74"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="C77:G77"/>
-    <mergeCell ref="C78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="C80:G80"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C109:G109"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C20:G20"/>
+  